--- a/05-automation-vba/01-recording-macros/5.1-recording-macros.xlsx
+++ b/05-automation-vba/01-recording-macros/5.1-recording-macros.xlsx
@@ -266,6 +266,9 @@
     <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,14 +285,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -809,7 +809,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing your work with the answer key.</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
           <t>Right-click a shape → Assign Macro</t>
         </is>
       </c>
-      <c r="D15" s="21" t="n"/>
+      <c r="D15" s="25" t="n"/>
       <c r="E15" s="22" t="inlineStr">
         <is>
           <t>See key</t>
@@ -1430,37 +1430,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>CensusDate</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>FacilityID</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>DeptID</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>StaffedBeds</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>Admissions</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>Discharges</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>MidnightCensus</t>
         </is>
@@ -2301,37 +2301,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>CensusDate</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>FacilityID</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>DeptID</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>StaffedBeds</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>Admissions</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>Discharges</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>MidnightCensus</t>
         </is>
@@ -3201,52 +3201,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>EDVisitID</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>PatientID</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>ArrivalDateTime</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>ArrivalMode</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>ESILevel</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>ChiefComplaint</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>TriageDateTime</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>ProviderSeenDateTime</t>
         </is>
       </c>
-      <c r="I1" s="25" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>DepartureDateTime</t>
         </is>
       </c>
-      <c r="J1" s="25" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>EDDisposition</t>
         </is>
@@ -3263,7 +3263,7 @@
           <t>PT10005</t>
         </is>
       </c>
-      <c r="C2" s="26" t="n">
+      <c r="C2" s="27" t="n">
         <v>45962.22708333333</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -3279,13 +3279,13 @@
           <t>Abdominal Pain / Vomiting</t>
         </is>
       </c>
-      <c r="G2" s="26" t="n">
+      <c r="G2" s="27" t="n">
         <v>45962.22986111111</v>
       </c>
-      <c r="H2" s="26" t="n">
+      <c r="H2" s="27" t="n">
         <v>45962.23125</v>
       </c>
-      <c r="I2" s="26" t="n">
+      <c r="I2" s="27" t="n">
         <v>45962.35902777778</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -3305,7 +3305,7 @@
           <t>PT10010</t>
         </is>
       </c>
-      <c r="C3" s="26" t="n">
+      <c r="C3" s="27" t="n">
         <v>45988.65208333333</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -3321,13 +3321,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G3" s="26" t="n">
+      <c r="G3" s="27" t="n">
         <v>45988.66180555556</v>
       </c>
-      <c r="H3" s="26" t="n">
+      <c r="H3" s="27" t="n">
         <v>45988.67152777778</v>
       </c>
-      <c r="I3" s="26" t="n">
+      <c r="I3" s="27" t="n">
         <v>45988.74305555555</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -3347,7 +3347,7 @@
           <t>PT10062</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="27" t="n">
         <v>45976.31527777778</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -3363,13 +3363,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="27" t="n">
         <v>45976.32222222222</v>
       </c>
-      <c r="H4" s="26" t="n">
+      <c r="H4" s="27" t="n">
         <v>45976.35486111111</v>
       </c>
-      <c r="I4" s="26" t="n">
+      <c r="I4" s="27" t="n">
         <v>45976.45208333333</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -3389,7 +3389,7 @@
           <t>PT10074</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="27" t="n">
         <v>45978.54583333333</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -3405,13 +3405,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="27" t="n">
         <v>45978.55416666667</v>
       </c>
-      <c r="H5" s="26" t="n">
+      <c r="H5" s="27" t="n">
         <v>45978.55902777778</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="27" t="n">
         <v>45978.66597222222</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -3431,7 +3431,7 @@
           <t>PT10177</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>45979.63611111111</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -3447,13 +3447,13 @@
           <t>Tremors / Alcohol Withdrawal</t>
         </is>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="27" t="n">
         <v>45979.64583333334</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="27" t="n">
         <v>45979.65347222222</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="27" t="n">
         <v>45979.77916666667</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -3473,7 +3473,7 @@
           <t>PT10181</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="27" t="n">
         <v>45985.73125</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -3489,13 +3489,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="27" t="n">
         <v>45985.73611111111</v>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="27" t="n">
         <v>45985.80625</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="27" t="n">
         <v>45985.88680555556</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -3515,7 +3515,7 @@
           <t>PT10387</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="27" t="n">
         <v>45985.55</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -3531,13 +3531,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="27" t="n">
         <v>45985.55277777778</v>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="27" t="n">
         <v>45985.55555555555</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="27" t="n">
         <v>45985.83125</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -3557,7 +3557,7 @@
           <t>PT10398</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="27" t="n">
         <v>45967.71111111111</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -3573,13 +3573,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="27" t="n">
         <v>45967.71736111111</v>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="27" t="n">
         <v>45967.75277777778</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="27" t="n">
         <v>45967.91458333333</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -3599,7 +3599,7 @@
           <t>PT10460</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="27" t="n">
         <v>45982.75833333333</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -3615,13 +3615,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="27" t="n">
         <v>45982.76041666666</v>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="27" t="n">
         <v>45982.78611111111</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="27" t="n">
         <v>45982.90208333333</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -3641,7 +3641,7 @@
           <t>PT10463</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="27" t="n">
         <v>45982.24513888889</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -3657,13 +3657,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="27" t="n">
         <v>45982.24861111111</v>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="27" t="n">
         <v>45982.25694444445</v>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I11" s="27" t="n">
         <v>45982.37361111111</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -3683,7 +3683,7 @@
           <t>PT10475</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="27" t="n">
         <v>45991.58055555556</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -3699,13 +3699,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="27" t="n">
         <v>45991.58888888889</v>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="27" t="n">
         <v>45991.61388888889</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="27" t="n">
         <v>45991.65208333333</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -3725,7 +3725,7 @@
           <t>PT10510</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="27" t="n">
         <v>45980.76944444444</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -3741,13 +3741,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="27" t="n">
         <v>45980.77986111111</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="27" t="n">
         <v>45980.79375</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="27" t="n">
         <v>45981.00902777778</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -3767,7 +3767,7 @@
           <t>PT10537</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>45978.65069444444</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -3783,13 +3783,13 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="27" t="n">
         <v>45978.65486111111</v>
       </c>
-      <c r="H14" s="26" t="n">
+      <c r="H14" s="27" t="n">
         <v>45978.72222222222</v>
       </c>
-      <c r="I14" s="26" t="n">
+      <c r="I14" s="27" t="n">
         <v>45979.04027777778</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -3809,7 +3809,7 @@
           <t>PT10568</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>45978.12638888889</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3825,13 +3825,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="27" t="n">
         <v>45978.13055555556</v>
       </c>
-      <c r="H15" s="26" t="n">
+      <c r="H15" s="27" t="n">
         <v>45978.13819444444</v>
       </c>
-      <c r="I15" s="26" t="n">
+      <c r="I15" s="27" t="n">
         <v>45978.24583333333</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -3851,7 +3851,7 @@
           <t>PT10601</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>45966.72430555556</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3867,13 +3867,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="27" t="n">
         <v>45966.72777777778</v>
       </c>
-      <c r="H16" s="26" t="n">
+      <c r="H16" s="27" t="n">
         <v>45966.73472222222</v>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I16" s="27" t="n">
         <v>45966.79652777778</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -3893,7 +3893,7 @@
           <t>PT10662</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>45968.65</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3909,13 +3909,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="27" t="n">
         <v>45968.65416666667</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="27" t="n">
         <v>45968.69513888889</v>
       </c>
-      <c r="I17" s="26" t="n">
+      <c r="I17" s="27" t="n">
         <v>45968.85</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -3935,7 +3935,7 @@
           <t>PT10749</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>45962.53680555556</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3951,13 +3951,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="27" t="n">
         <v>45962.54375</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="27" t="n">
         <v>45962.54513888889</v>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I18" s="27" t="n">
         <v>45962.74930555555</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -3977,7 +3977,7 @@
           <t>PT10774</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>45978.95694444444</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3993,13 +3993,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="27" t="n">
         <v>45978.96111111111</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="27" t="n">
         <v>45978.97847222222</v>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="27" t="n">
         <v>45979.12847222222</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -4019,7 +4019,7 @@
           <t>PT10786</t>
         </is>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>45966.63055555556</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -4035,13 +4035,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="27" t="n">
         <v>45966.64097222222</v>
       </c>
-      <c r="H20" s="26" t="n">
+      <c r="H20" s="27" t="n">
         <v>45966.67569444444</v>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I20" s="27" t="n">
         <v>45966.73194444444</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -4061,7 +4061,7 @@
           <t>PT10866</t>
         </is>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>45983.75902777778</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -4077,13 +4077,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G21" s="27" t="n">
         <v>45983.775</v>
       </c>
-      <c r="H21" s="26" t="n">
+      <c r="H21" s="27" t="n">
         <v>45983.77708333333</v>
       </c>
-      <c r="I21" s="26" t="n">
+      <c r="I21" s="27" t="n">
         <v>45984.00416666667</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -4103,7 +4103,7 @@
           <t>PT10891</t>
         </is>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>45969.90069444444</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -4119,13 +4119,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G22" s="26" t="n">
+      <c r="G22" s="27" t="n">
         <v>45969.90694444445</v>
       </c>
-      <c r="H22" s="26" t="n">
+      <c r="H22" s="27" t="n">
         <v>45969.90763888889</v>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I22" s="27" t="n">
         <v>45970.08541666667</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -4145,7 +4145,7 @@
           <t>PT10932</t>
         </is>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>45973.47986111111</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -4161,13 +4161,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G23" s="26" t="n">
+      <c r="G23" s="27" t="n">
         <v>45973.48472222222</v>
       </c>
-      <c r="H23" s="26" t="n">
+      <c r="H23" s="27" t="n">
         <v>45973.50138888889</v>
       </c>
-      <c r="I23" s="26" t="n">
+      <c r="I23" s="27" t="n">
         <v>45973.61319444444</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -4187,7 +4187,7 @@
           <t>PT10943</t>
         </is>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>45986.31041666667</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -4203,13 +4203,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G24" s="27" t="n">
         <v>45986.32361111111</v>
       </c>
-      <c r="H24" s="26" t="n">
+      <c r="H24" s="27" t="n">
         <v>45986.3375</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="27" t="n">
         <v>45986.48680555556</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -4229,7 +4229,7 @@
           <t>PT10956</t>
         </is>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>45967.41458333333</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -4245,13 +4245,13 @@
           <t>Fall / Hip Pain</t>
         </is>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="27" t="n">
         <v>45967.42083333333</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="27" t="n">
         <v>45967.43333333333</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="27" t="n">
         <v>45967.63680555556</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -4271,7 +4271,7 @@
           <t>PT11141</t>
         </is>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>45977.93055555555</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -4287,13 +4287,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="27" t="n">
         <v>45977.93333333333</v>
       </c>
-      <c r="H26" s="26" t="n">
+      <c r="H26" s="27" t="n">
         <v>45977.98333333333</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="27" t="n">
         <v>45978.10416666666</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -4313,7 +4313,7 @@
           <t>PT11188</t>
         </is>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>45973.53888888889</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -4329,13 +4329,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="27" t="n">
         <v>45973.54583333333</v>
       </c>
-      <c r="H27" s="26" t="n">
+      <c r="H27" s="27" t="n">
         <v>45973.55833333333</v>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="27" t="n">
         <v>45973.675</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -4355,7 +4355,7 @@
           <t>PT11188</t>
         </is>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>45982.75833333333</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -4371,13 +4371,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="27" t="n">
         <v>45982.76111111111</v>
       </c>
-      <c r="H28" s="26" t="n">
+      <c r="H28" s="27" t="n">
         <v>45982.78333333333</v>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I28" s="27" t="n">
         <v>45982.95208333333</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -4397,7 +4397,7 @@
           <t>PT11231</t>
         </is>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>45963.43402777778</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -4413,13 +4413,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G29" s="26" t="n">
+      <c r="G29" s="27" t="n">
         <v>45963.4375</v>
       </c>
-      <c r="H29" s="26" t="n">
+      <c r="H29" s="27" t="n">
         <v>45963.49097222222</v>
       </c>
-      <c r="I29" s="26" t="n">
+      <c r="I29" s="27" t="n">
         <v>45963.53819444445</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -4439,7 +4439,7 @@
           <t>PT11243</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>45964.74652777778</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -4455,13 +4455,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G30" s="27" t="n">
         <v>45964.75416666667</v>
       </c>
-      <c r="H30" s="26" t="n">
+      <c r="H30" s="27" t="n">
         <v>45964.77638888889</v>
       </c>
-      <c r="I30" s="26" t="n">
+      <c r="I30" s="27" t="n">
         <v>45964.84791666667</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -4481,7 +4481,7 @@
           <t>PT11274</t>
         </is>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>45980.45763888889</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -4497,13 +4497,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G31" s="26" t="n">
+      <c r="G31" s="27" t="n">
         <v>45980.46111111111</v>
       </c>
-      <c r="H31" s="26" t="n">
+      <c r="H31" s="27" t="n">
         <v>45980.51875</v>
       </c>
-      <c r="I31" s="26" t="n">
+      <c r="I31" s="27" t="n">
         <v>45980.68402777778</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -4523,7 +4523,7 @@
           <t>PT11381</t>
         </is>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>45966.8875</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -4539,13 +4539,13 @@
           <t>High Blood Sugar</t>
         </is>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G32" s="27" t="n">
         <v>45966.89375</v>
       </c>
-      <c r="H32" s="26" t="n">
+      <c r="H32" s="27" t="n">
         <v>45966.93402777778</v>
       </c>
-      <c r="I32" s="26" t="n">
+      <c r="I32" s="27" t="n">
         <v>45967.05625</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -4565,7 +4565,7 @@
           <t>PT11401</t>
         </is>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>45973.4875</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -4581,13 +4581,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G33" s="27" t="n">
         <v>45973.49166666667</v>
       </c>
-      <c r="H33" s="26" t="n">
+      <c r="H33" s="27" t="n">
         <v>45973.57083333333</v>
       </c>
-      <c r="I33" s="26" t="n">
+      <c r="I33" s="27" t="n">
         <v>45973.62430555555</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -4607,7 +4607,7 @@
           <t>PT11412</t>
         </is>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>45972.04166666666</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -4623,13 +4623,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G34" s="26" t="n">
+      <c r="G34" s="27" t="n">
         <v>45972.05555555555</v>
       </c>
-      <c r="H34" s="26" t="n">
+      <c r="H34" s="27" t="n">
         <v>45972.05625</v>
       </c>
-      <c r="I34" s="26" t="n">
+      <c r="I34" s="27" t="n">
         <v>45972.28263888889</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -4649,7 +4649,7 @@
           <t>PT11433</t>
         </is>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>45982.39097222222</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -4665,13 +4665,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G35" s="26" t="n">
+      <c r="G35" s="27" t="n">
         <v>45982.39305555556</v>
       </c>
-      <c r="H35" s="26" t="n">
+      <c r="H35" s="27" t="n">
         <v>45982.40416666667</v>
       </c>
-      <c r="I35" s="26" t="n">
+      <c r="I35" s="27" t="n">
         <v>45982.54305555556</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -4691,7 +4691,7 @@
           <t>PT11443</t>
         </is>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>45978.29791666667</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -4707,13 +4707,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G36" s="26" t="n">
+      <c r="G36" s="27" t="n">
         <v>45978.31041666667</v>
       </c>
-      <c r="H36" s="26" t="n">
+      <c r="H36" s="27" t="n">
         <v>45978.325</v>
       </c>
-      <c r="I36" s="26" t="n">
+      <c r="I36" s="27" t="n">
         <v>45978.42152777778</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -4733,7 +4733,7 @@
           <t>PT11456</t>
         </is>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>45967.47361111111</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -4749,13 +4749,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G37" s="26" t="n">
+      <c r="G37" s="27" t="n">
         <v>45967.47638888889</v>
       </c>
-      <c r="H37" s="26" t="n">
+      <c r="H37" s="27" t="n">
         <v>45967.48958333334</v>
       </c>
-      <c r="I37" s="26" t="n">
+      <c r="I37" s="27" t="n">
         <v>45967.87638888889</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -4775,7 +4775,7 @@
           <t>PT11485</t>
         </is>
       </c>
-      <c r="C38" s="26" t="n">
+      <c r="C38" s="27" t="n">
         <v>45973.91736111111</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -4791,13 +4791,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G38" s="26" t="n">
+      <c r="G38" s="27" t="n">
         <v>45973.92291666667</v>
       </c>
-      <c r="H38" s="26" t="n">
+      <c r="H38" s="27" t="n">
         <v>45973.92361111111</v>
       </c>
-      <c r="I38" s="26" t="n">
+      <c r="I38" s="27" t="n">
         <v>45974.06041666667</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -4817,7 +4817,7 @@
           <t>PT11591</t>
         </is>
       </c>
-      <c r="C39" s="26" t="n">
+      <c r="C39" s="27" t="n">
         <v>45974.81458333333</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -4833,13 +4833,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G39" s="26" t="n">
+      <c r="G39" s="27" t="n">
         <v>45974.81944444445</v>
       </c>
-      <c r="H39" s="26" t="n">
+      <c r="H39" s="27" t="n">
         <v>45974.82152777778</v>
       </c>
-      <c r="I39" s="26" t="n">
+      <c r="I39" s="27" t="n">
         <v>45974.86527777778</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -4859,7 +4859,7 @@
           <t>PT11783</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n">
+      <c r="C40" s="27" t="n">
         <v>45965.52222222222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -4875,13 +4875,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G40" s="26" t="n">
+      <c r="G40" s="27" t="n">
         <v>45965.52430555555</v>
       </c>
-      <c r="H40" s="26" t="n">
+      <c r="H40" s="27" t="n">
         <v>45965.54722222222</v>
       </c>
-      <c r="I40" s="26" t="n">
+      <c r="I40" s="27" t="n">
         <v>45965.67361111111</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -4901,7 +4901,7 @@
           <t>PT11816</t>
         </is>
       </c>
-      <c r="C41" s="26" t="n">
+      <c r="C41" s="27" t="n">
         <v>45980.73888888889</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -4917,13 +4917,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G41" s="26" t="n">
+      <c r="G41" s="27" t="n">
         <v>45980.74375</v>
       </c>
-      <c r="H41" s="26" t="n">
+      <c r="H41" s="27" t="n">
         <v>45980.80972222222</v>
       </c>
-      <c r="I41" s="26" t="n">
+      <c r="I41" s="27" t="n">
         <v>45980.83541666667</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -4943,7 +4943,7 @@
           <t>PT11832</t>
         </is>
       </c>
-      <c r="C42" s="26" t="n">
+      <c r="C42" s="27" t="n">
         <v>45986.54097222222</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -4959,13 +4959,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G42" s="27" t="n">
         <v>45986.54930555556</v>
       </c>
-      <c r="H42" s="26" t="n">
+      <c r="H42" s="27" t="n">
         <v>45986.57013888889</v>
       </c>
-      <c r="I42" s="26" t="n">
+      <c r="I42" s="27" t="n">
         <v>45986.73194444444</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -4985,7 +4985,7 @@
           <t>PT11926</t>
         </is>
       </c>
-      <c r="C43" s="26" t="n">
+      <c r="C43" s="27" t="n">
         <v>45977.91319444445</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -5001,13 +5001,13 @@
           <t>Fall</t>
         </is>
       </c>
-      <c r="G43" s="26" t="n">
+      <c r="G43" s="27" t="n">
         <v>45977.92083333333</v>
       </c>
-      <c r="H43" s="26" t="n">
+      <c r="H43" s="27" t="n">
         <v>45977.92152777778</v>
       </c>
-      <c r="I43" s="26" t="n">
+      <c r="I43" s="27" t="n">
         <v>45978.11944444444</v>
       </c>
       <c r="J43" t="inlineStr">
@@ -5027,7 +5027,7 @@
           <t>PT12026</t>
         </is>
       </c>
-      <c r="C44" s="26" t="n">
+      <c r="C44" s="27" t="n">
         <v>45969.66875</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -5043,13 +5043,13 @@
           <t>Back Pain</t>
         </is>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G44" s="27" t="n">
         <v>45969.67430555556</v>
       </c>
-      <c r="H44" s="26" t="n">
+      <c r="H44" s="27" t="n">
         <v>45969.68888888889</v>
       </c>
-      <c r="I44" s="26" t="n">
+      <c r="I44" s="27" t="n">
         <v>45969.75763888889</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -5069,7 +5069,7 @@
           <t>PT12081</t>
         </is>
       </c>
-      <c r="C45" s="26" t="n">
+      <c r="C45" s="27" t="n">
         <v>45969.28888888889</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -5085,13 +5085,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G45" s="26" t="n">
+      <c r="G45" s="27" t="n">
         <v>45969.29444444444</v>
       </c>
-      <c r="H45" s="26" t="n">
+      <c r="H45" s="27" t="n">
         <v>45969.30694444444</v>
       </c>
-      <c r="I45" s="26" t="n">
+      <c r="I45" s="27" t="n">
         <v>45969.38055555556</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -5111,7 +5111,7 @@
           <t>PT12105</t>
         </is>
       </c>
-      <c r="C46" s="26" t="n">
+      <c r="C46" s="27" t="n">
         <v>45986.35</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -5127,13 +5127,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G46" s="26" t="n">
+      <c r="G46" s="27" t="n">
         <v>45986.35277777778</v>
       </c>
-      <c r="H46" s="26" t="n">
+      <c r="H46" s="27" t="n">
         <v>45986.37152777778</v>
       </c>
-      <c r="I46" s="26" t="n">
+      <c r="I46" s="27" t="n">
         <v>45986.41111111111</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -5153,7 +5153,7 @@
           <t>PT12123</t>
         </is>
       </c>
-      <c r="C47" s="26" t="n">
+      <c r="C47" s="27" t="n">
         <v>45981.42222222222</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -5169,13 +5169,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G47" s="26" t="n">
+      <c r="G47" s="27" t="n">
         <v>45981.42708333334</v>
       </c>
-      <c r="H47" s="26" t="n">
+      <c r="H47" s="27" t="n">
         <v>45981.45</v>
       </c>
-      <c r="I47" s="26" t="n">
+      <c r="I47" s="27" t="n">
         <v>45981.49583333333</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -5195,7 +5195,7 @@
           <t>PT12166</t>
         </is>
       </c>
-      <c r="C48" s="26" t="n">
+      <c r="C48" s="27" t="n">
         <v>45962.35902777778</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -5211,13 +5211,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G48" s="26" t="n">
+      <c r="G48" s="27" t="n">
         <v>45962.36458333334</v>
       </c>
-      <c r="H48" s="26" t="n">
+      <c r="H48" s="27" t="n">
         <v>45962.42847222222</v>
       </c>
-      <c r="I48" s="26" t="n">
+      <c r="I48" s="27" t="n">
         <v>45962.49166666667</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -5237,7 +5237,7 @@
           <t>PT12166</t>
         </is>
       </c>
-      <c r="C49" s="26" t="n">
+      <c r="C49" s="27" t="n">
         <v>45973.89791666667</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -5253,13 +5253,13 @@
           <t>Bloody Stool / Vomiting Blood</t>
         </is>
       </c>
-      <c r="G49" s="26" t="n">
+      <c r="G49" s="27" t="n">
         <v>45973.90486111111</v>
       </c>
-      <c r="H49" s="26" t="n">
+      <c r="H49" s="27" t="n">
         <v>45973.90555555555</v>
       </c>
-      <c r="I49" s="26" t="n">
+      <c r="I49" s="27" t="n">
         <v>45974.27430555555</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -5279,7 +5279,7 @@
           <t>PT12206</t>
         </is>
       </c>
-      <c r="C50" s="26" t="n">
+      <c r="C50" s="27" t="n">
         <v>45972.43958333333</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -5295,13 +5295,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G50" s="26" t="n">
+      <c r="G50" s="27" t="n">
         <v>45972.45625</v>
       </c>
-      <c r="H50" s="26" t="n">
+      <c r="H50" s="27" t="n">
         <v>45972.45694444444</v>
       </c>
-      <c r="I50" s="26" t="n">
+      <c r="I50" s="27" t="n">
         <v>45972.90972222222</v>
       </c>
       <c r="J50" t="inlineStr">
@@ -5321,7 +5321,7 @@
           <t>PT12242</t>
         </is>
       </c>
-      <c r="C51" s="26" t="n">
+      <c r="C51" s="27" t="n">
         <v>45967.6375</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -5337,13 +5337,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G51" s="26" t="n">
+      <c r="G51" s="27" t="n">
         <v>45967.64097222222</v>
       </c>
-      <c r="H51" s="26" t="n">
+      <c r="H51" s="27" t="n">
         <v>45967.65763888889</v>
       </c>
-      <c r="I51" s="26" t="n">
+      <c r="I51" s="27" t="n">
         <v>45967.80277777778</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -5363,7 +5363,7 @@
           <t>PT12285</t>
         </is>
       </c>
-      <c r="C52" s="26" t="n">
+      <c r="C52" s="27" t="n">
         <v>45985.57569444444</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -5379,13 +5379,13 @@
           <t>Laceration</t>
         </is>
       </c>
-      <c r="G52" s="26" t="n">
+      <c r="G52" s="27" t="n">
         <v>45985.58125</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H52" s="27" t="n">
         <v>45985.65625</v>
       </c>
-      <c r="I52" s="26" t="n">
+      <c r="I52" s="27" t="n">
         <v>45985.79791666667</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -5405,7 +5405,7 @@
           <t>PT12299</t>
         </is>
       </c>
-      <c r="C53" s="26" t="n">
+      <c r="C53" s="27" t="n">
         <v>45974.40555555555</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -5421,13 +5421,13 @@
           <t>Dizziness</t>
         </is>
       </c>
-      <c r="G53" s="26" t="n">
+      <c r="G53" s="27" t="n">
         <v>45974.41180555556</v>
       </c>
-      <c r="H53" s="26" t="n">
+      <c r="H53" s="27" t="n">
         <v>45974.47013888889</v>
       </c>
-      <c r="I53" s="26" t="n">
+      <c r="I53" s="27" t="n">
         <v>45974.69236111111</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -5447,7 +5447,7 @@
           <t>PT12314</t>
         </is>
       </c>
-      <c r="C54" s="26" t="n">
+      <c r="C54" s="27" t="n">
         <v>45987.23402777778</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -5463,13 +5463,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G54" s="26" t="n">
+      <c r="G54" s="27" t="n">
         <v>45987.23958333334</v>
       </c>
-      <c r="H54" s="26" t="n">
+      <c r="H54" s="27" t="n">
         <v>45987.26458333333</v>
       </c>
-      <c r="I54" s="26" t="n">
+      <c r="I54" s="27" t="n">
         <v>45987.37361111111</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -5489,7 +5489,7 @@
           <t>PT12519</t>
         </is>
       </c>
-      <c r="C55" s="26" t="n">
+      <c r="C55" s="27" t="n">
         <v>45971.49513888889</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -5505,13 +5505,13 @@
           <t>Weakness / Fatigue</t>
         </is>
       </c>
-      <c r="G55" s="26" t="n">
+      <c r="G55" s="27" t="n">
         <v>45971.50486111111</v>
       </c>
-      <c r="H55" s="26" t="n">
+      <c r="H55" s="27" t="n">
         <v>45971.51111111111</v>
       </c>
-      <c r="I55" s="26" t="n">
+      <c r="I55" s="27" t="n">
         <v>45971.77361111111</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -5531,7 +5531,7 @@
           <t>PT12563</t>
         </is>
       </c>
-      <c r="C56" s="26" t="n">
+      <c r="C56" s="27" t="n">
         <v>45991.15972222222</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -5547,13 +5547,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G56" s="26" t="n">
+      <c r="G56" s="27" t="n">
         <v>45991.16527777778</v>
       </c>
-      <c r="H56" s="26" t="n">
+      <c r="H56" s="27" t="n">
         <v>45991.16597222222</v>
       </c>
-      <c r="I56" s="26" t="n">
+      <c r="I56" s="27" t="n">
         <v>45991.33888888889</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -5573,7 +5573,7 @@
           <t>PT12641</t>
         </is>
       </c>
-      <c r="C57" s="26" t="n">
+      <c r="C57" s="27" t="n">
         <v>45982.55347222222</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -5589,13 +5589,13 @@
           <t>Vomiting / Diarrhea</t>
         </is>
       </c>
-      <c r="G57" s="26" t="n">
+      <c r="G57" s="27" t="n">
         <v>45982.56041666667</v>
       </c>
-      <c r="H57" s="26" t="n">
+      <c r="H57" s="27" t="n">
         <v>45982.62708333333</v>
       </c>
-      <c r="I57" s="26" t="n">
+      <c r="I57" s="27" t="n">
         <v>45982.70555555556</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -5615,7 +5615,7 @@
           <t>PT12695</t>
         </is>
       </c>
-      <c r="C58" s="26" t="n">
+      <c r="C58" s="27" t="n">
         <v>45989.82986111111</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -5631,13 +5631,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G58" s="26" t="n">
+      <c r="G58" s="27" t="n">
         <v>45989.83472222222</v>
       </c>
-      <c r="H58" s="26" t="n">
+      <c r="H58" s="27" t="n">
         <v>45989.89861111111</v>
       </c>
-      <c r="I58" s="26" t="n">
+      <c r="I58" s="27" t="n">
         <v>45989.98541666667</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -5657,7 +5657,7 @@
           <t>PT12735</t>
         </is>
       </c>
-      <c r="C59" s="26" t="n">
+      <c r="C59" s="27" t="n">
         <v>45964.76944444444</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -5673,13 +5673,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G59" s="26" t="n">
+      <c r="G59" s="27" t="n">
         <v>45964.77291666667</v>
       </c>
-      <c r="H59" s="26" t="n">
+      <c r="H59" s="27" t="n">
         <v>45964.78888888889</v>
       </c>
-      <c r="I59" s="26" t="n">
+      <c r="I59" s="27" t="n">
         <v>45964.88958333333</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -5699,7 +5699,7 @@
           <t>PT12735</t>
         </is>
       </c>
-      <c r="C60" s="26" t="n">
+      <c r="C60" s="27" t="n">
         <v>45977.00694444445</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -5715,13 +5715,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G60" s="26" t="n">
+      <c r="G60" s="27" t="n">
         <v>45977.01180555556</v>
       </c>
-      <c r="H60" s="26" t="n">
+      <c r="H60" s="27" t="n">
         <v>45977.03611111111</v>
       </c>
-      <c r="I60" s="26" t="n">
+      <c r="I60" s="27" t="n">
         <v>45977.14652777778</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -5741,7 +5741,7 @@
           <t>PT12749</t>
         </is>
       </c>
-      <c r="C61" s="26" t="n">
+      <c r="C61" s="27" t="n">
         <v>45963.88263888889</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -5757,13 +5757,13 @@
           <t>Rash</t>
         </is>
       </c>
-      <c r="G61" s="26" t="n">
+      <c r="G61" s="27" t="n">
         <v>45963.8875</v>
       </c>
-      <c r="H61" s="26" t="n">
+      <c r="H61" s="27" t="n">
         <v>45963.89861111111</v>
       </c>
-      <c r="I61" s="26" t="n">
+      <c r="I61" s="27" t="n">
         <v>45964.10347222222</v>
       </c>
       <c r="J61" t="inlineStr">
@@ -5783,7 +5783,7 @@
           <t>PT12774</t>
         </is>
       </c>
-      <c r="C62" s="26" t="n">
+      <c r="C62" s="27" t="n">
         <v>45984.73333333333</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -5799,10 +5799,10 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G62" s="26" t="n">
+      <c r="G62" s="27" t="n">
         <v>45984.73888888889</v>
       </c>
-      <c r="I62" s="26" t="n">
+      <c r="I62" s="27" t="n">
         <v>45984.78333333333</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -5822,7 +5822,7 @@
           <t>PT12802</t>
         </is>
       </c>
-      <c r="C63" s="26" t="n">
+      <c r="C63" s="27" t="n">
         <v>45965.56875</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -5838,13 +5838,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G63" s="26" t="n">
+      <c r="G63" s="27" t="n">
         <v>45965.57638888889</v>
       </c>
-      <c r="H63" s="26" t="n">
+      <c r="H63" s="27" t="n">
         <v>45965.6125</v>
       </c>
-      <c r="I63" s="26" t="n">
+      <c r="I63" s="27" t="n">
         <v>45965.72569444445</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -5864,7 +5864,7 @@
           <t>PT12851</t>
         </is>
       </c>
-      <c r="C64" s="26" t="n">
+      <c r="C64" s="27" t="n">
         <v>45977.26041666666</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -5880,13 +5880,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G64" s="26" t="n">
+      <c r="G64" s="27" t="n">
         <v>45977.26458333333</v>
       </c>
-      <c r="H64" s="26" t="n">
+      <c r="H64" s="27" t="n">
         <v>45977.27083333334</v>
       </c>
-      <c r="I64" s="26" t="n">
+      <c r="I64" s="27" t="n">
         <v>45977.43680555555</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -5906,7 +5906,7 @@
           <t>PT12893</t>
         </is>
       </c>
-      <c r="C65" s="26" t="n">
+      <c r="C65" s="27" t="n">
         <v>45988.59583333333</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -5922,13 +5922,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G65" s="26" t="n">
+      <c r="G65" s="27" t="n">
         <v>45988.60208333333</v>
       </c>
-      <c r="H65" s="26" t="n">
+      <c r="H65" s="27" t="n">
         <v>45988.65138888889</v>
       </c>
-      <c r="I65" s="26" t="n">
+      <c r="I65" s="27" t="n">
         <v>45988.71319444444</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -5948,7 +5948,7 @@
           <t>PT12896</t>
         </is>
       </c>
-      <c r="C66" s="26" t="n">
+      <c r="C66" s="27" t="n">
         <v>45963.58194444444</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -5964,13 +5964,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G66" s="26" t="n">
+      <c r="G66" s="27" t="n">
         <v>45963.58958333333</v>
       </c>
-      <c r="H66" s="26" t="n">
+      <c r="H66" s="27" t="n">
         <v>45963.59861111111</v>
       </c>
-      <c r="I66" s="26" t="n">
+      <c r="I66" s="27" t="n">
         <v>45963.80138888889</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -5990,7 +5990,7 @@
           <t>PT12929</t>
         </is>
       </c>
-      <c r="C67" s="26" t="n">
+      <c r="C67" s="27" t="n">
         <v>45982.09166666667</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -6006,13 +6006,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G67" s="26" t="n">
+      <c r="G67" s="27" t="n">
         <v>45982.09652777778</v>
       </c>
-      <c r="H67" s="26" t="n">
+      <c r="H67" s="27" t="n">
         <v>45982.11111111111</v>
       </c>
-      <c r="I67" s="26" t="n">
+      <c r="I67" s="27" t="n">
         <v>45982.14722222222</v>
       </c>
       <c r="J67" t="inlineStr">
@@ -6032,7 +6032,7 @@
           <t>PT12938</t>
         </is>
       </c>
-      <c r="C68" s="26" t="n">
+      <c r="C68" s="27" t="n">
         <v>45964.40972222222</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -6048,13 +6048,13 @@
           <t>High Blood Sugar</t>
         </is>
       </c>
-      <c r="G68" s="26" t="n">
+      <c r="G68" s="27" t="n">
         <v>45964.41527777778</v>
       </c>
-      <c r="H68" s="26" t="n">
+      <c r="H68" s="27" t="n">
         <v>45964.43125</v>
       </c>
-      <c r="I68" s="26" t="n">
+      <c r="I68" s="27" t="n">
         <v>45964.59791666667</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -6074,7 +6074,7 @@
           <t>PT12989</t>
         </is>
       </c>
-      <c r="C69" s="26" t="n">
+      <c r="C69" s="27" t="n">
         <v>45985.6875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -6090,10 +6090,10 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G69" s="26" t="n">
+      <c r="G69" s="27" t="n">
         <v>45985.68958333333</v>
       </c>
-      <c r="I69" s="26" t="n">
+      <c r="I69" s="27" t="n">
         <v>45985.79652777778</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -6113,7 +6113,7 @@
           <t>PT13110</t>
         </is>
       </c>
-      <c r="C70" s="26" t="n">
+      <c r="C70" s="27" t="n">
         <v>45970.00972222222</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -6129,13 +6129,13 @@
           <t>Palpitations</t>
         </is>
       </c>
-      <c r="G70" s="26" t="n">
+      <c r="G70" s="27" t="n">
         <v>45970.01319444444</v>
       </c>
-      <c r="H70" s="26" t="n">
+      <c r="H70" s="27" t="n">
         <v>45970.01388888889</v>
       </c>
-      <c r="I70" s="26" t="n">
+      <c r="I70" s="27" t="n">
         <v>45970.11736111111</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -6155,7 +6155,7 @@
           <t>PT13179</t>
         </is>
       </c>
-      <c r="C71" s="26" t="n">
+      <c r="C71" s="27" t="n">
         <v>45972.275</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -6171,13 +6171,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G71" s="26" t="n">
+      <c r="G71" s="27" t="n">
         <v>45972.27916666667</v>
       </c>
-      <c r="H71" s="26" t="n">
+      <c r="H71" s="27" t="n">
         <v>45972.28680555556</v>
       </c>
-      <c r="I71" s="26" t="n">
+      <c r="I71" s="27" t="n">
         <v>45972.36666666667</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -6197,7 +6197,7 @@
           <t>PT13217</t>
         </is>
       </c>
-      <c r="C72" s="26" t="n">
+      <c r="C72" s="27" t="n">
         <v>45984.72847222222</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -6213,13 +6213,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G72" s="26" t="n">
+      <c r="G72" s="27" t="n">
         <v>45984.73194444444</v>
       </c>
-      <c r="H72" s="26" t="n">
+      <c r="H72" s="27" t="n">
         <v>45984.75972222222</v>
       </c>
-      <c r="I72" s="26" t="n">
+      <c r="I72" s="27" t="n">
         <v>45984.99305555555</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -6239,7 +6239,7 @@
           <t>PT13427</t>
         </is>
       </c>
-      <c r="C73" s="26" t="n">
+      <c r="C73" s="27" t="n">
         <v>45990.44930555556</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -6255,13 +6255,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G73" s="26" t="n">
+      <c r="G73" s="27" t="n">
         <v>45990.45833333334</v>
       </c>
-      <c r="H73" s="26" t="n">
+      <c r="H73" s="27" t="n">
         <v>45990.47777777778</v>
       </c>
-      <c r="I73" s="26" t="n">
+      <c r="I73" s="27" t="n">
         <v>45990.60902777778</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -6281,7 +6281,7 @@
           <t>PT13519</t>
         </is>
       </c>
-      <c r="C74" s="26" t="n">
+      <c r="C74" s="27" t="n">
         <v>45991.72430555556</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -6297,13 +6297,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G74" s="26" t="n">
+      <c r="G74" s="27" t="n">
         <v>45991.72708333333</v>
       </c>
-      <c r="H74" s="26" t="n">
+      <c r="H74" s="27" t="n">
         <v>45991.74652777778</v>
       </c>
-      <c r="I74" s="26" t="n">
+      <c r="I74" s="27" t="n">
         <v>45992.02361111111</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -6323,7 +6323,7 @@
           <t>PT13560</t>
         </is>
       </c>
-      <c r="C75" s="26" t="n">
+      <c r="C75" s="27" t="n">
         <v>45978.92708333334</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -6339,10 +6339,10 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G75" s="26" t="n">
+      <c r="G75" s="27" t="n">
         <v>45978.93125</v>
       </c>
-      <c r="I75" s="26" t="n">
+      <c r="I75" s="27" t="n">
         <v>45978.97638888889</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -6362,7 +6362,7 @@
           <t>PT13575</t>
         </is>
       </c>
-      <c r="C76" s="26" t="n">
+      <c r="C76" s="27" t="n">
         <v>45984.97152777778</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -6378,13 +6378,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G76" s="26" t="n">
+      <c r="G76" s="27" t="n">
         <v>45984.97916666666</v>
       </c>
-      <c r="H76" s="26" t="n">
+      <c r="H76" s="27" t="n">
         <v>45984.98125</v>
       </c>
-      <c r="I76" s="26" t="n">
+      <c r="I76" s="27" t="n">
         <v>45985.04722222222</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -6404,7 +6404,7 @@
           <t>PT13601</t>
         </is>
       </c>
-      <c r="C77" s="26" t="n">
+      <c r="C77" s="27" t="n">
         <v>45968.84861111111</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -6420,13 +6420,13 @@
           <t>Fall</t>
         </is>
       </c>
-      <c r="G77" s="26" t="n">
+      <c r="G77" s="27" t="n">
         <v>45968.85902777778</v>
       </c>
-      <c r="H77" s="26" t="n">
+      <c r="H77" s="27" t="n">
         <v>45968.88611111111</v>
       </c>
-      <c r="I77" s="26" t="n">
+      <c r="I77" s="27" t="n">
         <v>45968.91527777778</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -6446,7 +6446,7 @@
           <t>PT13628</t>
         </is>
       </c>
-      <c r="C78" s="26" t="n">
+      <c r="C78" s="27" t="n">
         <v>45982.79513888889</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -6462,13 +6462,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G78" s="26" t="n">
+      <c r="G78" s="27" t="n">
         <v>45982.80486111111</v>
       </c>
-      <c r="H78" s="26" t="n">
+      <c r="H78" s="27" t="n">
         <v>45982.84375</v>
       </c>
-      <c r="I78" s="26" t="n">
+      <c r="I78" s="27" t="n">
         <v>45982.91527777778</v>
       </c>
       <c r="J78" t="inlineStr">
@@ -6488,7 +6488,7 @@
           <t>PT13702</t>
         </is>
       </c>
-      <c r="C79" s="26" t="n">
+      <c r="C79" s="27" t="n">
         <v>45991.50069444445</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -6504,13 +6504,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G79" s="26" t="n">
+      <c r="G79" s="27" t="n">
         <v>45991.50833333333</v>
       </c>
-      <c r="H79" s="26" t="n">
+      <c r="H79" s="27" t="n">
         <v>45991.50972222222</v>
       </c>
-      <c r="I79" s="26" t="n">
+      <c r="I79" s="27" t="n">
         <v>45991.60555555556</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -6530,7 +6530,7 @@
           <t>PT13869</t>
         </is>
       </c>
-      <c r="C80" s="26" t="n">
+      <c r="C80" s="27" t="n">
         <v>45990.72847222222</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -6546,13 +6546,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G80" s="26" t="n">
+      <c r="G80" s="27" t="n">
         <v>45990.73194444444</v>
       </c>
-      <c r="H80" s="26" t="n">
+      <c r="H80" s="27" t="n">
         <v>45990.74027777778</v>
       </c>
-      <c r="I80" s="26" t="n">
+      <c r="I80" s="27" t="n">
         <v>45990.82638888889</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -6572,7 +6572,7 @@
           <t>PT13940</t>
         </is>
       </c>
-      <c r="C81" s="26" t="n">
+      <c r="C81" s="27" t="n">
         <v>45963.57361111111</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -6588,13 +6588,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G81" s="26" t="n">
+      <c r="G81" s="27" t="n">
         <v>45963.57847222222</v>
       </c>
-      <c r="H81" s="26" t="n">
+      <c r="H81" s="27" t="n">
         <v>45963.58194444444</v>
       </c>
-      <c r="I81" s="26" t="n">
+      <c r="I81" s="27" t="n">
         <v>45963.72986111111</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -6630,52 +6630,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>EDVisitID</t>
         </is>
       </c>
-      <c r="B1" s="25" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>PatientID</t>
         </is>
       </c>
-      <c r="C1" s="25" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>ArrivalDateTime</t>
         </is>
       </c>
-      <c r="D1" s="25" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>ArrivalMode</t>
         </is>
       </c>
-      <c r="E1" s="25" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>ESILevel</t>
         </is>
       </c>
-      <c r="F1" s="25" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>ChiefComplaint</t>
         </is>
       </c>
-      <c r="G1" s="25" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>TriageDateTime</t>
         </is>
       </c>
-      <c r="H1" s="25" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>ProviderSeenDateTime</t>
         </is>
       </c>
-      <c r="I1" s="25" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>DepartureDateTime</t>
         </is>
       </c>
-      <c r="J1" s="25" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>EDDisposition</t>
         </is>
@@ -6692,7 +6692,7 @@
           <t>PT10032</t>
         </is>
       </c>
-      <c r="C2" s="26" t="n">
+      <c r="C2" s="27" t="n">
         <v>45995.46180555555</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6708,13 +6708,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G2" s="26" t="n">
+      <c r="G2" s="27" t="n">
         <v>45995.46597222222</v>
       </c>
-      <c r="H2" s="26" t="n">
+      <c r="H2" s="27" t="n">
         <v>45995.57847222222</v>
       </c>
-      <c r="I2" s="26" t="n">
+      <c r="I2" s="27" t="n">
         <v>45995.63055555556</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -6734,7 +6734,7 @@
           <t>PT10032</t>
         </is>
       </c>
-      <c r="C3" s="26" t="n">
+      <c r="C3" s="27" t="n">
         <v>46012.51111111111</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6750,10 +6750,10 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G3" s="26" t="n">
+      <c r="G3" s="27" t="n">
         <v>46012.51597222222</v>
       </c>
-      <c r="I3" s="26" t="n">
+      <c r="I3" s="27" t="n">
         <v>46012.60763888889</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -6773,7 +6773,7 @@
           <t>PT10052</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="27" t="n">
         <v>46011.26805555556</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6789,13 +6789,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="27" t="n">
         <v>46011.27291666667</v>
       </c>
-      <c r="H4" s="26" t="n">
+      <c r="H4" s="27" t="n">
         <v>46011.27361111111</v>
       </c>
-      <c r="I4" s="26" t="n">
+      <c r="I4" s="27" t="n">
         <v>46011.32708333333</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -6815,7 +6815,7 @@
           <t>PT10299</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="27" t="n">
         <v>45999.15555555555</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6831,13 +6831,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="27" t="n">
         <v>45999.15763888889</v>
       </c>
-      <c r="H5" s="26" t="n">
+      <c r="H5" s="27" t="n">
         <v>45999.175</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="27" t="n">
         <v>45999.27916666667</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -6857,7 +6857,7 @@
           <t>PT10337</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>46007.88819444444</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6873,13 +6873,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="27" t="n">
         <v>46007.89027777778</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="27" t="n">
         <v>46007.96041666667</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="27" t="n">
         <v>46008.12569444445</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -6899,7 +6899,7 @@
           <t>PT10384</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="27" t="n">
         <v>46010.8125</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6915,13 +6915,13 @@
           <t>Vomiting / Diarrhea</t>
         </is>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="27" t="n">
         <v>46010.81736111111</v>
       </c>
-      <c r="H7" s="26" t="n">
+      <c r="H7" s="27" t="n">
         <v>46010.85763888889</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="27" t="n">
         <v>46010.92013888889</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -6941,7 +6941,7 @@
           <t>PT10422</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="27" t="n">
         <v>46019.59027777778</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6957,13 +6957,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="27" t="n">
         <v>46019.60069444445</v>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="27" t="n">
         <v>46019.61875</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="27" t="n">
         <v>46019.67638888889</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -6983,7 +6983,7 @@
           <t>PT10495</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="27" t="n">
         <v>46006.52083333334</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6999,13 +6999,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="27" t="n">
         <v>46006.52638888889</v>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="27" t="n">
         <v>46006.54652777778</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="27" t="n">
         <v>46006.6375</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -7025,7 +7025,7 @@
           <t>PT10523</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="27" t="n">
         <v>45994.00208333333</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7041,13 +7041,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="27" t="n">
         <v>45994.00555555556</v>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="27" t="n">
         <v>45994.00694444445</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="27" t="n">
         <v>45994.15277777778</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -7067,7 +7067,7 @@
           <t>PT10591</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="27" t="n">
         <v>46021.76666666667</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7083,13 +7083,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="27" t="n">
         <v>46021.77083333334</v>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="27" t="n">
         <v>46021.78819444445</v>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I11" s="27" t="n">
         <v>46021.90763888889</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -7109,7 +7109,7 @@
           <t>PT10611</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="27" t="n">
         <v>46016.1</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7125,13 +7125,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="27" t="n">
         <v>46016.10555555556</v>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="27" t="n">
         <v>46016.10694444444</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="27" t="n">
         <v>46016.35486111111</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -7151,7 +7151,7 @@
           <t>PT10668</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="27" t="n">
         <v>45994.56319444445</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7167,13 +7167,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="27" t="n">
         <v>45994.56458333333</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="27" t="n">
         <v>45994.56527777778</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="27" t="n">
         <v>45994.77291666667</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -7193,7 +7193,7 @@
           <t>PT10721</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>45997.6875</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7209,13 +7209,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="27" t="n">
         <v>45997.69861111111</v>
       </c>
-      <c r="H14" s="26" t="n">
+      <c r="H14" s="27" t="n">
         <v>45997.71736111111</v>
       </c>
-      <c r="I14" s="26" t="n">
+      <c r="I14" s="27" t="n">
         <v>45998.27847222222</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -7235,7 +7235,7 @@
           <t>PT10786</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>46011.51041666666</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7251,13 +7251,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="27" t="n">
         <v>46011.51527777778</v>
       </c>
-      <c r="H15" s="26" t="n">
+      <c r="H15" s="27" t="n">
         <v>46011.51597222222</v>
       </c>
-      <c r="I15" s="26" t="n">
+      <c r="I15" s="27" t="n">
         <v>46011.81388888889</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -7277,7 +7277,7 @@
           <t>PT10786</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>46016.525</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7293,13 +7293,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="27" t="n">
         <v>46016.53125</v>
       </c>
-      <c r="H16" s="26" t="n">
+      <c r="H16" s="27" t="n">
         <v>46016.54375</v>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I16" s="27" t="n">
         <v>46016.58472222222</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -7319,7 +7319,7 @@
           <t>PT10815</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>45999.85347222222</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7335,13 +7335,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="27" t="n">
         <v>45999.85347222222</v>
       </c>
-      <c r="H17" s="26" t="n">
+      <c r="H17" s="27" t="n">
         <v>45999.85486111111</v>
       </c>
-      <c r="I17" s="26" t="n">
+      <c r="I17" s="27" t="n">
         <v>46000.03055555555</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -7361,7 +7361,7 @@
           <t>PT10855</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>46020.88541666666</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7377,13 +7377,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="27" t="n">
         <v>46020.89027777778</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="27" t="n">
         <v>46020.93680555555</v>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I18" s="27" t="n">
         <v>46020.99513888889</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -7403,7 +7403,7 @@
           <t>PT10886</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>46000.38263888889</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7419,13 +7419,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="27" t="n">
         <v>46000.38541666666</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="27" t="n">
         <v>46000.41388888889</v>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="27" t="n">
         <v>46000.49583333333</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -7445,7 +7445,7 @@
           <t>PT10969</t>
         </is>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>45993.33888888889</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7461,13 +7461,13 @@
           <t>Weakness / Fatigue</t>
         </is>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="27" t="n">
         <v>45993.34097222222</v>
       </c>
-      <c r="H20" s="26" t="n">
+      <c r="H20" s="27" t="n">
         <v>45993.38958333333</v>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I20" s="27" t="n">
         <v>45993.63958333333</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -7487,7 +7487,7 @@
           <t>PT10971</t>
         </is>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>45998.72013888889</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7503,13 +7503,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G21" s="27" t="n">
         <v>45998.725</v>
       </c>
-      <c r="H21" s="26" t="n">
+      <c r="H21" s="27" t="n">
         <v>45998.79236111111</v>
       </c>
-      <c r="I21" s="26" t="n">
+      <c r="I21" s="27" t="n">
         <v>45998.92986111111</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -7529,7 +7529,7 @@
           <t>PT11034</t>
         </is>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>46003.49722222222</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7545,13 +7545,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G22" s="26" t="n">
+      <c r="G22" s="27" t="n">
         <v>46003.50069444445</v>
       </c>
-      <c r="H22" s="26" t="n">
+      <c r="H22" s="27" t="n">
         <v>46003.53055555555</v>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I22" s="27" t="n">
         <v>46003.84652777778</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -7571,7 +7571,7 @@
           <t>PT11068</t>
         </is>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>46016.62013888889</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7587,13 +7587,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G23" s="26" t="n">
+      <c r="G23" s="27" t="n">
         <v>46016.63125</v>
       </c>
-      <c r="H23" s="26" t="n">
+      <c r="H23" s="27" t="n">
         <v>46016.67013888889</v>
       </c>
-      <c r="I23" s="26" t="n">
+      <c r="I23" s="27" t="n">
         <v>46016.72083333333</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -7613,7 +7613,7 @@
           <t>PT11101</t>
         </is>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>46006.94791666666</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7629,13 +7629,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G24" s="27" t="n">
         <v>46006.95277777778</v>
       </c>
-      <c r="H24" s="26" t="n">
+      <c r="H24" s="27" t="n">
         <v>46006.95486111111</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="27" t="n">
         <v>46007.25416666667</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -7655,7 +7655,7 @@
           <t>PT11115</t>
         </is>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>46004.24375</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7671,13 +7671,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="27" t="n">
         <v>46004.25347222222</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="27" t="n">
         <v>46004.25416666667</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="27" t="n">
         <v>46004.40902777778</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -7697,7 +7697,7 @@
           <t>PT11122</t>
         </is>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>45998.40277777778</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7713,13 +7713,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="27" t="n">
         <v>45998.41388888889</v>
       </c>
-      <c r="H26" s="26" t="n">
+      <c r="H26" s="27" t="n">
         <v>45998.41527777778</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="27" t="n">
         <v>45998.75277777778</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -7739,7 +7739,7 @@
           <t>PT11149</t>
         </is>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>45998.05208333334</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7755,13 +7755,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="27" t="n">
         <v>45998.05625</v>
       </c>
-      <c r="H27" s="26" t="n">
+      <c r="H27" s="27" t="n">
         <v>45998.05694444444</v>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="27" t="n">
         <v>45998.21736111111</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -7781,7 +7781,7 @@
           <t>PT11168</t>
         </is>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>45992.59166666667</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7797,13 +7797,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="27" t="n">
         <v>45992.59583333333</v>
       </c>
-      <c r="H28" s="26" t="n">
+      <c r="H28" s="27" t="n">
         <v>45992.62777777778</v>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I28" s="27" t="n">
         <v>45992.6625</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -7823,7 +7823,7 @@
           <t>PT11214</t>
         </is>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>46003.74444444444</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7839,13 +7839,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G29" s="26" t="n">
+      <c r="G29" s="27" t="n">
         <v>46003.74652777778</v>
       </c>
-      <c r="H29" s="26" t="n">
+      <c r="H29" s="27" t="n">
         <v>46003.76388888889</v>
       </c>
-      <c r="I29" s="26" t="n">
+      <c r="I29" s="27" t="n">
         <v>46004.13958333333</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -7865,7 +7865,7 @@
           <t>PT11240</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>46015.57847222222</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7881,13 +7881,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G30" s="27" t="n">
         <v>46015.58125</v>
       </c>
-      <c r="H30" s="26" t="n">
+      <c r="H30" s="27" t="n">
         <v>46015.64444444444</v>
       </c>
-      <c r="I30" s="26" t="n">
+      <c r="I30" s="27" t="n">
         <v>46015.99027777778</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -7907,7 +7907,7 @@
           <t>PT11246</t>
         </is>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>46016.66527777778</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7923,13 +7923,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G31" s="26" t="n">
+      <c r="G31" s="27" t="n">
         <v>46016.67013888889</v>
       </c>
-      <c r="H31" s="26" t="n">
+      <c r="H31" s="27" t="n">
         <v>46016.72013888889</v>
       </c>
-      <c r="I31" s="26" t="n">
+      <c r="I31" s="27" t="n">
         <v>46017.02361111111</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -7949,7 +7949,7 @@
           <t>PT11247</t>
         </is>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>45992.84583333333</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7965,13 +7965,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G32" s="27" t="n">
         <v>45992.85625</v>
       </c>
-      <c r="H32" s="26" t="n">
+      <c r="H32" s="27" t="n">
         <v>45992.86597222222</v>
       </c>
-      <c r="I32" s="26" t="n">
+      <c r="I32" s="27" t="n">
         <v>45993.11319444444</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -7991,7 +7991,7 @@
           <t>PT11427</t>
         </is>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>46018.62361111111</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8007,13 +8007,13 @@
           <t>Back Pain</t>
         </is>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G33" s="27" t="n">
         <v>46018.62916666667</v>
       </c>
-      <c r="H33" s="26" t="n">
+      <c r="H33" s="27" t="n">
         <v>46018.65208333333</v>
       </c>
-      <c r="I33" s="26" t="n">
+      <c r="I33" s="27" t="n">
         <v>46018.77986111111</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -8033,7 +8033,7 @@
           <t>PT11452</t>
         </is>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>46021.72222222222</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8049,13 +8049,13 @@
           <t>Rash</t>
         </is>
       </c>
-      <c r="G34" s="26" t="n">
+      <c r="G34" s="27" t="n">
         <v>46021.72638888889</v>
       </c>
-      <c r="H34" s="26" t="n">
+      <c r="H34" s="27" t="n">
         <v>46021.76041666666</v>
       </c>
-      <c r="I34" s="26" t="n">
+      <c r="I34" s="27" t="n">
         <v>46021.88958333333</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -8075,7 +8075,7 @@
           <t>PT11518</t>
         </is>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>46004.63194444445</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8091,13 +8091,13 @@
           <t>Vomiting / Diarrhea</t>
         </is>
       </c>
-      <c r="G35" s="26" t="n">
+      <c r="G35" s="27" t="n">
         <v>46004.63472222222</v>
       </c>
-      <c r="H35" s="26" t="n">
+      <c r="H35" s="27" t="n">
         <v>46004.67916666667</v>
       </c>
-      <c r="I35" s="26" t="n">
+      <c r="I35" s="27" t="n">
         <v>46004.80555555555</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -8117,7 +8117,7 @@
           <t>PT11542</t>
         </is>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>46013.27569444444</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8133,13 +8133,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G36" s="26" t="n">
+      <c r="G36" s="27" t="n">
         <v>46013.28402777778</v>
       </c>
-      <c r="H36" s="26" t="n">
+      <c r="H36" s="27" t="n">
         <v>46013.35</v>
       </c>
-      <c r="I36" s="26" t="n">
+      <c r="I36" s="27" t="n">
         <v>46013.43263888889</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -8159,7 +8159,7 @@
           <t>PT11548</t>
         </is>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>46004.5375</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8175,13 +8175,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G37" s="26" t="n">
+      <c r="G37" s="27" t="n">
         <v>46004.54236111111</v>
       </c>
-      <c r="H37" s="26" t="n">
+      <c r="H37" s="27" t="n">
         <v>46004.56111111111</v>
       </c>
-      <c r="I37" s="26" t="n">
+      <c r="I37" s="27" t="n">
         <v>46004.70694444444</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -8201,7 +8201,7 @@
           <t>PT11673</t>
         </is>
       </c>
-      <c r="C38" s="26" t="n">
+      <c r="C38" s="27" t="n">
         <v>45993.775</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8217,13 +8217,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G38" s="26" t="n">
+      <c r="G38" s="27" t="n">
         <v>45993.78333333333</v>
       </c>
-      <c r="H38" s="26" t="n">
+      <c r="H38" s="27" t="n">
         <v>45993.81527777778</v>
       </c>
-      <c r="I38" s="26" t="n">
+      <c r="I38" s="27" t="n">
         <v>45993.88055555556</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>PT11720</t>
         </is>
       </c>
-      <c r="C39" s="26" t="n">
+      <c r="C39" s="27" t="n">
         <v>46013.49513888889</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8259,13 +8259,13 @@
           <t>Fall / Hip Pain</t>
         </is>
       </c>
-      <c r="G39" s="26" t="n">
+      <c r="G39" s="27" t="n">
         <v>46013.49722222222</v>
       </c>
-      <c r="H39" s="26" t="n">
+      <c r="H39" s="27" t="n">
         <v>46013.51597222222</v>
       </c>
-      <c r="I39" s="26" t="n">
+      <c r="I39" s="27" t="n">
         <v>46013.78680555556</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -8285,7 +8285,7 @@
           <t>PT11727</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n">
+      <c r="C40" s="27" t="n">
         <v>46006.34444444445</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8301,13 +8301,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G40" s="26" t="n">
+      <c r="G40" s="27" t="n">
         <v>46006.34722222222</v>
       </c>
-      <c r="H40" s="26" t="n">
+      <c r="H40" s="27" t="n">
         <v>46006.35208333333</v>
       </c>
-      <c r="I40" s="26" t="n">
+      <c r="I40" s="27" t="n">
         <v>46006.51875</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -8327,7 +8327,7 @@
           <t>PT11783</t>
         </is>
       </c>
-      <c r="C41" s="26" t="n">
+      <c r="C41" s="27" t="n">
         <v>46017.37569444445</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8343,13 +8343,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G41" s="26" t="n">
+      <c r="G41" s="27" t="n">
         <v>46017.38194444445</v>
       </c>
-      <c r="H41" s="26" t="n">
+      <c r="H41" s="27" t="n">
         <v>46017.40972222222</v>
       </c>
-      <c r="I41" s="26" t="n">
+      <c r="I41" s="27" t="n">
         <v>46017.47777777778</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -8369,7 +8369,7 @@
           <t>PT11816</t>
         </is>
       </c>
-      <c r="C42" s="26" t="n">
+      <c r="C42" s="27" t="n">
         <v>46001.32847222222</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8385,13 +8385,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G42" s="27" t="n">
         <v>46001.33333333334</v>
       </c>
-      <c r="H42" s="26" t="n">
+      <c r="H42" s="27" t="n">
         <v>46001.33402777778</v>
       </c>
-      <c r="I42" s="26" t="n">
+      <c r="I42" s="27" t="n">
         <v>46001.59375</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -8411,7 +8411,7 @@
           <t>PT11968</t>
         </is>
       </c>
-      <c r="C43" s="26" t="n">
+      <c r="C43" s="27" t="n">
         <v>45998.75555555556</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8427,13 +8427,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G43" s="26" t="n">
+      <c r="G43" s="27" t="n">
         <v>45998.76527777778</v>
       </c>
-      <c r="H43" s="26" t="n">
+      <c r="H43" s="27" t="n">
         <v>45998.76597222222</v>
       </c>
-      <c r="I43" s="26" t="n">
+      <c r="I43" s="27" t="n">
         <v>45998.88472222222</v>
       </c>
       <c r="J43" t="inlineStr">
@@ -8453,7 +8453,7 @@
           <t>PT11968</t>
         </is>
       </c>
-      <c r="C44" s="26" t="n">
+      <c r="C44" s="27" t="n">
         <v>46003.28333333333</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8469,13 +8469,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G44" s="27" t="n">
         <v>46003.29027777778</v>
       </c>
-      <c r="H44" s="26" t="n">
+      <c r="H44" s="27" t="n">
         <v>46003.30625</v>
       </c>
-      <c r="I44" s="26" t="n">
+      <c r="I44" s="27" t="n">
         <v>46003.46527777778</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -8495,7 +8495,7 @@
           <t>PT11977</t>
         </is>
       </c>
-      <c r="C45" s="26" t="n">
+      <c r="C45" s="27" t="n">
         <v>46007.77708333333</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8511,13 +8511,13 @@
           <t>Bloody Stool / Vomiting Blood</t>
         </is>
       </c>
-      <c r="G45" s="26" t="n">
+      <c r="G45" s="27" t="n">
         <v>46007.79444444444</v>
       </c>
-      <c r="H45" s="26" t="n">
+      <c r="H45" s="27" t="n">
         <v>46007.81180555555</v>
       </c>
-      <c r="I45" s="26" t="n">
+      <c r="I45" s="27" t="n">
         <v>46007.98888888889</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -8537,7 +8537,7 @@
           <t>PT12024</t>
         </is>
       </c>
-      <c r="C46" s="26" t="n">
+      <c r="C46" s="27" t="n">
         <v>46001.67569444444</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8553,13 +8553,13 @@
           <t>Laceration</t>
         </is>
       </c>
-      <c r="G46" s="26" t="n">
+      <c r="G46" s="27" t="n">
         <v>46001.68263888889</v>
       </c>
-      <c r="H46" s="26" t="n">
+      <c r="H46" s="27" t="n">
         <v>46001.70277777778</v>
       </c>
-      <c r="I46" s="26" t="n">
+      <c r="I46" s="27" t="n">
         <v>46001.88541666666</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -8579,7 +8579,7 @@
           <t>PT12026</t>
         </is>
       </c>
-      <c r="C47" s="26" t="n">
+      <c r="C47" s="27" t="n">
         <v>46008.67013888889</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8595,13 +8595,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G47" s="26" t="n">
+      <c r="G47" s="27" t="n">
         <v>46008.67361111111</v>
       </c>
-      <c r="H47" s="26" t="n">
+      <c r="H47" s="27" t="n">
         <v>46008.73194444444</v>
       </c>
-      <c r="I47" s="26" t="n">
+      <c r="I47" s="27" t="n">
         <v>46008.83819444444</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -8621,7 +8621,7 @@
           <t>PT12054</t>
         </is>
       </c>
-      <c r="C48" s="26" t="n">
+      <c r="C48" s="27" t="n">
         <v>46021.48055555556</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -8637,13 +8637,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G48" s="26" t="n">
+      <c r="G48" s="27" t="n">
         <v>46021.48472222222</v>
       </c>
-      <c r="H48" s="26" t="n">
+      <c r="H48" s="27" t="n">
         <v>46021.53263888889</v>
       </c>
-      <c r="I48" s="26" t="n">
+      <c r="I48" s="27" t="n">
         <v>46021.61527777778</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -8663,7 +8663,7 @@
           <t>PT12159</t>
         </is>
       </c>
-      <c r="C49" s="26" t="n">
+      <c r="C49" s="27" t="n">
         <v>46007.76736111111</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -8679,13 +8679,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G49" s="26" t="n">
+      <c r="G49" s="27" t="n">
         <v>46007.76875</v>
       </c>
-      <c r="H49" s="26" t="n">
+      <c r="H49" s="27" t="n">
         <v>46007.78819444445</v>
       </c>
-      <c r="I49" s="26" t="n">
+      <c r="I49" s="27" t="n">
         <v>46007.94097222222</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -8705,7 +8705,7 @@
           <t>PT12166</t>
         </is>
       </c>
-      <c r="C50" s="26" t="n">
+      <c r="C50" s="27" t="n">
         <v>46020.66388888889</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -8721,13 +8721,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G50" s="26" t="n">
+      <c r="G50" s="27" t="n">
         <v>46020.67013888889</v>
       </c>
-      <c r="H50" s="26" t="n">
+      <c r="H50" s="27" t="n">
         <v>46020.71180555555</v>
       </c>
-      <c r="I50" s="26" t="n">
+      <c r="I50" s="27" t="n">
         <v>46020.79861111111</v>
       </c>
       <c r="J50" t="inlineStr">
@@ -8747,7 +8747,7 @@
           <t>PT12187</t>
         </is>
       </c>
-      <c r="C51" s="26" t="n">
+      <c r="C51" s="27" t="n">
         <v>45992.74791666667</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -8763,13 +8763,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G51" s="26" t="n">
+      <c r="G51" s="27" t="n">
         <v>45992.75625</v>
       </c>
-      <c r="H51" s="26" t="n">
+      <c r="H51" s="27" t="n">
         <v>45992.82083333333</v>
       </c>
-      <c r="I51" s="26" t="n">
+      <c r="I51" s="27" t="n">
         <v>45992.90625</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -8789,7 +8789,7 @@
           <t>PT12210</t>
         </is>
       </c>
-      <c r="C52" s="26" t="n">
+      <c r="C52" s="27" t="n">
         <v>46009.04722222222</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -8805,13 +8805,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G52" s="26" t="n">
+      <c r="G52" s="27" t="n">
         <v>46009.05763888889</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H52" s="27" t="n">
         <v>46009.06180555555</v>
       </c>
-      <c r="I52" s="26" t="n">
+      <c r="I52" s="27" t="n">
         <v>46009.18819444445</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -8831,7 +8831,7 @@
           <t>PT12274</t>
         </is>
       </c>
-      <c r="C53" s="26" t="n">
+      <c r="C53" s="27" t="n">
         <v>46013.71180555555</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -8847,13 +8847,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G53" s="26" t="n">
+      <c r="G53" s="27" t="n">
         <v>46013.72430555556</v>
       </c>
-      <c r="H53" s="26" t="n">
+      <c r="H53" s="27" t="n">
         <v>46013.75972222222</v>
       </c>
-      <c r="I53" s="26" t="n">
+      <c r="I53" s="27" t="n">
         <v>46013.84652777778</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -8873,7 +8873,7 @@
           <t>PT12307</t>
         </is>
       </c>
-      <c r="C54" s="26" t="n">
+      <c r="C54" s="27" t="n">
         <v>45993.67083333333</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -8889,13 +8889,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G54" s="26" t="n">
+      <c r="G54" s="27" t="n">
         <v>45993.68402777778</v>
       </c>
-      <c r="H54" s="26" t="n">
+      <c r="H54" s="27" t="n">
         <v>45993.74236111111</v>
       </c>
-      <c r="I54" s="26" t="n">
+      <c r="I54" s="27" t="n">
         <v>45993.78055555555</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -8915,7 +8915,7 @@
           <t>PT12325</t>
         </is>
       </c>
-      <c r="C55" s="26" t="n">
+      <c r="C55" s="27" t="n">
         <v>46010.80902777778</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -8931,13 +8931,13 @@
           <t>Fall / Hip Pain</t>
         </is>
       </c>
-      <c r="G55" s="26" t="n">
+      <c r="G55" s="27" t="n">
         <v>46010.8125</v>
       </c>
-      <c r="H55" s="26" t="n">
+      <c r="H55" s="27" t="n">
         <v>46010.87361111111</v>
       </c>
-      <c r="I55" s="26" t="n">
+      <c r="I55" s="27" t="n">
         <v>46011.19652777778</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -8957,7 +8957,7 @@
           <t>PT12362</t>
         </is>
       </c>
-      <c r="C56" s="26" t="n">
+      <c r="C56" s="27" t="n">
         <v>46016.23888888889</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8973,13 +8973,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G56" s="26" t="n">
+      <c r="G56" s="27" t="n">
         <v>46016.24444444444</v>
       </c>
-      <c r="H56" s="26" t="n">
+      <c r="H56" s="27" t="n">
         <v>46016.26805555556</v>
       </c>
-      <c r="I56" s="26" t="n">
+      <c r="I56" s="27" t="n">
         <v>46016.29652777778</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -8999,7 +8999,7 @@
           <t>PT12399</t>
         </is>
       </c>
-      <c r="C57" s="26" t="n">
+      <c r="C57" s="27" t="n">
         <v>46014.87638888889</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9015,13 +9015,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G57" s="26" t="n">
+      <c r="G57" s="27" t="n">
         <v>46014.88263888889</v>
       </c>
-      <c r="H57" s="26" t="n">
+      <c r="H57" s="27" t="n">
         <v>46014.92430555556</v>
       </c>
-      <c r="I57" s="26" t="n">
+      <c r="I57" s="27" t="n">
         <v>46015.19097222222</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -9041,7 +9041,7 @@
           <t>PT12426</t>
         </is>
       </c>
-      <c r="C58" s="26" t="n">
+      <c r="C58" s="27" t="n">
         <v>46004.79097222222</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9057,13 +9057,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G58" s="26" t="n">
+      <c r="G58" s="27" t="n">
         <v>46004.79583333333</v>
       </c>
-      <c r="H58" s="26" t="n">
+      <c r="H58" s="27" t="n">
         <v>46004.8125</v>
       </c>
-      <c r="I58" s="26" t="n">
+      <c r="I58" s="27" t="n">
         <v>46004.86736111111</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -9083,7 +9083,7 @@
           <t>PT12454</t>
         </is>
       </c>
-      <c r="C59" s="26" t="n">
+      <c r="C59" s="27" t="n">
         <v>46000.40277777778</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9099,13 +9099,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G59" s="26" t="n">
+      <c r="G59" s="27" t="n">
         <v>46000.41805555556</v>
       </c>
-      <c r="H59" s="26" t="n">
+      <c r="H59" s="27" t="n">
         <v>46000.42986111111</v>
       </c>
-      <c r="I59" s="26" t="n">
+      <c r="I59" s="27" t="n">
         <v>46000.70347222222</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -9125,7 +9125,7 @@
           <t>PT12464</t>
         </is>
       </c>
-      <c r="C60" s="26" t="n">
+      <c r="C60" s="27" t="n">
         <v>46012.48888888889</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9141,13 +9141,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G60" s="26" t="n">
+      <c r="G60" s="27" t="n">
         <v>46012.49861111111</v>
       </c>
-      <c r="H60" s="26" t="n">
+      <c r="H60" s="27" t="n">
         <v>46012.55416666667</v>
       </c>
-      <c r="I60" s="26" t="n">
+      <c r="I60" s="27" t="n">
         <v>46012.78888888889</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -9167,7 +9167,7 @@
           <t>PT12485</t>
         </is>
       </c>
-      <c r="C61" s="26" t="n">
+      <c r="C61" s="27" t="n">
         <v>45998.61875</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9183,13 +9183,13 @@
           <t>Head Injury</t>
         </is>
       </c>
-      <c r="G61" s="26" t="n">
+      <c r="G61" s="27" t="n">
         <v>45998.62222222222</v>
       </c>
-      <c r="H61" s="26" t="n">
+      <c r="H61" s="27" t="n">
         <v>45998.66597222222</v>
       </c>
-      <c r="I61" s="26" t="n">
+      <c r="I61" s="27" t="n">
         <v>45998.70138888889</v>
       </c>
       <c r="J61" t="inlineStr">
@@ -9209,7 +9209,7 @@
           <t>PT12485</t>
         </is>
       </c>
-      <c r="C62" s="26" t="n">
+      <c r="C62" s="27" t="n">
         <v>46019.37430555555</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9225,13 +9225,13 @@
           <t>Fall</t>
         </is>
       </c>
-      <c r="G62" s="26" t="n">
+      <c r="G62" s="27" t="n">
         <v>46019.38611111111</v>
       </c>
-      <c r="H62" s="26" t="n">
+      <c r="H62" s="27" t="n">
         <v>46019.43819444445</v>
       </c>
-      <c r="I62" s="26" t="n">
+      <c r="I62" s="27" t="n">
         <v>46019.59027777778</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -9251,7 +9251,7 @@
           <t>PT12544</t>
         </is>
       </c>
-      <c r="C63" s="26" t="n">
+      <c r="C63" s="27" t="n">
         <v>46005.71666666667</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9267,13 +9267,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G63" s="26" t="n">
+      <c r="G63" s="27" t="n">
         <v>46005.72638888889</v>
       </c>
-      <c r="H63" s="26" t="n">
+      <c r="H63" s="27" t="n">
         <v>46005.78541666667</v>
       </c>
-      <c r="I63" s="26" t="n">
+      <c r="I63" s="27" t="n">
         <v>46005.94791666666</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -9293,7 +9293,7 @@
           <t>PT12586</t>
         </is>
       </c>
-      <c r="C64" s="26" t="n">
+      <c r="C64" s="27" t="n">
         <v>46016.61944444444</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9309,13 +9309,13 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G64" s="26" t="n">
+      <c r="G64" s="27" t="n">
         <v>46016.62291666667</v>
       </c>
-      <c r="H64" s="26" t="n">
+      <c r="H64" s="27" t="n">
         <v>46016.73055555556</v>
       </c>
-      <c r="I64" s="26" t="n">
+      <c r="I64" s="27" t="n">
         <v>46017.02083333334</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -9335,7 +9335,7 @@
           <t>PT12635</t>
         </is>
       </c>
-      <c r="C65" s="26" t="n">
+      <c r="C65" s="27" t="n">
         <v>46014.85347222222</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -9351,13 +9351,13 @@
           <t>Rash</t>
         </is>
       </c>
-      <c r="G65" s="26" t="n">
+      <c r="G65" s="27" t="n">
         <v>46014.85833333333</v>
       </c>
-      <c r="H65" s="26" t="n">
+      <c r="H65" s="27" t="n">
         <v>46014.96944444445</v>
       </c>
-      <c r="I65" s="26" t="n">
+      <c r="I65" s="27" t="n">
         <v>46015.05972222222</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -9377,7 +9377,7 @@
           <t>PT12649</t>
         </is>
       </c>
-      <c r="C66" s="26" t="n">
+      <c r="C66" s="27" t="n">
         <v>46012.3875</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -9393,13 +9393,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G66" s="26" t="n">
+      <c r="G66" s="27" t="n">
         <v>46012.39166666667</v>
       </c>
-      <c r="H66" s="26" t="n">
+      <c r="H66" s="27" t="n">
         <v>46012.42916666667</v>
       </c>
-      <c r="I66" s="26" t="n">
+      <c r="I66" s="27" t="n">
         <v>46012.47291666667</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -9419,7 +9419,7 @@
           <t>PT12677</t>
         </is>
       </c>
-      <c r="C67" s="26" t="n">
+      <c r="C67" s="27" t="n">
         <v>45995.16388888889</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -9435,13 +9435,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G67" s="26" t="n">
+      <c r="G67" s="27" t="n">
         <v>45995.16666666666</v>
       </c>
-      <c r="H67" s="26" t="n">
+      <c r="H67" s="27" t="n">
         <v>45995.17430555556</v>
       </c>
-      <c r="I67" s="26" t="n">
+      <c r="I67" s="27" t="n">
         <v>45995.43333333333</v>
       </c>
       <c r="J67" t="inlineStr">
@@ -9461,7 +9461,7 @@
           <t>PT12687</t>
         </is>
       </c>
-      <c r="C68" s="26" t="n">
+      <c r="C68" s="27" t="n">
         <v>46020.64444444444</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -9477,13 +9477,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G68" s="26" t="n">
+      <c r="G68" s="27" t="n">
         <v>46020.64791666667</v>
       </c>
-      <c r="H68" s="26" t="n">
+      <c r="H68" s="27" t="n">
         <v>46020.69652777778</v>
       </c>
-      <c r="I68" s="26" t="n">
+      <c r="I68" s="27" t="n">
         <v>46020.74861111111</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -9503,7 +9503,7 @@
           <t>PT12732</t>
         </is>
       </c>
-      <c r="C69" s="26" t="n">
+      <c r="C69" s="27" t="n">
         <v>46013.72777777778</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -9519,13 +9519,13 @@
           <t>Laceration</t>
         </is>
       </c>
-      <c r="G69" s="26" t="n">
+      <c r="G69" s="27" t="n">
         <v>46013.73333333333</v>
       </c>
-      <c r="H69" s="26" t="n">
+      <c r="H69" s="27" t="n">
         <v>46013.73958333334</v>
       </c>
-      <c r="I69" s="26" t="n">
+      <c r="I69" s="27" t="n">
         <v>46013.9125</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -9545,7 +9545,7 @@
           <t>PT12770</t>
         </is>
       </c>
-      <c r="C70" s="26" t="n">
+      <c r="C70" s="27" t="n">
         <v>45998.23958333334</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -9561,13 +9561,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G70" s="26" t="n">
+      <c r="G70" s="27" t="n">
         <v>45998.24791666667</v>
       </c>
-      <c r="H70" s="26" t="n">
+      <c r="H70" s="27" t="n">
         <v>45998.24861111111</v>
       </c>
-      <c r="I70" s="26" t="n">
+      <c r="I70" s="27" t="n">
         <v>45998.30763888889</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -9587,7 +9587,7 @@
           <t>PT12826</t>
         </is>
       </c>
-      <c r="C71" s="26" t="n">
+      <c r="C71" s="27" t="n">
         <v>45996.64097222222</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -9603,13 +9603,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G71" s="26" t="n">
+      <c r="G71" s="27" t="n">
         <v>45996.64861111111</v>
       </c>
-      <c r="H71" s="26" t="n">
+      <c r="H71" s="27" t="n">
         <v>45996.69236111111</v>
       </c>
-      <c r="I71" s="26" t="n">
+      <c r="I71" s="27" t="n">
         <v>45996.76111111111</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -9629,7 +9629,7 @@
           <t>PT12829</t>
         </is>
       </c>
-      <c r="C72" s="26" t="n">
+      <c r="C72" s="27" t="n">
         <v>46010.43055555555</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -9645,13 +9645,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G72" s="26" t="n">
+      <c r="G72" s="27" t="n">
         <v>46010.43541666667</v>
       </c>
-      <c r="H72" s="26" t="n">
+      <c r="H72" s="27" t="n">
         <v>46010.48402777778</v>
       </c>
-      <c r="I72" s="26" t="n">
+      <c r="I72" s="27" t="n">
         <v>46010.54791666667</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -9671,7 +9671,7 @@
           <t>PT12851</t>
         </is>
       </c>
-      <c r="C73" s="26" t="n">
+      <c r="C73" s="27" t="n">
         <v>46009.11180555556</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -9687,13 +9687,13 @@
           <t>Head Injury</t>
         </is>
       </c>
-      <c r="G73" s="26" t="n">
+      <c r="G73" s="27" t="n">
         <v>46009.12569444445</v>
       </c>
-      <c r="H73" s="26" t="n">
+      <c r="H73" s="27" t="n">
         <v>46009.12638888889</v>
       </c>
-      <c r="I73" s="26" t="n">
+      <c r="I73" s="27" t="n">
         <v>46009.21736111111</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -9713,7 +9713,7 @@
           <t>PT12860</t>
         </is>
       </c>
-      <c r="C74" s="26" t="n">
+      <c r="C74" s="27" t="n">
         <v>46017.00208333333</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -9729,13 +9729,13 @@
           <t>Palpitations</t>
         </is>
       </c>
-      <c r="G74" s="26" t="n">
+      <c r="G74" s="27" t="n">
         <v>46017.01041666666</v>
       </c>
-      <c r="H74" s="26" t="n">
+      <c r="H74" s="27" t="n">
         <v>46017.01111111111</v>
       </c>
-      <c r="I74" s="26" t="n">
+      <c r="I74" s="27" t="n">
         <v>46017.17361111111</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -9755,7 +9755,7 @@
           <t>PT12890</t>
         </is>
       </c>
-      <c r="C75" s="26" t="n">
+      <c r="C75" s="27" t="n">
         <v>45997.28680555556</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -9771,13 +9771,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G75" s="26" t="n">
+      <c r="G75" s="27" t="n">
         <v>45997.29097222222</v>
       </c>
-      <c r="H75" s="26" t="n">
+      <c r="H75" s="27" t="n">
         <v>45997.30277777778</v>
       </c>
-      <c r="I75" s="26" t="n">
+      <c r="I75" s="27" t="n">
         <v>45997.4625</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -9797,7 +9797,7 @@
           <t>PT12893</t>
         </is>
       </c>
-      <c r="C76" s="26" t="n">
+      <c r="C76" s="27" t="n">
         <v>46006.75902777778</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -9813,13 +9813,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G76" s="26" t="n">
+      <c r="G76" s="27" t="n">
         <v>46006.76041666666</v>
       </c>
-      <c r="H76" s="26" t="n">
+      <c r="H76" s="27" t="n">
         <v>46006.84513888889</v>
       </c>
-      <c r="I76" s="26" t="n">
+      <c r="I76" s="27" t="n">
         <v>46006.91111111111</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -9839,7 +9839,7 @@
           <t>PT12945</t>
         </is>
       </c>
-      <c r="C77" s="26" t="n">
+      <c r="C77" s="27" t="n">
         <v>46012.37083333333</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -9855,13 +9855,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G77" s="26" t="n">
+      <c r="G77" s="27" t="n">
         <v>46012.37569444445</v>
       </c>
-      <c r="H77" s="26" t="n">
+      <c r="H77" s="27" t="n">
         <v>46012.39375</v>
       </c>
-      <c r="I77" s="26" t="n">
+      <c r="I77" s="27" t="n">
         <v>46012.60902777778</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -9881,7 +9881,7 @@
           <t>PT12963</t>
         </is>
       </c>
-      <c r="C78" s="26" t="n">
+      <c r="C78" s="27" t="n">
         <v>45999.46319444444</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -9897,13 +9897,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G78" s="26" t="n">
+      <c r="G78" s="27" t="n">
         <v>45999.47013888889</v>
       </c>
-      <c r="H78" s="26" t="n">
+      <c r="H78" s="27" t="n">
         <v>45999.48125</v>
       </c>
-      <c r="I78" s="26" t="n">
+      <c r="I78" s="27" t="n">
         <v>45999.58125</v>
       </c>
       <c r="J78" t="inlineStr">
@@ -9923,7 +9923,7 @@
           <t>PT12983</t>
         </is>
       </c>
-      <c r="C79" s="26" t="n">
+      <c r="C79" s="27" t="n">
         <v>46007.86041666667</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -9939,13 +9939,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G79" s="26" t="n">
+      <c r="G79" s="27" t="n">
         <v>46007.86319444444</v>
       </c>
-      <c r="H79" s="26" t="n">
+      <c r="H79" s="27" t="n">
         <v>46007.88263888889</v>
       </c>
-      <c r="I79" s="26" t="n">
+      <c r="I79" s="27" t="n">
         <v>46007.94166666667</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -9965,7 +9965,7 @@
           <t>PT12989</t>
         </is>
       </c>
-      <c r="C80" s="26" t="n">
+      <c r="C80" s="27" t="n">
         <v>45992.5125</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -9981,13 +9981,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G80" s="26" t="n">
+      <c r="G80" s="27" t="n">
         <v>45992.51319444444</v>
       </c>
-      <c r="H80" s="26" t="n">
+      <c r="H80" s="27" t="n">
         <v>45992.51388888889</v>
       </c>
-      <c r="I80" s="26" t="n">
+      <c r="I80" s="27" t="n">
         <v>45992.82152777778</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -10007,7 +10007,7 @@
           <t>PT13031</t>
         </is>
       </c>
-      <c r="C81" s="26" t="n">
+      <c r="C81" s="27" t="n">
         <v>46018.11597222222</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -10023,13 +10023,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G81" s="26" t="n">
+      <c r="G81" s="27" t="n">
         <v>46018.11875</v>
       </c>
-      <c r="H81" s="26" t="n">
+      <c r="H81" s="27" t="n">
         <v>46018.12986111111</v>
       </c>
-      <c r="I81" s="26" t="n">
+      <c r="I81" s="27" t="n">
         <v>46018.29513888889</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -10049,7 +10049,7 @@
           <t>PT13107</t>
         </is>
       </c>
-      <c r="C82" s="26" t="n">
+      <c r="C82" s="27" t="n">
         <v>46020.52083333334</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -10065,13 +10065,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G82" s="26" t="n">
+      <c r="G82" s="27" t="n">
         <v>46020.52430555555</v>
       </c>
-      <c r="H82" s="26" t="n">
+      <c r="H82" s="27" t="n">
         <v>46020.64236111111</v>
       </c>
-      <c r="I82" s="26" t="n">
+      <c r="I82" s="27" t="n">
         <v>46020.78888888889</v>
       </c>
       <c r="J82" t="inlineStr">
@@ -10091,7 +10091,7 @@
           <t>PT13158</t>
         </is>
       </c>
-      <c r="C83" s="26" t="n">
+      <c r="C83" s="27" t="n">
         <v>46006.4375</v>
       </c>
       <c r="D83" t="inlineStr">
@@ -10107,13 +10107,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G83" s="26" t="n">
+      <c r="G83" s="27" t="n">
         <v>46006.43888888889</v>
       </c>
-      <c r="H83" s="26" t="n">
+      <c r="H83" s="27" t="n">
         <v>46006.45902777778</v>
       </c>
-      <c r="I83" s="26" t="n">
+      <c r="I83" s="27" t="n">
         <v>46006.53888888889</v>
       </c>
       <c r="J83" t="inlineStr">
@@ -10133,7 +10133,7 @@
           <t>PT13305</t>
         </is>
       </c>
-      <c r="C84" s="26" t="n">
+      <c r="C84" s="27" t="n">
         <v>45998.60486111111</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -10149,13 +10149,13 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G84" s="26" t="n">
+      <c r="G84" s="27" t="n">
         <v>45998.61041666667</v>
       </c>
-      <c r="H84" s="26" t="n">
+      <c r="H84" s="27" t="n">
         <v>45998.61666666667</v>
       </c>
-      <c r="I84" s="26" t="n">
+      <c r="I84" s="27" t="n">
         <v>45998.77291666667</v>
       </c>
       <c r="J84" t="inlineStr">
@@ -10175,7 +10175,7 @@
           <t>PT13330</t>
         </is>
       </c>
-      <c r="C85" s="26" t="n">
+      <c r="C85" s="27" t="n">
         <v>46003.71527777778</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -10191,13 +10191,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G85" s="26" t="n">
+      <c r="G85" s="27" t="n">
         <v>46003.71805555555</v>
       </c>
-      <c r="H85" s="26" t="n">
+      <c r="H85" s="27" t="n">
         <v>46003.75555555556</v>
       </c>
-      <c r="I85" s="26" t="n">
+      <c r="I85" s="27" t="n">
         <v>46003.78888888889</v>
       </c>
       <c r="J85" t="inlineStr">
@@ -10217,7 +10217,7 @@
           <t>PT13353</t>
         </is>
       </c>
-      <c r="C86" s="26" t="n">
+      <c r="C86" s="27" t="n">
         <v>46022.65</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -10233,13 +10233,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G86" s="26" t="n">
+      <c r="G86" s="27" t="n">
         <v>46022.65694444445</v>
       </c>
-      <c r="H86" s="26" t="n">
+      <c r="H86" s="27" t="n">
         <v>46022.68958333333</v>
       </c>
-      <c r="I86" s="26" t="n">
+      <c r="I86" s="27" t="n">
         <v>46022.82916666667</v>
       </c>
       <c r="J86" t="inlineStr">
@@ -10259,7 +10259,7 @@
           <t>PT13473</t>
         </is>
       </c>
-      <c r="C87" s="26" t="n">
+      <c r="C87" s="27" t="n">
         <v>46010.82361111111</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -10275,13 +10275,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G87" s="26" t="n">
+      <c r="G87" s="27" t="n">
         <v>46010.83194444444</v>
       </c>
-      <c r="H87" s="26" t="n">
+      <c r="H87" s="27" t="n">
         <v>46010.94722222222</v>
       </c>
-      <c r="I87" s="26" t="n">
+      <c r="I87" s="27" t="n">
         <v>46011.04861111111</v>
       </c>
       <c r="J87" t="inlineStr">
@@ -10301,7 +10301,7 @@
           <t>PT13601</t>
         </is>
       </c>
-      <c r="C88" s="26" t="n">
+      <c r="C88" s="27" t="n">
         <v>45992.75555555556</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -10317,13 +10317,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G88" s="26" t="n">
+      <c r="G88" s="27" t="n">
         <v>45992.75972222222</v>
       </c>
-      <c r="H88" s="26" t="n">
+      <c r="H88" s="27" t="n">
         <v>45992.76944444444</v>
       </c>
-      <c r="I88" s="26" t="n">
+      <c r="I88" s="27" t="n">
         <v>45992.84305555555</v>
       </c>
       <c r="J88" t="inlineStr">
@@ -10343,7 +10343,7 @@
           <t>PT13632</t>
         </is>
       </c>
-      <c r="C89" s="26" t="n">
+      <c r="C89" s="27" t="n">
         <v>45994.4</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -10359,13 +10359,13 @@
           <t>Dizziness</t>
         </is>
       </c>
-      <c r="G89" s="26" t="n">
+      <c r="G89" s="27" t="n">
         <v>45994.40555555555</v>
       </c>
-      <c r="H89" s="26" t="n">
+      <c r="H89" s="27" t="n">
         <v>45994.43680555555</v>
       </c>
-      <c r="I89" s="26" t="n">
+      <c r="I89" s="27" t="n">
         <v>45994.70416666667</v>
       </c>
       <c r="J89" t="inlineStr">
@@ -10385,7 +10385,7 @@
           <t>PT13672</t>
         </is>
       </c>
-      <c r="C90" s="26" t="n">
+      <c r="C90" s="27" t="n">
         <v>45994.45208333333</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -10401,13 +10401,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G90" s="26" t="n">
+      <c r="G90" s="27" t="n">
         <v>45994.45833333334</v>
       </c>
-      <c r="H90" s="26" t="n">
+      <c r="H90" s="27" t="n">
         <v>45994.48472222222</v>
       </c>
-      <c r="I90" s="26" t="n">
+      <c r="I90" s="27" t="n">
         <v>45994.70277777778</v>
       </c>
       <c r="J90" t="inlineStr">
@@ -10427,7 +10427,7 @@
           <t>PT13682</t>
         </is>
       </c>
-      <c r="C91" s="26" t="n">
+      <c r="C91" s="27" t="n">
         <v>46005.61458333334</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -10443,13 +10443,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G91" s="26" t="n">
+      <c r="G91" s="27" t="n">
         <v>46005.61666666667</v>
       </c>
-      <c r="H91" s="26" t="n">
+      <c r="H91" s="27" t="n">
         <v>46005.64861111111</v>
       </c>
-      <c r="I91" s="26" t="n">
+      <c r="I91" s="27" t="n">
         <v>46005.72986111111</v>
       </c>
       <c r="J91" t="inlineStr">
@@ -10469,7 +10469,7 @@
           <t>PT13806</t>
         </is>
       </c>
-      <c r="C92" s="26" t="n">
+      <c r="C92" s="27" t="n">
         <v>46002.34930555556</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -10485,13 +10485,13 @@
           <t>Head Injury</t>
         </is>
       </c>
-      <c r="G92" s="26" t="n">
+      <c r="G92" s="27" t="n">
         <v>46002.35347222222</v>
       </c>
-      <c r="H92" s="26" t="n">
+      <c r="H92" s="27" t="n">
         <v>46002.35416666666</v>
       </c>
-      <c r="I92" s="26" t="n">
+      <c r="I92" s="27" t="n">
         <v>46002.52152777778</v>
       </c>
       <c r="J92" t="inlineStr">
@@ -10511,7 +10511,7 @@
           <t>PT13869</t>
         </is>
       </c>
-      <c r="C93" s="26" t="n">
+      <c r="C93" s="27" t="n">
         <v>46001.64791666667</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -10527,13 +10527,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G93" s="26" t="n">
+      <c r="G93" s="27" t="n">
         <v>46001.65138888889</v>
       </c>
-      <c r="H93" s="26" t="n">
+      <c r="H93" s="27" t="n">
         <v>46001.73680555556</v>
       </c>
-      <c r="I93" s="26" t="n">
+      <c r="I93" s="27" t="n">
         <v>46001.78333333333</v>
       </c>
       <c r="J93" t="inlineStr">
@@ -10553,7 +10553,7 @@
           <t>PT13940</t>
         </is>
       </c>
-      <c r="C94" s="26" t="n">
+      <c r="C94" s="27" t="n">
         <v>46010.40694444445</v>
       </c>
       <c r="D94" t="inlineStr">
@@ -10569,13 +10569,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G94" s="26" t="n">
+      <c r="G94" s="27" t="n">
         <v>46010.41180555556</v>
       </c>
-      <c r="H94" s="26" t="n">
+      <c r="H94" s="27" t="n">
         <v>46010.49236111111</v>
       </c>
-      <c r="I94" s="26" t="n">
+      <c r="I94" s="27" t="n">
         <v>46010.52569444444</v>
       </c>
       <c r="J94" t="inlineStr">
@@ -10613,7 +10613,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="289" customHeight="1">
+    <row r="2" ht="259" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Cedar Ridge's ED medical director reviews every high-acuity visit (ESI 1 or 2) each month. The tracking system exports the month's visits sorted by PatientID, and someone spends 20 minutes turning that export into a list. Automate it. The macro must:
@@ -10707,7 +10707,7 @@
           <t>It should be the earliest ESI 1 arrival in December</t>
         </is>
       </c>
-      <c r="D7" cm="1" s="27">
+      <c r="D7" cm="1" s="28">
         <f t="array" ref="D7">IFERROR(INDIRECT("'HighAcuity'!A2")&amp;"","")</f>
         <v/>
       </c>
@@ -10732,7 +10732,7 @@
           <t>This cell depends on both sort levels</t>
         </is>
       </c>
-      <c r="D8" cm="1" s="27">
+      <c r="D8" cm="1" s="28">
         <f t="array" ref="D8">IFERROR(INDIRECT("'HighAcuity'!A5")&amp;"","")</f>
         <v/>
       </c>
@@ -10757,7 +10757,7 @@
           <t>Rows below row 21 are only sorted if the sort range adapts</t>
         </is>
       </c>
-      <c r="D9" cm="1" s="27">
+      <c r="D9" cm="1" s="28">
         <f t="array" ref="D9">IFERROR(IF(ISREF(INDIRECT("'HighAcuity'!A1")),INDEX(INDIRECT("'HighAcuity'!A:A"),MAX(1,COUNTA(INDIRECT("'HighAcuity'!A:A"))))&amp;"",""),"")</f>
         <v/>
       </c>
@@ -10824,51 +10824,51 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>🔑 Answer Key — Lesson 5.1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -10885,14 +10885,14 @@
           <t>This workbook is an .xlsx file, which can't store macros. Which file extension does the Excel Macro-Enabled Workbook format use, the format you save it in before you record? Type the extension, like .xlsx</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>.xlsm</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>**.xlsm**: File → Save As (F12; Mac: ⌘ + Shift + S) → *Save as type:* **Excel Macro-Enabled Workbook (*.xlsm)**.</t>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>.xlsm: File → Save As (F12; Mac: ⌘ + Shift + S) → Save as type: Excel Macro-Enabled Workbook (*.xlsm).</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>An .xlsx file can't contain VBA code. If you save a workbook that has macros as .xlsx, Excel warns you that the *VB project* can't be saved, and if you click Yes it throws the code away. .xlsb, .xltm, .xlam and the old .xls can hold macros too, but .xlsm is the everyday format for a workbook with macros. Save as .xlsm now, before you record, so nothing gets lost.</t>
+          <t>An .xlsx file can't contain VBA code. If you save a workbook that has macros as .xlsx, Excel warns you that the VB project can't be saved, and if you click Yes it throws the code away. .xlsb, .xltm, .xlam and the old .xls can hold macros too, but .xlsm is the everyday format for a workbook with macros. Save as .xlsm now, before you record, so nothing gets lost.</t>
         </is>
       </c>
     </row>
@@ -10921,14 +10921,14 @@
 D: Rename the file to .xlsx.</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
-        <is>
-          <t>**B.** Confirm the sender, save the file, then File Explorer → right-click → **Properties** → **General** → tick **Unblock** → **OK**. Reopen it and click **Enable Content** on the yellow bar.</t>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>B. Confirm the sender, save the file, then File Explorer → right-click → Properties → General → tick Unblock → OK. Reopen it and click Enable Content on the yellow bar.</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -10953,14 +10953,14 @@
           <t>Which function key do you press with Alt (Mac: Option) to open the Visual Basic Editor? Type just the key, like F5.</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>F11</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>**F11**: Alt + F11 on Windows, Option + F11 on a Mac (add Fn if your top-row keys control brightness and volume).</t>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>F11: Alt + F11 on Windows, Option + F11 on a Mac (add Fn if your top-row keys control brightness and volume).</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -10985,14 +10985,14 @@
           <t>On Windows, what is the file name (with extension) of the Personal Macro Workbook, the hidden workbook that makes a macro available in every workbook you open?</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>PERSONAL.XLSB</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>**PERSONAL.XLSB**, stored in `%APPDATA%\Microsoft\Excel\XLSTART`.</t>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>PERSONAL.XLSB, stored in %APPDATA%\Microsoft\Excel\XLSTART.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Choosing *Store macro in: Personal Macro Workbook* creates PERSONAL.XLSB the first time. Excel opens every file in XLSTART automatically and hides this one, so its macros are always available on your computer (but not on anyone else's).</t>
+          <t>Choosing Store macro in: Personal Macro Workbook creates PERSONAL.XLSB the first time. Excel opens every file in XLSTART automatically and hides this one, so its macros are always available on your computer (but not on anyone else's).</t>
         </is>
       </c>
     </row>
@@ -11017,14 +11017,14 @@
           <t>With Use Relative References OFF, you click Record Macro, click cell B3, type Verified, press Enter, and stop recording. Later you select H10 and run the macro. Which cell receives Verified? Type the address, like A1.</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>The recorder wrote `Range("B3").Select`, so the macro always goes to **B3**.</t>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>The recorder wrote Range("B3").Select, so the macro always goes to B3.</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -11049,14 +11049,14 @@
           <t>This time A1 is selected when you click Record Macro. You turn ON Use Relative References, click B3, type Verified, press Enter, and stop. Later you select H10 and run the macro. Which cell receives Verified?</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>I12</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>The recorder wrote `ActiveCell.Offset(2, 1).Range("A1").Select`: 2 rows down and 1 column right of the active cell. From H10 that is **I12**.</t>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>The recorder wrote ActiveCell.Offset(2, 1).Range("A1").Select: 2 rows down and 1 column right of the active cell. From H10 that is I12.</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -11081,10 +11081,10 @@
           <t>Record the FormatCensusReport macro on the Census_Nov sheet by following the recipe in Guide section 7 (TOTAL row recorded with relative references, shortcut Ctrl + Shift + R). The gray cell finds the row your macro labeled TOTAL and reads its MidnightCensus cell, which should equal November's patient days.</t>
         </is>
       </c>
-      <c r="C11" s="31" t="n">
+      <c r="C11" s="32" t="n">
         <v>809</v>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Sub FormatCensusReport()
 '
@@ -11134,7 +11134,7 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E11" cm="1" s="33">
+      <c r="E11" cm="1" s="19">
         <f t="array" ref="E11">SUM(Census_Nov!G2:G31)</f>
         <v/>
       </c>
@@ -11158,9 +11158,9 @@
       <c r="C12" s="34" t="n">
         <v>0.8988888888888888</v>
       </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>In H32 type `=G32/D32`, then Percent Style and Increase Decimal once. The recorder stores it as `"=RC[-1]/RC[-4]"`: same row, 1 and 4 columns to the left.</t>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>In H32 type =G32/D32, then Percent Style and Increase Decimal once. The recorder stores it as "=RC[-1]/RC[-4]": same row, 1 and 4 columns to the left.</t>
         </is>
       </c>
       <c r="E12" cm="1" s="35">
@@ -11184,14 +11184,14 @@
           <t>In the Record Macro dialog you typed an uppercase R in the Shortcut key box. Which key combination runs the macro on Windows? Type it like Ctrl+Alt+X.</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>Ctrl+Shift+R</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>**Ctrl + Shift + R** (Mac: Option + ⌘ + Shift + R).</t>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + R (Mac: Option + ⌘ + Shift + R).</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -11205,7 +11205,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="396" customHeight="1">
+    <row r="14" ht="366" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -11216,19 +11216,19 @@
           <t>Add two more ways to run FormatCensusReport: (a) a button on the Census_Dec sheet labeled Build report, and (b) a button on the Quick Access Toolbar. Don't click them yet.</t>
         </is>
       </c>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>**Sheet button**
-1. On Census_Dec, choose **Insert → Shapes → Rectangle: Rounded Corners** and draw it to the right of the data (for example over columns J:K).
-2. Type **Build report** while the shape is selected.
-3. Right-click the shape's border → **Assign Macro…** → pick **FormatCensusReport** → **OK**.
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>Sheet button
+1. On Census_Dec, choose Insert → Shapes → Rectangle: Rounded Corners and draw it to the right of the data (for example over columns J:K).
+2. Type Build report while the shape is selected.
+3. Right-click the shape's border → Assign Macro… → pick FormatCensusReport → OK.
 4. Click a cell to deselect. The pointer becomes a hand over the shape, and one click runs the macro.
-**Quick Access Toolbar** (Windows)
-1. **File → Options → Quick Access Toolbar**.
-2. *Choose commands from:* **Macros** → select **FormatCensusReport** → **Add &gt;&gt;**.
-3. Click **Modify…**, pick an icon, set the display name to *Build census report* → **OK** → **OK**.
-If you can't see the toolbar, right-click the ribbon → **Show Quick Access Toolbar**.</t>
+Quick Access Toolbar (Windows)
+1. File → Options → Quick Access Toolbar.
+2. Choose commands from: Macros → select FormatCensusReport → Add &gt;&gt;.
+3. Click Modify…, pick an icon, set the display name to Build census report → OK → OK.
+If you can't see the toolbar, right-click the ribbon → Show Quick Access Toolbar.</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -11253,15 +11253,15 @@
           <t>Go to Census_Dec and run your macro (Ctrl + Shift + R or your button). December has 31 days. The gray cell finds your TOTAL row and counts the daily rows above it. It should show all 31 days.</t>
         </is>
       </c>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="32" t="n">
         <v>31</v>
       </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Click the **Census_Dec** tab and press **Ctrl + Shift + R**. `Selection.End(xlDown)` finds the last date (row 32) and `ActiveCell.Offset(1, 0)` steps to row 33.</t>
-        </is>
-      </c>
-      <c r="E15" cm="1" s="33">
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Click the Census_Dec tab and press Ctrl + Shift + R. Selection.End(xlDown) finds the last date (row 32) and ActiveCell.Offset(1, 0) steps to row 33.</t>
+        </is>
+      </c>
+      <c r="E15" cm="1" s="19">
         <f t="array" ref="E15">COUNT(Census_Dec!A2:A32)</f>
         <v/>
       </c>
@@ -11282,15 +11282,15 @@
           <t>On Census_Dec, the gray cell reads the MidnightCensus total in your TOTAL row. It should equal December's patient days (all 31 days).</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="32" t="n">
         <v>863</v>
       </c>
-      <c r="D16" s="32" t="inlineStr">
-        <is>
-          <t>The recorded formula `=SUM(R2C:R[-1]C)` becomes `=SUM(G$2:G32)` in row 33.</t>
-        </is>
-      </c>
-      <c r="E16" cm="1" s="33">
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>The recorded formula =SUM(R2C:R[-1]C) becomes =SUM(G$2:G32) in row 33.</t>
+        </is>
+      </c>
+      <c r="E16" cm="1" s="19">
         <f t="array" ref="E16">SUM(Census_Dec!G2:G32)</f>
         <v/>
       </c>
@@ -11311,14 +11311,14 @@
           <t>Read this recorded line: ActiveCell.FormulaR1C1 = "=SUM(R[-31]C[-1]:R[-1]C[-1])". If it runs while H33 is the active cell, which range does the SUM add up? Type it like A1:A9.</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>G2:G32</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
-        <is>
-          <t>**G2:G32**: R[-31] is 31 rows above row 33 (row 2), R[-1] is the row above (row 32), and C[-1] is one column left of H, which is G.</t>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>G2:G32: R[-31] is 31 rows above row 33 (row 2), R[-1] is the row above (row 32), and C[-1] is one column left of H, which is G.</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>It's the R1C1 form of =SUM(G2:G32) typed in H33. Square brackets mean *relative to the formula's own cell*. A number without brackets is a fixed row or column, so R2C means row 2 of this column. Every part of this formula is relative, so in H34 it would add G3:G33. Reading R1C1 like this tells you whether a recorded formula will still be right when the data has a different number of rows.</t>
+          <t>It's the R1C1 form of =SUM(G2:G32) typed in H33. Square brackets mean relative to the formula's own cell. A number without brackets is a fixed row or column, so R2C means row 2 of this column. Every part of this formula is relative, so in H34 it would add G3:G33. Reading R1C1 like this tells you whether a recorded formula will still be right when the data has a different number of rows.</t>
         </is>
       </c>
     </row>
@@ -11355,51 +11355,51 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>🔑 Bonus Key — Lesson 5.1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>Sample solution</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>Live result</t>
         </is>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -11416,10 +11416,10 @@
           <t>How many visits (data rows, not counting the header) are on the HighAcuity sheet built from ED_Dec?</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Sub ExtractHighAcuity()
 '
@@ -11466,7 +11466,7 @@
 End Sub</t>
         </is>
       </c>
-      <c r="E5" cm="1" s="33">
+      <c r="E5" cm="1" s="19">
         <f t="array" ref="E5">COUNTIF(ED_Dec!E2:E94,"&lt;=2")</f>
         <v/>
       </c>
@@ -11492,17 +11492,17 @@
           <t>Which EDVisitID is in the first data row (A2) of HighAcuity?</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>ED211706</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
-        <is>
-          <t>**ED211706**, the earliest-arriving ESI 1 visit (12/01/2025 12:18).</t>
-        </is>
-      </c>
-      <c r="E6" cm="1" s="33">
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>ED211706, the earliest-arriving ESI 1 visit (12/01/2025 12:18).</t>
+        </is>
+      </c>
+      <c r="E6" cm="1" s="19">
         <f t="array" ref="E6">INDEX(ED_Dec!A2:A94,MATCH(_xlfn.MINIFS(ED_Dec!C2:C94,ED_Dec!E2:E94,1),ED_Dec!C2:C94,0))</f>
         <v/>
       </c>
@@ -11523,17 +11523,17 @@
           <t>Which EDVisitID is in cell A5 of HighAcuity?</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>ED211715</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>**ED211715**, the earliest-arriving ESI 2 visit (12/01/2025 20:18).</t>
-        </is>
-      </c>
-      <c r="E7" cm="1" s="33">
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>ED211715, the earliest-arriving ESI 2 visit (12/01/2025 20:18).</t>
+        </is>
+      </c>
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">INDEX(ED_Dec!A2:A94,MATCH(_xlfn.MINIFS(ED_Dec!C2:C94,ED_Dec!E2:E94,2),ED_Dec!C2:C94,0))</f>
         <v/>
       </c>
@@ -11554,17 +11554,17 @@
           <t>Which EDVisitID is in the last data row of HighAcuity?</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>ED212209</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>**ED212209**, the latest-arriving ESI 2 visit (12/26/2025 00:03).</t>
-        </is>
-      </c>
-      <c r="E8" cm="1" s="33">
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>ED212209, the latest-arriving ESI 2 visit (12/26/2025 00:03).</t>
+        </is>
+      </c>
+      <c r="E8" cm="1" s="19">
         <f t="array" ref="E8">INDEX(ED_Dec!A2:A94,MATCH(_xlfn.MAXIFS(ED_Dec!C2:C94,ED_Dec!E2:E94,2),ED_Dec!C2:C94,0))</f>
         <v/>
       </c>
@@ -11585,15 +11585,15 @@
           <t>After your macro finishes, how many rows of ED_Dec are visible? The gray cell counts them with SUBTOTAL(103, …), which skips rows a filter hides. It should be every December visit. It stays blank until HighAcuity holds December visits.</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="32" t="n">
         <v>93</v>
       </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>End the macro with `Sheets("ED_Dec").Select`, `Range("A1").Select`, `Selection.AutoFilter`. That toggles the filter off, so all 93 visits show again.</t>
-        </is>
-      </c>
-      <c r="E9" cm="1" s="33">
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>End the macro with Sheets("ED_Dec").Select, Range("A1").Select, Selection.AutoFilter. That toggles the filter off, so all 93 visits show again.</t>
+        </is>
+      </c>
+      <c r="E9" cm="1" s="19">
         <f t="array" ref="E9">COUNTA(ED_Dec!A2:A94)</f>
         <v/>
       </c>

--- a/05-automation-vba/01-recording-macros/5.1-recording-macros.xlsx
+++ b/05-automation-vba/01-recording-macros/5.1-recording-macros.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C34"/>
+  <dimension ref="B1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -707,7 +707,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Expert  ·  about 45 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Expert  ·  about 110 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -942,70 +942,94 @@
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Census_Nov</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 30 rows</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Census_Dec</t>
+          <t>Census_Nov</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows</t>
+          <t>Data: 30 rows</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>ED_Nov</t>
+          <t>Census_Dec</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 80 rows</t>
+          <t>Data: 31 rows</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
+          <t>ED_Nov</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Data: 80 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>ED_Dec</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Data: 93 rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Raw daily census exports for the Medical-Surgical unit at Cedar Ridge Medical Center (November and December 2025), plus the hospital's raw Emergency Department visit exports for the same two months (bonus).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Raw daily census exports for the Medical-Surgical unit at Cedar Ridge Medical Center (November and December 2025), plus the hospital's raw Emergency Department visit exports for the same two months (bonus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/05-automation-vba/01-recording-macros/5.1-recording-macros.xlsx
+++ b/05-automation-vba/01-recording-macros/5.1-recording-macros.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Practice" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Census_Nov" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Census_Dec" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ED_Nov" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ED_Dec" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Bonus" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bonus" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ED_Nov" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ED_Dec" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Answer Key" sheetId="8" state="hidden" r:id="rId8"/>
     <sheet name="Bonus Key" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
@@ -270,10 +270,10 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Ctrl + Z can't undo a macro. Save before you run a macro you just recorded, so you can close without saving if it goes wrong.</t>
+          <t>Ctrl + Z (Mac: ⌘ + Z) can't undo a macro. Save before you run a macro you just recorded, so you can close without saving if it goes wrong.</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 30 rows</t>
+          <t>Data: 30 rows. November's raw census export. Record FormatCensusReport here (tasks 7–8).</t>
         </is>
       </c>
     </row>
@@ -971,43 +971,43 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Data: 31 rows</t>
+          <t>Data: 31 rows. December's raw census export. Add the button and run your macro here (tasks 10–12).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ED_Nov</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Data: 80 rows</t>
+          <t>The bonus challenge (5 parts).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ED_Dec</t>
+          <t>ED_Nov</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Data: 93 rows</t>
+          <t>Data: 80 rows. November's raw ED export (bonus only). Record ExtractHighAcuity here.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>ED_Dec</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>The bonus challenge (5 parts).</t>
+          <t>Data: 93 rows. December's raw ED export (bonus only). Your edited macro builds HighAcuity from it.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>It's also on the Developer tab: Visual Basic</t>
+          <t>It's also on the ribbon: Developer → Visual Basic</t>
         </is>
       </c>
       <c r="D8" s="21" t="n"/>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="66" customHeight="1">
+    <row r="12" ht="81" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>7</t>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Record the FormatCensusReport macro on the Census_Nov sheet by following the recipe in Guide section 7 (TOTAL row recorded with relative references, shortcut Ctrl + Shift + R). The gray cell finds the row your macro labeled TOTAL and reads its MidnightCensus cell, which should equal November's patient days.</t>
+          <t>Record the FormatCensusReport macro on the Census_Nov sheet by following the recipe in Guide section 7 (TOTAL row recorded with relative references, shortcut Ctrl + Shift + R, Mac: Option + ⌘ + Shift + R). The gray cell finds the row your macro labeled TOTAL and reads its MidnightCensus cell, which should equal November's patient days.</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>In the Record Macro dialog you typed an uppercase R in the Shortcut key box. Which key combination runs the macro on Windows? Type it like Ctrl+Alt+X.</t>
+          <t>In the Record Macro dialog you typed an uppercase R in the Shortcut key box. Which key combination runs the macro on Windows? Type it like Ctrl + Alt + X.</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22">
-        <f>IF(IFERROR(D14="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D14&amp;""))=LOWER(TRIM('Answer Key'!$C$13&amp;"")),LOWER(TRIM(D14&amp;""))="ctrl + shift + r",LOWER(TRIM(D14&amp;""))="shift+ctrl+r",LOWER(TRIM(D14&amp;""))="shift + ctrl + r",LOWER(TRIM(D14&amp;""))="control+shift+r",LOWER(TRIM(D14&amp;""))="ctrl shift r",LOWER(TRIM(D14&amp;""))="ctrl-shift-r"),FALSE),"✔ Correct","✘ Not yet"))</f>
+        <f>IF(IFERROR(D14="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D14&amp;""))=LOWER(TRIM('Answer Key'!$C$13&amp;"")),LOWER(TRIM(D14&amp;""))="ctrl+shift+r",LOWER(TRIM(D14&amp;""))="shift+ctrl+r",LOWER(TRIM(D14&amp;""))="shift + ctrl + r",LOWER(TRIM(D14&amp;""))="control+shift+r",LOWER(TRIM(D14&amp;""))="control + shift + r",LOWER(TRIM(D14&amp;""))="ctrl shift r",LOWER(TRIM(D14&amp;""))="ctrl-shift-r"),FALSE),"✔ Correct","✘ Not yet"))</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Right-click a shape → Assign Macro</t>
+          <t>Right-click a shape → Assign Macro…</t>
         </is>
       </c>
       <c r="D15" s="25" t="n"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Go to Census_Dec and run your macro (Ctrl + Shift + R or your button). December has 31 days. The gray cell finds your TOTAL row and counts the daily rows above it. It should show all 31 days.</t>
+          <t>Go to Census_Dec and run your macro (Ctrl + Shift + R, Mac: Option + ⌘ + Shift + R, or your button). December has 31 days. The gray cell finds your TOTAL row and counts the daily rows above it. It should show all 31 days.</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -3206,6 +3206,227 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF9000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Lesson 5.1 · Bonus: The high-acuity ED list</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="259" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Cedar Ridge's ED medical director reviews every high-acuity visit (ESI 1 or 2) each month. The tracking system exports the month's visits sorted by PatientID, and someone spends 20 minutes turning that export into a list. Automate it. The macro must:
+1. Filter the export's ESILevel column to values less than or equal to 2.
+2. Copy the visible rows, with the header, to a new sheet named HighAcuity.
+3. Sort that sheet by ESILevel (smallest first), then ArrivalDateTime (oldest first), and AutoFit the columns.
+4. Go back to the export and turn its filter off.
+Recording tips: Check that Use Relative References is off. Click A1 and turn the filter on with Data → Filter, then use the ESILevel filter arrow → Number Filters → Less Than Or Equal To → 2 → OK. Select the data with Ctrl + Shift + → and then Ctrl + Shift + ↓ (Mac: ⌘ + Shift + arrows), and copy it with Ctrl + C (Mac: ⌘ + C). Add a sheet with the + (New sheet) button next to the sheet tabs, paste with Ctrl + V (Mac: ⌘ + V), and rename the sheet by double-clicking its tab. In Data → Sort (Lesson 1.6), sort by ESILevel (Smallest to Largest), then click Add Level and pick ArrivalDateTime (Oldest to Newest). AutoFit every column: click the Select All button (the triangle where the row and column headings meet), then double-click any column boundary. Finish by clicking the ED_Nov tab, then A1, then Data → Filter again.
+Record it on ED_Nov (80 visits) as ExtractHighAcuity (shortcut Ctrl + Shift + H, Mac: Option + ⌘ + Shift + H). Then delete the HighAcuity sheet it made (right-click its tab → Delete), open the VBE with Alt + F11 (Mac: Option + F11, or Developer → Visual Basic), and edit the code so it works on ED_Dec (93 visits). Guide section 9 lists the edits recorded code usually needs and what to do if the macro stops with a run-time error. Run it on ED_Dec. The gray cells read the HighAcuity sheet your macro builds from December, so they stay blank until it exists. While the sheet from your November recording is still there, they show ✘ Not yet or stay blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>There's nothing to type on this sheet. The gray cells read the HighAcuity sheet your macro builds from ED_Dec, and the Check column turns green when they match. Stuck? Read the hint, then Guide section 9. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16">
+        <f>"Score: "&amp;COUNTIF(E6:E10,"✔*")&amp;" of 5 auto-checked tasks correct"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Hint</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Your Answer</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>How many visits (data rows, not counting the header) are on the HighAcuity sheet built from ED_Dec?</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>COUNTIF on ED_Dec's ESILevel column gives you a target to compare with</t>
+        </is>
+      </c>
+      <c r="D6" cm="1" s="23">
+        <f t="array" ref="D6">IF(ISREF(INDIRECT("'HighAcuity'!A1")),COUNTA(INDIRECT("'HighAcuity'!A:A"))-1,"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="22">
+        <f>IF(IFERROR(D6="",FALSE),"",IF(IFERROR(AND(ISNUMBER(D6),OR(ABS(D6-'Bonus Key'!$C$5)&lt;=0.0001)),FALSE),"✔ Correct","✘ Not yet"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Which EDVisitID is in the first data row (A2) of HighAcuity?</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>It should be the earliest ESI 1 arrival in December</t>
+        </is>
+      </c>
+      <c r="D7" cm="1" s="27">
+        <f t="array" ref="D7">IFERROR(INDIRECT("'HighAcuity'!A2")&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>IF(IFERROR(D7="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D7&amp;""))=LOWER(TRIM('Bonus Key'!$C$6&amp;""))),FALSE),"✔ Correct","✘ Not yet"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Which EDVisitID is in cell A5 of HighAcuity?</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>This cell depends on both sort levels</t>
+        </is>
+      </c>
+      <c r="D8" cm="1" s="27">
+        <f t="array" ref="D8">IFERROR(INDIRECT("'HighAcuity'!A5")&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E8" s="22">
+        <f>IF(IFERROR(D8="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D8&amp;""))=LOWER(TRIM('Bonus Key'!$C$7&amp;""))),FALSE),"✔ Correct","✘ Not yet"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Which EDVisitID is in the last data row of HighAcuity?</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Rows below row 21 are only sorted if the sort range adapts</t>
+        </is>
+      </c>
+      <c r="D9" cm="1" s="27">
+        <f t="array" ref="D9">IFERROR(IF(ISREF(INDIRECT("'HighAcuity'!A1")),INDEX(INDIRECT("'HighAcuity'!A:A"),MAX(1,COUNTA(INDIRECT("'HighAcuity'!A:A"))))&amp;"",""),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>IF(IFERROR(D9="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D9&amp;""))=LOWER(TRIM('Bonus Key'!$C$8&amp;""))),FALSE),"✔ Correct","✘ Not yet"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>After your macro finishes, how many rows of ED_Dec are visible? The gray cell counts them with SUBTOTAL(103, …), which skips rows a filter hides. It should be every December visit. It stays blank until HighAcuity holds December visits.</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Which sheet does the end of your recorded code go back to?</t>
+        </is>
+      </c>
+      <c r="D10" cm="1" s="23">
+        <f t="array" ref="D10">IFERROR(IF(ISREF(INDIRECT("'HighAcuity'!A1")),IF(COUNTIF(ED_Dec!A2:A94,INDIRECT("'HighAcuity'!A2")&amp;"")&gt;0,SUBTOTAL(103,ED_Dec!A2:A94),""),""),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>IF(IFERROR(D10="",FALSE),"",IF(IFERROR(AND(ISNUMBER(D10),OR(ABS(D10-'Bonus Key'!$C$9)&lt;=0.0001)),FALSE),"✔ Correct","✘ Not yet"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E6:E10">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT(E6,1)="✔"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>LEFT(E6,1)="✘"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3287,7 +3508,7 @@
           <t>PT10005</t>
         </is>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="28" t="n">
         <v>45962.22708333333</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -3303,13 +3524,13 @@
           <t>Abdominal Pain / Vomiting</t>
         </is>
       </c>
-      <c r="G2" s="27" t="n">
+      <c r="G2" s="28" t="n">
         <v>45962.22986111111</v>
       </c>
-      <c r="H2" s="27" t="n">
+      <c r="H2" s="28" t="n">
         <v>45962.23125</v>
       </c>
-      <c r="I2" s="27" t="n">
+      <c r="I2" s="28" t="n">
         <v>45962.35902777778</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -3329,7 +3550,7 @@
           <t>PT10010</t>
         </is>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="C3" s="28" t="n">
         <v>45988.65208333333</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -3345,13 +3566,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G3" s="27" t="n">
+      <c r="G3" s="28" t="n">
         <v>45988.66180555556</v>
       </c>
-      <c r="H3" s="27" t="n">
+      <c r="H3" s="28" t="n">
         <v>45988.67152777778</v>
       </c>
-      <c r="I3" s="27" t="n">
+      <c r="I3" s="28" t="n">
         <v>45988.74305555555</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -3371,7 +3592,7 @@
           <t>PT10062</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>45976.31527777778</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -3387,13 +3608,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="G4" s="28" t="n">
         <v>45976.32222222222</v>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="H4" s="28" t="n">
         <v>45976.35486111111</v>
       </c>
-      <c r="I4" s="27" t="n">
+      <c r="I4" s="28" t="n">
         <v>45976.45208333333</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -3413,7 +3634,7 @@
           <t>PT10074</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>45978.54583333333</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -3429,13 +3650,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="28" t="n">
         <v>45978.55416666667</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="28" t="n">
         <v>45978.55902777778</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="I5" s="28" t="n">
         <v>45978.66597222222</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -3455,7 +3676,7 @@
           <t>PT10177</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>45979.63611111111</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -3471,13 +3692,13 @@
           <t>Tremors / Alcohol Withdrawal</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="28" t="n">
         <v>45979.64583333334</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="28" t="n">
         <v>45979.65347222222</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="28" t="n">
         <v>45979.77916666667</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -3497,7 +3718,7 @@
           <t>PT10181</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>45985.73125</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -3513,13 +3734,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="28" t="n">
         <v>45985.73611111111</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="28" t="n">
         <v>45985.80625</v>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I7" s="28" t="n">
         <v>45985.88680555556</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -3539,7 +3760,7 @@
           <t>PT10387</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>45985.55</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -3555,13 +3776,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="28" t="n">
         <v>45985.55277777778</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="28" t="n">
         <v>45985.55555555555</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="28" t="n">
         <v>45985.83125</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -3581,7 +3802,7 @@
           <t>PT10398</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>45967.71111111111</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -3597,13 +3818,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="28" t="n">
         <v>45967.71736111111</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="28" t="n">
         <v>45967.75277777778</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="28" t="n">
         <v>45967.91458333333</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -3623,7 +3844,7 @@
           <t>PT10460</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <v>45982.75833333333</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -3639,13 +3860,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="28" t="n">
         <v>45982.76041666666</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="28" t="n">
         <v>45982.78611111111</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="28" t="n">
         <v>45982.90208333333</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -3665,7 +3886,7 @@
           <t>PT10463</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <v>45982.24513888889</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -3681,13 +3902,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="28" t="n">
         <v>45982.24861111111</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="28" t="n">
         <v>45982.25694444445</v>
       </c>
-      <c r="I11" s="27" t="n">
+      <c r="I11" s="28" t="n">
         <v>45982.37361111111</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -3707,7 +3928,7 @@
           <t>PT10475</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="28" t="n">
         <v>45991.58055555556</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -3723,13 +3944,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="28" t="n">
         <v>45991.58888888889</v>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="28" t="n">
         <v>45991.61388888889</v>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I12" s="28" t="n">
         <v>45991.65208333333</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -3749,7 +3970,7 @@
           <t>PT10510</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="28" t="n">
         <v>45980.76944444444</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -3765,13 +3986,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="28" t="n">
         <v>45980.77986111111</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="28" t="n">
         <v>45980.79375</v>
       </c>
-      <c r="I13" s="27" t="n">
+      <c r="I13" s="28" t="n">
         <v>45981.00902777778</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -3791,7 +4012,7 @@
           <t>PT10537</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="28" t="n">
         <v>45978.65069444444</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -3807,13 +4028,13 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="28" t="n">
         <v>45978.65486111111</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="28" t="n">
         <v>45978.72222222222</v>
       </c>
-      <c r="I14" s="27" t="n">
+      <c r="I14" s="28" t="n">
         <v>45979.04027777778</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -3833,7 +4054,7 @@
           <t>PT10568</t>
         </is>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="28" t="n">
         <v>45978.12638888889</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3849,13 +4070,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="28" t="n">
         <v>45978.13055555556</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="28" t="n">
         <v>45978.13819444444</v>
       </c>
-      <c r="I15" s="27" t="n">
+      <c r="I15" s="28" t="n">
         <v>45978.24583333333</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -3875,7 +4096,7 @@
           <t>PT10601</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <v>45966.72430555556</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3891,13 +4112,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="28" t="n">
         <v>45966.72777777778</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="28" t="n">
         <v>45966.73472222222</v>
       </c>
-      <c r="I16" s="27" t="n">
+      <c r="I16" s="28" t="n">
         <v>45966.79652777778</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -3917,7 +4138,7 @@
           <t>PT10662</t>
         </is>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <v>45968.65</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3933,13 +4154,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="28" t="n">
         <v>45968.65416666667</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="28" t="n">
         <v>45968.69513888889</v>
       </c>
-      <c r="I17" s="27" t="n">
+      <c r="I17" s="28" t="n">
         <v>45968.85</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -3959,7 +4180,7 @@
           <t>PT10749</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="28" t="n">
         <v>45962.53680555556</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3975,13 +4196,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="G18" s="28" t="n">
         <v>45962.54375</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="28" t="n">
         <v>45962.54513888889</v>
       </c>
-      <c r="I18" s="27" t="n">
+      <c r="I18" s="28" t="n">
         <v>45962.74930555555</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -4001,7 +4222,7 @@
           <t>PT10774</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C19" s="28" t="n">
         <v>45978.95694444444</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -4017,13 +4238,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G19" s="28" t="n">
         <v>45978.96111111111</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="28" t="n">
         <v>45978.97847222222</v>
       </c>
-      <c r="I19" s="27" t="n">
+      <c r="I19" s="28" t="n">
         <v>45979.12847222222</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -4043,7 +4264,7 @@
           <t>PT10786</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="28" t="n">
         <v>45966.63055555556</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -4059,13 +4280,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="28" t="n">
         <v>45966.64097222222</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <v>45966.67569444444</v>
       </c>
-      <c r="I20" s="27" t="n">
+      <c r="I20" s="28" t="n">
         <v>45966.73194444444</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -4085,7 +4306,7 @@
           <t>PT10866</t>
         </is>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="28" t="n">
         <v>45983.75902777778</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -4101,13 +4322,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="28" t="n">
         <v>45983.775</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="28" t="n">
         <v>45983.77708333333</v>
       </c>
-      <c r="I21" s="27" t="n">
+      <c r="I21" s="28" t="n">
         <v>45984.00416666667</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -4127,7 +4348,7 @@
           <t>PT10891</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="28" t="n">
         <v>45969.90069444444</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -4143,13 +4364,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="28" t="n">
         <v>45969.90694444445</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="28" t="n">
         <v>45969.90763888889</v>
       </c>
-      <c r="I22" s="27" t="n">
+      <c r="I22" s="28" t="n">
         <v>45970.08541666667</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -4169,7 +4390,7 @@
           <t>PT10932</t>
         </is>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="28" t="n">
         <v>45973.47986111111</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -4185,13 +4406,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G23" s="27" t="n">
+      <c r="G23" s="28" t="n">
         <v>45973.48472222222</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="28" t="n">
         <v>45973.50138888889</v>
       </c>
-      <c r="I23" s="27" t="n">
+      <c r="I23" s="28" t="n">
         <v>45973.61319444444</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -4211,7 +4432,7 @@
           <t>PT10943</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="28" t="n">
         <v>45986.31041666667</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -4227,13 +4448,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="28" t="n">
         <v>45986.32361111111</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="28" t="n">
         <v>45986.3375</v>
       </c>
-      <c r="I24" s="27" t="n">
+      <c r="I24" s="28" t="n">
         <v>45986.48680555556</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -4253,7 +4474,7 @@
           <t>PT10956</t>
         </is>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C25" s="28" t="n">
         <v>45967.41458333333</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -4269,13 +4490,13 @@
           <t>Fall / Hip Pain</t>
         </is>
       </c>
-      <c r="G25" s="27" t="n">
+      <c r="G25" s="28" t="n">
         <v>45967.42083333333</v>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="28" t="n">
         <v>45967.43333333333</v>
       </c>
-      <c r="I25" s="27" t="n">
+      <c r="I25" s="28" t="n">
         <v>45967.63680555556</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -4295,7 +4516,7 @@
           <t>PT11141</t>
         </is>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="28" t="n">
         <v>45977.93055555555</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -4311,13 +4532,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="28" t="n">
         <v>45977.93333333333</v>
       </c>
-      <c r="H26" s="27" t="n">
+      <c r="H26" s="28" t="n">
         <v>45977.98333333333</v>
       </c>
-      <c r="I26" s="27" t="n">
+      <c r="I26" s="28" t="n">
         <v>45978.10416666666</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -4337,7 +4558,7 @@
           <t>PT11188</t>
         </is>
       </c>
-      <c r="C27" s="27" t="n">
+      <c r="C27" s="28" t="n">
         <v>45973.53888888889</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -4353,13 +4574,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="G27" s="28" t="n">
         <v>45973.54583333333</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="28" t="n">
         <v>45973.55833333333</v>
       </c>
-      <c r="I27" s="27" t="n">
+      <c r="I27" s="28" t="n">
         <v>45973.675</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -4379,7 +4600,7 @@
           <t>PT11188</t>
         </is>
       </c>
-      <c r="C28" s="27" t="n">
+      <c r="C28" s="28" t="n">
         <v>45982.75833333333</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -4395,13 +4616,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="G28" s="28" t="n">
         <v>45982.76111111111</v>
       </c>
-      <c r="H28" s="27" t="n">
+      <c r="H28" s="28" t="n">
         <v>45982.78333333333</v>
       </c>
-      <c r="I28" s="27" t="n">
+      <c r="I28" s="28" t="n">
         <v>45982.95208333333</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -4421,7 +4642,7 @@
           <t>PT11231</t>
         </is>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="28" t="n">
         <v>45963.43402777778</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -4437,13 +4658,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G29" s="27" t="n">
+      <c r="G29" s="28" t="n">
         <v>45963.4375</v>
       </c>
-      <c r="H29" s="27" t="n">
+      <c r="H29" s="28" t="n">
         <v>45963.49097222222</v>
       </c>
-      <c r="I29" s="27" t="n">
+      <c r="I29" s="28" t="n">
         <v>45963.53819444445</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -4463,7 +4684,7 @@
           <t>PT11243</t>
         </is>
       </c>
-      <c r="C30" s="27" t="n">
+      <c r="C30" s="28" t="n">
         <v>45964.74652777778</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -4479,13 +4700,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G30" s="27" t="n">
+      <c r="G30" s="28" t="n">
         <v>45964.75416666667</v>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="H30" s="28" t="n">
         <v>45964.77638888889</v>
       </c>
-      <c r="I30" s="27" t="n">
+      <c r="I30" s="28" t="n">
         <v>45964.84791666667</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -4505,7 +4726,7 @@
           <t>PT11274</t>
         </is>
       </c>
-      <c r="C31" s="27" t="n">
+      <c r="C31" s="28" t="n">
         <v>45980.45763888889</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -4521,13 +4742,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G31" s="27" t="n">
+      <c r="G31" s="28" t="n">
         <v>45980.46111111111</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="28" t="n">
         <v>45980.51875</v>
       </c>
-      <c r="I31" s="27" t="n">
+      <c r="I31" s="28" t="n">
         <v>45980.68402777778</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -4547,7 +4768,7 @@
           <t>PT11381</t>
         </is>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="28" t="n">
         <v>45966.8875</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -4563,13 +4784,13 @@
           <t>High Blood Sugar</t>
         </is>
       </c>
-      <c r="G32" s="27" t="n">
+      <c r="G32" s="28" t="n">
         <v>45966.89375</v>
       </c>
-      <c r="H32" s="27" t="n">
+      <c r="H32" s="28" t="n">
         <v>45966.93402777778</v>
       </c>
-      <c r="I32" s="27" t="n">
+      <c r="I32" s="28" t="n">
         <v>45967.05625</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -4589,7 +4810,7 @@
           <t>PT11401</t>
         </is>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="28" t="n">
         <v>45973.4875</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -4605,13 +4826,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G33" s="27" t="n">
+      <c r="G33" s="28" t="n">
         <v>45973.49166666667</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="28" t="n">
         <v>45973.57083333333</v>
       </c>
-      <c r="I33" s="27" t="n">
+      <c r="I33" s="28" t="n">
         <v>45973.62430555555</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -4631,7 +4852,7 @@
           <t>PT11412</t>
         </is>
       </c>
-      <c r="C34" s="27" t="n">
+      <c r="C34" s="28" t="n">
         <v>45972.04166666666</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -4647,13 +4868,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G34" s="27" t="n">
+      <c r="G34" s="28" t="n">
         <v>45972.05555555555</v>
       </c>
-      <c r="H34" s="27" t="n">
+      <c r="H34" s="28" t="n">
         <v>45972.05625</v>
       </c>
-      <c r="I34" s="27" t="n">
+      <c r="I34" s="28" t="n">
         <v>45972.28263888889</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -4673,7 +4894,7 @@
           <t>PT11433</t>
         </is>
       </c>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="28" t="n">
         <v>45982.39097222222</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -4689,13 +4910,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G35" s="27" t="n">
+      <c r="G35" s="28" t="n">
         <v>45982.39305555556</v>
       </c>
-      <c r="H35" s="27" t="n">
+      <c r="H35" s="28" t="n">
         <v>45982.40416666667</v>
       </c>
-      <c r="I35" s="27" t="n">
+      <c r="I35" s="28" t="n">
         <v>45982.54305555556</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -4715,7 +4936,7 @@
           <t>PT11443</t>
         </is>
       </c>
-      <c r="C36" s="27" t="n">
+      <c r="C36" s="28" t="n">
         <v>45978.29791666667</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -4731,13 +4952,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G36" s="27" t="n">
+      <c r="G36" s="28" t="n">
         <v>45978.31041666667</v>
       </c>
-      <c r="H36" s="27" t="n">
+      <c r="H36" s="28" t="n">
         <v>45978.325</v>
       </c>
-      <c r="I36" s="27" t="n">
+      <c r="I36" s="28" t="n">
         <v>45978.42152777778</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -4757,7 +4978,7 @@
           <t>PT11456</t>
         </is>
       </c>
-      <c r="C37" s="27" t="n">
+      <c r="C37" s="28" t="n">
         <v>45967.47361111111</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -4773,13 +4994,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G37" s="27" t="n">
+      <c r="G37" s="28" t="n">
         <v>45967.47638888889</v>
       </c>
-      <c r="H37" s="27" t="n">
+      <c r="H37" s="28" t="n">
         <v>45967.48958333334</v>
       </c>
-      <c r="I37" s="27" t="n">
+      <c r="I37" s="28" t="n">
         <v>45967.87638888889</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -4799,7 +5020,7 @@
           <t>PT11485</t>
         </is>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="28" t="n">
         <v>45973.91736111111</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -4815,13 +5036,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G38" s="28" t="n">
         <v>45973.92291666667</v>
       </c>
-      <c r="H38" s="27" t="n">
+      <c r="H38" s="28" t="n">
         <v>45973.92361111111</v>
       </c>
-      <c r="I38" s="27" t="n">
+      <c r="I38" s="28" t="n">
         <v>45974.06041666667</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -4841,7 +5062,7 @@
           <t>PT11591</t>
         </is>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C39" s="28" t="n">
         <v>45974.81458333333</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -4857,13 +5078,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G39" s="28" t="n">
         <v>45974.81944444445</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="28" t="n">
         <v>45974.82152777778</v>
       </c>
-      <c r="I39" s="27" t="n">
+      <c r="I39" s="28" t="n">
         <v>45974.86527777778</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -4883,7 +5104,7 @@
           <t>PT11783</t>
         </is>
       </c>
-      <c r="C40" s="27" t="n">
+      <c r="C40" s="28" t="n">
         <v>45965.52222222222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -4899,13 +5120,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="G40" s="28" t="n">
         <v>45965.52430555555</v>
       </c>
-      <c r="H40" s="27" t="n">
+      <c r="H40" s="28" t="n">
         <v>45965.54722222222</v>
       </c>
-      <c r="I40" s="27" t="n">
+      <c r="I40" s="28" t="n">
         <v>45965.67361111111</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -4925,7 +5146,7 @@
           <t>PT11816</t>
         </is>
       </c>
-      <c r="C41" s="27" t="n">
+      <c r="C41" s="28" t="n">
         <v>45980.73888888889</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -4941,13 +5162,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G41" s="27" t="n">
+      <c r="G41" s="28" t="n">
         <v>45980.74375</v>
       </c>
-      <c r="H41" s="27" t="n">
+      <c r="H41" s="28" t="n">
         <v>45980.80972222222</v>
       </c>
-      <c r="I41" s="27" t="n">
+      <c r="I41" s="28" t="n">
         <v>45980.83541666667</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -4967,7 +5188,7 @@
           <t>PT11832</t>
         </is>
       </c>
-      <c r="C42" s="27" t="n">
+      <c r="C42" s="28" t="n">
         <v>45986.54097222222</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -4983,13 +5204,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G42" s="27" t="n">
+      <c r="G42" s="28" t="n">
         <v>45986.54930555556</v>
       </c>
-      <c r="H42" s="27" t="n">
+      <c r="H42" s="28" t="n">
         <v>45986.57013888889</v>
       </c>
-      <c r="I42" s="27" t="n">
+      <c r="I42" s="28" t="n">
         <v>45986.73194444444</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -5009,7 +5230,7 @@
           <t>PT11926</t>
         </is>
       </c>
-      <c r="C43" s="27" t="n">
+      <c r="C43" s="28" t="n">
         <v>45977.91319444445</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -5025,13 +5246,13 @@
           <t>Fall</t>
         </is>
       </c>
-      <c r="G43" s="27" t="n">
+      <c r="G43" s="28" t="n">
         <v>45977.92083333333</v>
       </c>
-      <c r="H43" s="27" t="n">
+      <c r="H43" s="28" t="n">
         <v>45977.92152777778</v>
       </c>
-      <c r="I43" s="27" t="n">
+      <c r="I43" s="28" t="n">
         <v>45978.11944444444</v>
       </c>
       <c r="J43" t="inlineStr">
@@ -5051,7 +5272,7 @@
           <t>PT12026</t>
         </is>
       </c>
-      <c r="C44" s="27" t="n">
+      <c r="C44" s="28" t="n">
         <v>45969.66875</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -5067,13 +5288,13 @@
           <t>Back Pain</t>
         </is>
       </c>
-      <c r="G44" s="27" t="n">
+      <c r="G44" s="28" t="n">
         <v>45969.67430555556</v>
       </c>
-      <c r="H44" s="27" t="n">
+      <c r="H44" s="28" t="n">
         <v>45969.68888888889</v>
       </c>
-      <c r="I44" s="27" t="n">
+      <c r="I44" s="28" t="n">
         <v>45969.75763888889</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -5093,7 +5314,7 @@
           <t>PT12081</t>
         </is>
       </c>
-      <c r="C45" s="27" t="n">
+      <c r="C45" s="28" t="n">
         <v>45969.28888888889</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -5109,13 +5330,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G45" s="27" t="n">
+      <c r="G45" s="28" t="n">
         <v>45969.29444444444</v>
       </c>
-      <c r="H45" s="27" t="n">
+      <c r="H45" s="28" t="n">
         <v>45969.30694444444</v>
       </c>
-      <c r="I45" s="27" t="n">
+      <c r="I45" s="28" t="n">
         <v>45969.38055555556</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -5135,7 +5356,7 @@
           <t>PT12105</t>
         </is>
       </c>
-      <c r="C46" s="27" t="n">
+      <c r="C46" s="28" t="n">
         <v>45986.35</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -5151,13 +5372,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G46" s="27" t="n">
+      <c r="G46" s="28" t="n">
         <v>45986.35277777778</v>
       </c>
-      <c r="H46" s="27" t="n">
+      <c r="H46" s="28" t="n">
         <v>45986.37152777778</v>
       </c>
-      <c r="I46" s="27" t="n">
+      <c r="I46" s="28" t="n">
         <v>45986.41111111111</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -5177,7 +5398,7 @@
           <t>PT12123</t>
         </is>
       </c>
-      <c r="C47" s="27" t="n">
+      <c r="C47" s="28" t="n">
         <v>45981.42222222222</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -5193,13 +5414,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G47" s="27" t="n">
+      <c r="G47" s="28" t="n">
         <v>45981.42708333334</v>
       </c>
-      <c r="H47" s="27" t="n">
+      <c r="H47" s="28" t="n">
         <v>45981.45</v>
       </c>
-      <c r="I47" s="27" t="n">
+      <c r="I47" s="28" t="n">
         <v>45981.49583333333</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -5219,7 +5440,7 @@
           <t>PT12166</t>
         </is>
       </c>
-      <c r="C48" s="27" t="n">
+      <c r="C48" s="28" t="n">
         <v>45962.35902777778</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -5235,13 +5456,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G48" s="27" t="n">
+      <c r="G48" s="28" t="n">
         <v>45962.36458333334</v>
       </c>
-      <c r="H48" s="27" t="n">
+      <c r="H48" s="28" t="n">
         <v>45962.42847222222</v>
       </c>
-      <c r="I48" s="27" t="n">
+      <c r="I48" s="28" t="n">
         <v>45962.49166666667</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -5261,7 +5482,7 @@
           <t>PT12166</t>
         </is>
       </c>
-      <c r="C49" s="27" t="n">
+      <c r="C49" s="28" t="n">
         <v>45973.89791666667</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -5277,13 +5498,13 @@
           <t>Bloody Stool / Vomiting Blood</t>
         </is>
       </c>
-      <c r="G49" s="27" t="n">
+      <c r="G49" s="28" t="n">
         <v>45973.90486111111</v>
       </c>
-      <c r="H49" s="27" t="n">
+      <c r="H49" s="28" t="n">
         <v>45973.90555555555</v>
       </c>
-      <c r="I49" s="27" t="n">
+      <c r="I49" s="28" t="n">
         <v>45974.27430555555</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -5303,7 +5524,7 @@
           <t>PT12206</t>
         </is>
       </c>
-      <c r="C50" s="27" t="n">
+      <c r="C50" s="28" t="n">
         <v>45972.43958333333</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -5319,13 +5540,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G50" s="27" t="n">
+      <c r="G50" s="28" t="n">
         <v>45972.45625</v>
       </c>
-      <c r="H50" s="27" t="n">
+      <c r="H50" s="28" t="n">
         <v>45972.45694444444</v>
       </c>
-      <c r="I50" s="27" t="n">
+      <c r="I50" s="28" t="n">
         <v>45972.90972222222</v>
       </c>
       <c r="J50" t="inlineStr">
@@ -5345,7 +5566,7 @@
           <t>PT12242</t>
         </is>
       </c>
-      <c r="C51" s="27" t="n">
+      <c r="C51" s="28" t="n">
         <v>45967.6375</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -5361,13 +5582,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G51" s="27" t="n">
+      <c r="G51" s="28" t="n">
         <v>45967.64097222222</v>
       </c>
-      <c r="H51" s="27" t="n">
+      <c r="H51" s="28" t="n">
         <v>45967.65763888889</v>
       </c>
-      <c r="I51" s="27" t="n">
+      <c r="I51" s="28" t="n">
         <v>45967.80277777778</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -5387,7 +5608,7 @@
           <t>PT12285</t>
         </is>
       </c>
-      <c r="C52" s="27" t="n">
+      <c r="C52" s="28" t="n">
         <v>45985.57569444444</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -5403,13 +5624,13 @@
           <t>Laceration</t>
         </is>
       </c>
-      <c r="G52" s="27" t="n">
+      <c r="G52" s="28" t="n">
         <v>45985.58125</v>
       </c>
-      <c r="H52" s="27" t="n">
+      <c r="H52" s="28" t="n">
         <v>45985.65625</v>
       </c>
-      <c r="I52" s="27" t="n">
+      <c r="I52" s="28" t="n">
         <v>45985.79791666667</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -5429,7 +5650,7 @@
           <t>PT12299</t>
         </is>
       </c>
-      <c r="C53" s="27" t="n">
+      <c r="C53" s="28" t="n">
         <v>45974.40555555555</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -5445,13 +5666,13 @@
           <t>Dizziness</t>
         </is>
       </c>
-      <c r="G53" s="27" t="n">
+      <c r="G53" s="28" t="n">
         <v>45974.41180555556</v>
       </c>
-      <c r="H53" s="27" t="n">
+      <c r="H53" s="28" t="n">
         <v>45974.47013888889</v>
       </c>
-      <c r="I53" s="27" t="n">
+      <c r="I53" s="28" t="n">
         <v>45974.69236111111</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -5471,7 +5692,7 @@
           <t>PT12314</t>
         </is>
       </c>
-      <c r="C54" s="27" t="n">
+      <c r="C54" s="28" t="n">
         <v>45987.23402777778</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -5487,13 +5708,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G54" s="27" t="n">
+      <c r="G54" s="28" t="n">
         <v>45987.23958333334</v>
       </c>
-      <c r="H54" s="27" t="n">
+      <c r="H54" s="28" t="n">
         <v>45987.26458333333</v>
       </c>
-      <c r="I54" s="27" t="n">
+      <c r="I54" s="28" t="n">
         <v>45987.37361111111</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -5513,7 +5734,7 @@
           <t>PT12519</t>
         </is>
       </c>
-      <c r="C55" s="27" t="n">
+      <c r="C55" s="28" t="n">
         <v>45971.49513888889</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -5529,13 +5750,13 @@
           <t>Weakness / Fatigue</t>
         </is>
       </c>
-      <c r="G55" s="27" t="n">
+      <c r="G55" s="28" t="n">
         <v>45971.50486111111</v>
       </c>
-      <c r="H55" s="27" t="n">
+      <c r="H55" s="28" t="n">
         <v>45971.51111111111</v>
       </c>
-      <c r="I55" s="27" t="n">
+      <c r="I55" s="28" t="n">
         <v>45971.77361111111</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -5555,7 +5776,7 @@
           <t>PT12563</t>
         </is>
       </c>
-      <c r="C56" s="27" t="n">
+      <c r="C56" s="28" t="n">
         <v>45991.15972222222</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -5571,13 +5792,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G56" s="27" t="n">
+      <c r="G56" s="28" t="n">
         <v>45991.16527777778</v>
       </c>
-      <c r="H56" s="27" t="n">
+      <c r="H56" s="28" t="n">
         <v>45991.16597222222</v>
       </c>
-      <c r="I56" s="27" t="n">
+      <c r="I56" s="28" t="n">
         <v>45991.33888888889</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -5597,7 +5818,7 @@
           <t>PT12641</t>
         </is>
       </c>
-      <c r="C57" s="27" t="n">
+      <c r="C57" s="28" t="n">
         <v>45982.55347222222</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -5613,13 +5834,13 @@
           <t>Vomiting / Diarrhea</t>
         </is>
       </c>
-      <c r="G57" s="27" t="n">
+      <c r="G57" s="28" t="n">
         <v>45982.56041666667</v>
       </c>
-      <c r="H57" s="27" t="n">
+      <c r="H57" s="28" t="n">
         <v>45982.62708333333</v>
       </c>
-      <c r="I57" s="27" t="n">
+      <c r="I57" s="28" t="n">
         <v>45982.70555555556</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -5639,7 +5860,7 @@
           <t>PT12695</t>
         </is>
       </c>
-      <c r="C58" s="27" t="n">
+      <c r="C58" s="28" t="n">
         <v>45989.82986111111</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -5655,13 +5876,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G58" s="27" t="n">
+      <c r="G58" s="28" t="n">
         <v>45989.83472222222</v>
       </c>
-      <c r="H58" s="27" t="n">
+      <c r="H58" s="28" t="n">
         <v>45989.89861111111</v>
       </c>
-      <c r="I58" s="27" t="n">
+      <c r="I58" s="28" t="n">
         <v>45989.98541666667</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -5681,7 +5902,7 @@
           <t>PT12735</t>
         </is>
       </c>
-      <c r="C59" s="27" t="n">
+      <c r="C59" s="28" t="n">
         <v>45964.76944444444</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -5697,13 +5918,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G59" s="27" t="n">
+      <c r="G59" s="28" t="n">
         <v>45964.77291666667</v>
       </c>
-      <c r="H59" s="27" t="n">
+      <c r="H59" s="28" t="n">
         <v>45964.78888888889</v>
       </c>
-      <c r="I59" s="27" t="n">
+      <c r="I59" s="28" t="n">
         <v>45964.88958333333</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -5723,7 +5944,7 @@
           <t>PT12735</t>
         </is>
       </c>
-      <c r="C60" s="27" t="n">
+      <c r="C60" s="28" t="n">
         <v>45977.00694444445</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -5739,13 +5960,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G60" s="27" t="n">
+      <c r="G60" s="28" t="n">
         <v>45977.01180555556</v>
       </c>
-      <c r="H60" s="27" t="n">
+      <c r="H60" s="28" t="n">
         <v>45977.03611111111</v>
       </c>
-      <c r="I60" s="27" t="n">
+      <c r="I60" s="28" t="n">
         <v>45977.14652777778</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -5765,7 +5986,7 @@
           <t>PT12749</t>
         </is>
       </c>
-      <c r="C61" s="27" t="n">
+      <c r="C61" s="28" t="n">
         <v>45963.88263888889</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -5781,13 +6002,13 @@
           <t>Rash</t>
         </is>
       </c>
-      <c r="G61" s="27" t="n">
+      <c r="G61" s="28" t="n">
         <v>45963.8875</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H61" s="28" t="n">
         <v>45963.89861111111</v>
       </c>
-      <c r="I61" s="27" t="n">
+      <c r="I61" s="28" t="n">
         <v>45964.10347222222</v>
       </c>
       <c r="J61" t="inlineStr">
@@ -5807,7 +6028,7 @@
           <t>PT12774</t>
         </is>
       </c>
-      <c r="C62" s="27" t="n">
+      <c r="C62" s="28" t="n">
         <v>45984.73333333333</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -5823,10 +6044,10 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G62" s="27" t="n">
+      <c r="G62" s="28" t="n">
         <v>45984.73888888889</v>
       </c>
-      <c r="I62" s="27" t="n">
+      <c r="I62" s="28" t="n">
         <v>45984.78333333333</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -5846,7 +6067,7 @@
           <t>PT12802</t>
         </is>
       </c>
-      <c r="C63" s="27" t="n">
+      <c r="C63" s="28" t="n">
         <v>45965.56875</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -5862,13 +6083,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G63" s="27" t="n">
+      <c r="G63" s="28" t="n">
         <v>45965.57638888889</v>
       </c>
-      <c r="H63" s="27" t="n">
+      <c r="H63" s="28" t="n">
         <v>45965.6125</v>
       </c>
-      <c r="I63" s="27" t="n">
+      <c r="I63" s="28" t="n">
         <v>45965.72569444445</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -5888,7 +6109,7 @@
           <t>PT12851</t>
         </is>
       </c>
-      <c r="C64" s="27" t="n">
+      <c r="C64" s="28" t="n">
         <v>45977.26041666666</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -5904,13 +6125,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G64" s="27" t="n">
+      <c r="G64" s="28" t="n">
         <v>45977.26458333333</v>
       </c>
-      <c r="H64" s="27" t="n">
+      <c r="H64" s="28" t="n">
         <v>45977.27083333334</v>
       </c>
-      <c r="I64" s="27" t="n">
+      <c r="I64" s="28" t="n">
         <v>45977.43680555555</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -5930,7 +6151,7 @@
           <t>PT12893</t>
         </is>
       </c>
-      <c r="C65" s="27" t="n">
+      <c r="C65" s="28" t="n">
         <v>45988.59583333333</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -5946,13 +6167,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G65" s="27" t="n">
+      <c r="G65" s="28" t="n">
         <v>45988.60208333333</v>
       </c>
-      <c r="H65" s="27" t="n">
+      <c r="H65" s="28" t="n">
         <v>45988.65138888889</v>
       </c>
-      <c r="I65" s="27" t="n">
+      <c r="I65" s="28" t="n">
         <v>45988.71319444444</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -5972,7 +6193,7 @@
           <t>PT12896</t>
         </is>
       </c>
-      <c r="C66" s="27" t="n">
+      <c r="C66" s="28" t="n">
         <v>45963.58194444444</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -5988,13 +6209,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G66" s="27" t="n">
+      <c r="G66" s="28" t="n">
         <v>45963.58958333333</v>
       </c>
-      <c r="H66" s="27" t="n">
+      <c r="H66" s="28" t="n">
         <v>45963.59861111111</v>
       </c>
-      <c r="I66" s="27" t="n">
+      <c r="I66" s="28" t="n">
         <v>45963.80138888889</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -6014,7 +6235,7 @@
           <t>PT12929</t>
         </is>
       </c>
-      <c r="C67" s="27" t="n">
+      <c r="C67" s="28" t="n">
         <v>45982.09166666667</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -6030,13 +6251,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G67" s="27" t="n">
+      <c r="G67" s="28" t="n">
         <v>45982.09652777778</v>
       </c>
-      <c r="H67" s="27" t="n">
+      <c r="H67" s="28" t="n">
         <v>45982.11111111111</v>
       </c>
-      <c r="I67" s="27" t="n">
+      <c r="I67" s="28" t="n">
         <v>45982.14722222222</v>
       </c>
       <c r="J67" t="inlineStr">
@@ -6056,7 +6277,7 @@
           <t>PT12938</t>
         </is>
       </c>
-      <c r="C68" s="27" t="n">
+      <c r="C68" s="28" t="n">
         <v>45964.40972222222</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -6072,13 +6293,13 @@
           <t>High Blood Sugar</t>
         </is>
       </c>
-      <c r="G68" s="27" t="n">
+      <c r="G68" s="28" t="n">
         <v>45964.41527777778</v>
       </c>
-      <c r="H68" s="27" t="n">
+      <c r="H68" s="28" t="n">
         <v>45964.43125</v>
       </c>
-      <c r="I68" s="27" t="n">
+      <c r="I68" s="28" t="n">
         <v>45964.59791666667</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -6098,7 +6319,7 @@
           <t>PT12989</t>
         </is>
       </c>
-      <c r="C69" s="27" t="n">
+      <c r="C69" s="28" t="n">
         <v>45985.6875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -6114,10 +6335,10 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G69" s="27" t="n">
+      <c r="G69" s="28" t="n">
         <v>45985.68958333333</v>
       </c>
-      <c r="I69" s="27" t="n">
+      <c r="I69" s="28" t="n">
         <v>45985.79652777778</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -6137,7 +6358,7 @@
           <t>PT13110</t>
         </is>
       </c>
-      <c r="C70" s="27" t="n">
+      <c r="C70" s="28" t="n">
         <v>45970.00972222222</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -6153,13 +6374,13 @@
           <t>Palpitations</t>
         </is>
       </c>
-      <c r="G70" s="27" t="n">
+      <c r="G70" s="28" t="n">
         <v>45970.01319444444</v>
       </c>
-      <c r="H70" s="27" t="n">
+      <c r="H70" s="28" t="n">
         <v>45970.01388888889</v>
       </c>
-      <c r="I70" s="27" t="n">
+      <c r="I70" s="28" t="n">
         <v>45970.11736111111</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -6179,7 +6400,7 @@
           <t>PT13179</t>
         </is>
       </c>
-      <c r="C71" s="27" t="n">
+      <c r="C71" s="28" t="n">
         <v>45972.275</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -6195,13 +6416,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G71" s="27" t="n">
+      <c r="G71" s="28" t="n">
         <v>45972.27916666667</v>
       </c>
-      <c r="H71" s="27" t="n">
+      <c r="H71" s="28" t="n">
         <v>45972.28680555556</v>
       </c>
-      <c r="I71" s="27" t="n">
+      <c r="I71" s="28" t="n">
         <v>45972.36666666667</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -6221,7 +6442,7 @@
           <t>PT13217</t>
         </is>
       </c>
-      <c r="C72" s="27" t="n">
+      <c r="C72" s="28" t="n">
         <v>45984.72847222222</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -6237,13 +6458,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G72" s="27" t="n">
+      <c r="G72" s="28" t="n">
         <v>45984.73194444444</v>
       </c>
-      <c r="H72" s="27" t="n">
+      <c r="H72" s="28" t="n">
         <v>45984.75972222222</v>
       </c>
-      <c r="I72" s="27" t="n">
+      <c r="I72" s="28" t="n">
         <v>45984.99305555555</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -6263,7 +6484,7 @@
           <t>PT13427</t>
         </is>
       </c>
-      <c r="C73" s="27" t="n">
+      <c r="C73" s="28" t="n">
         <v>45990.44930555556</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -6279,13 +6500,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G73" s="27" t="n">
+      <c r="G73" s="28" t="n">
         <v>45990.45833333334</v>
       </c>
-      <c r="H73" s="27" t="n">
+      <c r="H73" s="28" t="n">
         <v>45990.47777777778</v>
       </c>
-      <c r="I73" s="27" t="n">
+      <c r="I73" s="28" t="n">
         <v>45990.60902777778</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -6305,7 +6526,7 @@
           <t>PT13519</t>
         </is>
       </c>
-      <c r="C74" s="27" t="n">
+      <c r="C74" s="28" t="n">
         <v>45991.72430555556</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -6321,13 +6542,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G74" s="27" t="n">
+      <c r="G74" s="28" t="n">
         <v>45991.72708333333</v>
       </c>
-      <c r="H74" s="27" t="n">
+      <c r="H74" s="28" t="n">
         <v>45991.74652777778</v>
       </c>
-      <c r="I74" s="27" t="n">
+      <c r="I74" s="28" t="n">
         <v>45992.02361111111</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -6347,7 +6568,7 @@
           <t>PT13560</t>
         </is>
       </c>
-      <c r="C75" s="27" t="n">
+      <c r="C75" s="28" t="n">
         <v>45978.92708333334</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -6363,10 +6584,10 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G75" s="27" t="n">
+      <c r="G75" s="28" t="n">
         <v>45978.93125</v>
       </c>
-      <c r="I75" s="27" t="n">
+      <c r="I75" s="28" t="n">
         <v>45978.97638888889</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -6386,7 +6607,7 @@
           <t>PT13575</t>
         </is>
       </c>
-      <c r="C76" s="27" t="n">
+      <c r="C76" s="28" t="n">
         <v>45984.97152777778</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -6402,13 +6623,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G76" s="27" t="n">
+      <c r="G76" s="28" t="n">
         <v>45984.97916666666</v>
       </c>
-      <c r="H76" s="27" t="n">
+      <c r="H76" s="28" t="n">
         <v>45984.98125</v>
       </c>
-      <c r="I76" s="27" t="n">
+      <c r="I76" s="28" t="n">
         <v>45985.04722222222</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -6428,7 +6649,7 @@
           <t>PT13601</t>
         </is>
       </c>
-      <c r="C77" s="27" t="n">
+      <c r="C77" s="28" t="n">
         <v>45968.84861111111</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -6444,13 +6665,13 @@
           <t>Fall</t>
         </is>
       </c>
-      <c r="G77" s="27" t="n">
+      <c r="G77" s="28" t="n">
         <v>45968.85902777778</v>
       </c>
-      <c r="H77" s="27" t="n">
+      <c r="H77" s="28" t="n">
         <v>45968.88611111111</v>
       </c>
-      <c r="I77" s="27" t="n">
+      <c r="I77" s="28" t="n">
         <v>45968.91527777778</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -6470,7 +6691,7 @@
           <t>PT13628</t>
         </is>
       </c>
-      <c r="C78" s="27" t="n">
+      <c r="C78" s="28" t="n">
         <v>45982.79513888889</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -6486,13 +6707,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G78" s="27" t="n">
+      <c r="G78" s="28" t="n">
         <v>45982.80486111111</v>
       </c>
-      <c r="H78" s="27" t="n">
+      <c r="H78" s="28" t="n">
         <v>45982.84375</v>
       </c>
-      <c r="I78" s="27" t="n">
+      <c r="I78" s="28" t="n">
         <v>45982.91527777778</v>
       </c>
       <c r="J78" t="inlineStr">
@@ -6512,7 +6733,7 @@
           <t>PT13702</t>
         </is>
       </c>
-      <c r="C79" s="27" t="n">
+      <c r="C79" s="28" t="n">
         <v>45991.50069444445</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -6528,13 +6749,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G79" s="27" t="n">
+      <c r="G79" s="28" t="n">
         <v>45991.50833333333</v>
       </c>
-      <c r="H79" s="27" t="n">
+      <c r="H79" s="28" t="n">
         <v>45991.50972222222</v>
       </c>
-      <c r="I79" s="27" t="n">
+      <c r="I79" s="28" t="n">
         <v>45991.60555555556</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -6554,7 +6775,7 @@
           <t>PT13869</t>
         </is>
       </c>
-      <c r="C80" s="27" t="n">
+      <c r="C80" s="28" t="n">
         <v>45990.72847222222</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -6570,13 +6791,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G80" s="27" t="n">
+      <c r="G80" s="28" t="n">
         <v>45990.73194444444</v>
       </c>
-      <c r="H80" s="27" t="n">
+      <c r="H80" s="28" t="n">
         <v>45990.74027777778</v>
       </c>
-      <c r="I80" s="27" t="n">
+      <c r="I80" s="28" t="n">
         <v>45990.82638888889</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -6596,7 +6817,7 @@
           <t>PT13940</t>
         </is>
       </c>
-      <c r="C81" s="27" t="n">
+      <c r="C81" s="28" t="n">
         <v>45963.57361111111</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -6612,13 +6833,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G81" s="27" t="n">
+      <c r="G81" s="28" t="n">
         <v>45963.57847222222</v>
       </c>
-      <c r="H81" s="27" t="n">
+      <c r="H81" s="28" t="n">
         <v>45963.58194444444</v>
       </c>
-      <c r="I81" s="27" t="n">
+      <c r="I81" s="28" t="n">
         <v>45963.72986111111</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -6632,7 +6853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6716,7 +6937,7 @@
           <t>PT10032</t>
         </is>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="28" t="n">
         <v>45995.46180555555</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6732,13 +6953,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G2" s="27" t="n">
+      <c r="G2" s="28" t="n">
         <v>45995.46597222222</v>
       </c>
-      <c r="H2" s="27" t="n">
+      <c r="H2" s="28" t="n">
         <v>45995.57847222222</v>
       </c>
-      <c r="I2" s="27" t="n">
+      <c r="I2" s="28" t="n">
         <v>45995.63055555556</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -6758,7 +6979,7 @@
           <t>PT10032</t>
         </is>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="C3" s="28" t="n">
         <v>46012.51111111111</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6774,10 +6995,10 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G3" s="27" t="n">
+      <c r="G3" s="28" t="n">
         <v>46012.51597222222</v>
       </c>
-      <c r="I3" s="27" t="n">
+      <c r="I3" s="28" t="n">
         <v>46012.60763888889</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -6797,7 +7018,7 @@
           <t>PT10052</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>46011.26805555556</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6813,13 +7034,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="G4" s="28" t="n">
         <v>46011.27291666667</v>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="H4" s="28" t="n">
         <v>46011.27361111111</v>
       </c>
-      <c r="I4" s="27" t="n">
+      <c r="I4" s="28" t="n">
         <v>46011.32708333333</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -6839,7 +7060,7 @@
           <t>PT10299</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>45999.15555555555</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6855,13 +7076,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="28" t="n">
         <v>45999.15763888889</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="28" t="n">
         <v>45999.175</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="I5" s="28" t="n">
         <v>45999.27916666667</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -6881,7 +7102,7 @@
           <t>PT10337</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>46007.88819444444</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6897,13 +7118,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="28" t="n">
         <v>46007.89027777778</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="28" t="n">
         <v>46007.96041666667</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="28" t="n">
         <v>46008.12569444445</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -6923,7 +7144,7 @@
           <t>PT10384</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>46010.8125</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6939,13 +7160,13 @@
           <t>Vomiting / Diarrhea</t>
         </is>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="28" t="n">
         <v>46010.81736111111</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="28" t="n">
         <v>46010.85763888889</v>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I7" s="28" t="n">
         <v>46010.92013888889</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -6965,7 +7186,7 @@
           <t>PT10422</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>46019.59027777778</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6981,13 +7202,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="28" t="n">
         <v>46019.60069444445</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="28" t="n">
         <v>46019.61875</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="28" t="n">
         <v>46019.67638888889</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -7007,7 +7228,7 @@
           <t>PT10495</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>46006.52083333334</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7023,13 +7244,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="28" t="n">
         <v>46006.52638888889</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="28" t="n">
         <v>46006.54652777778</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="28" t="n">
         <v>46006.6375</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -7049,7 +7270,7 @@
           <t>PT10523</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <v>45994.00208333333</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7065,13 +7286,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="28" t="n">
         <v>45994.00555555556</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="28" t="n">
         <v>45994.00694444445</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="28" t="n">
         <v>45994.15277777778</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -7091,7 +7312,7 @@
           <t>PT10591</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <v>46021.76666666667</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7107,13 +7328,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="28" t="n">
         <v>46021.77083333334</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="28" t="n">
         <v>46021.78819444445</v>
       </c>
-      <c r="I11" s="27" t="n">
+      <c r="I11" s="28" t="n">
         <v>46021.90763888889</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -7133,7 +7354,7 @@
           <t>PT10611</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="28" t="n">
         <v>46016.1</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7149,13 +7370,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="28" t="n">
         <v>46016.10555555556</v>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="28" t="n">
         <v>46016.10694444444</v>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I12" s="28" t="n">
         <v>46016.35486111111</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -7175,7 +7396,7 @@
           <t>PT10668</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="28" t="n">
         <v>45994.56319444445</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7191,13 +7412,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="28" t="n">
         <v>45994.56458333333</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="28" t="n">
         <v>45994.56527777778</v>
       </c>
-      <c r="I13" s="27" t="n">
+      <c r="I13" s="28" t="n">
         <v>45994.77291666667</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -7217,7 +7438,7 @@
           <t>PT10721</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="28" t="n">
         <v>45997.6875</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7233,13 +7454,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="28" t="n">
         <v>45997.69861111111</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="28" t="n">
         <v>45997.71736111111</v>
       </c>
-      <c r="I14" s="27" t="n">
+      <c r="I14" s="28" t="n">
         <v>45998.27847222222</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -7259,7 +7480,7 @@
           <t>PT10786</t>
         </is>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="28" t="n">
         <v>46011.51041666666</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7275,13 +7496,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="28" t="n">
         <v>46011.51527777778</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="28" t="n">
         <v>46011.51597222222</v>
       </c>
-      <c r="I15" s="27" t="n">
+      <c r="I15" s="28" t="n">
         <v>46011.81388888889</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -7301,7 +7522,7 @@
           <t>PT10786</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <v>46016.525</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7317,13 +7538,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="28" t="n">
         <v>46016.53125</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="28" t="n">
         <v>46016.54375</v>
       </c>
-      <c r="I16" s="27" t="n">
+      <c r="I16" s="28" t="n">
         <v>46016.58472222222</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -7343,7 +7564,7 @@
           <t>PT10815</t>
         </is>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <v>45999.85347222222</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7359,13 +7580,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="28" t="n">
         <v>45999.85347222222</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="28" t="n">
         <v>45999.85486111111</v>
       </c>
-      <c r="I17" s="27" t="n">
+      <c r="I17" s="28" t="n">
         <v>46000.03055555555</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -7385,7 +7606,7 @@
           <t>PT10855</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="28" t="n">
         <v>46020.88541666666</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7401,13 +7622,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="G18" s="28" t="n">
         <v>46020.89027777778</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="28" t="n">
         <v>46020.93680555555</v>
       </c>
-      <c r="I18" s="27" t="n">
+      <c r="I18" s="28" t="n">
         <v>46020.99513888889</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -7427,7 +7648,7 @@
           <t>PT10886</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C19" s="28" t="n">
         <v>46000.38263888889</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7443,13 +7664,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G19" s="28" t="n">
         <v>46000.38541666666</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="28" t="n">
         <v>46000.41388888889</v>
       </c>
-      <c r="I19" s="27" t="n">
+      <c r="I19" s="28" t="n">
         <v>46000.49583333333</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -7469,7 +7690,7 @@
           <t>PT10969</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="28" t="n">
         <v>45993.33888888889</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7485,13 +7706,13 @@
           <t>Weakness / Fatigue</t>
         </is>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="28" t="n">
         <v>45993.34097222222</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <v>45993.38958333333</v>
       </c>
-      <c r="I20" s="27" t="n">
+      <c r="I20" s="28" t="n">
         <v>45993.63958333333</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -7511,7 +7732,7 @@
           <t>PT10971</t>
         </is>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="28" t="n">
         <v>45998.72013888889</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7527,13 +7748,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="28" t="n">
         <v>45998.725</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="28" t="n">
         <v>45998.79236111111</v>
       </c>
-      <c r="I21" s="27" t="n">
+      <c r="I21" s="28" t="n">
         <v>45998.92986111111</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -7553,7 +7774,7 @@
           <t>PT11034</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="28" t="n">
         <v>46003.49722222222</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7569,13 +7790,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="28" t="n">
         <v>46003.50069444445</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="28" t="n">
         <v>46003.53055555555</v>
       </c>
-      <c r="I22" s="27" t="n">
+      <c r="I22" s="28" t="n">
         <v>46003.84652777778</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -7595,7 +7816,7 @@
           <t>PT11068</t>
         </is>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="28" t="n">
         <v>46016.62013888889</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7611,13 +7832,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G23" s="27" t="n">
+      <c r="G23" s="28" t="n">
         <v>46016.63125</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="28" t="n">
         <v>46016.67013888889</v>
       </c>
-      <c r="I23" s="27" t="n">
+      <c r="I23" s="28" t="n">
         <v>46016.72083333333</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -7637,7 +7858,7 @@
           <t>PT11101</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="28" t="n">
         <v>46006.94791666666</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7653,13 +7874,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="28" t="n">
         <v>46006.95277777778</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="28" t="n">
         <v>46006.95486111111</v>
       </c>
-      <c r="I24" s="27" t="n">
+      <c r="I24" s="28" t="n">
         <v>46007.25416666667</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -7679,7 +7900,7 @@
           <t>PT11115</t>
         </is>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C25" s="28" t="n">
         <v>46004.24375</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7695,13 +7916,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G25" s="27" t="n">
+      <c r="G25" s="28" t="n">
         <v>46004.25347222222</v>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="28" t="n">
         <v>46004.25416666667</v>
       </c>
-      <c r="I25" s="27" t="n">
+      <c r="I25" s="28" t="n">
         <v>46004.40902777778</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -7721,7 +7942,7 @@
           <t>PT11122</t>
         </is>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="28" t="n">
         <v>45998.40277777778</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7737,13 +7958,13 @@
           <t>Fever / Altered Mental Status</t>
         </is>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="28" t="n">
         <v>45998.41388888889</v>
       </c>
-      <c r="H26" s="27" t="n">
+      <c r="H26" s="28" t="n">
         <v>45998.41527777778</v>
       </c>
-      <c r="I26" s="27" t="n">
+      <c r="I26" s="28" t="n">
         <v>45998.75277777778</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -7763,7 +7984,7 @@
           <t>PT11149</t>
         </is>
       </c>
-      <c r="C27" s="27" t="n">
+      <c r="C27" s="28" t="n">
         <v>45998.05208333334</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7779,13 +8000,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="G27" s="28" t="n">
         <v>45998.05625</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="28" t="n">
         <v>45998.05694444444</v>
       </c>
-      <c r="I27" s="27" t="n">
+      <c r="I27" s="28" t="n">
         <v>45998.21736111111</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -7805,7 +8026,7 @@
           <t>PT11168</t>
         </is>
       </c>
-      <c r="C28" s="27" t="n">
+      <c r="C28" s="28" t="n">
         <v>45992.59166666667</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7821,13 +8042,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="G28" s="28" t="n">
         <v>45992.59583333333</v>
       </c>
-      <c r="H28" s="27" t="n">
+      <c r="H28" s="28" t="n">
         <v>45992.62777777778</v>
       </c>
-      <c r="I28" s="27" t="n">
+      <c r="I28" s="28" t="n">
         <v>45992.6625</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -7847,7 +8068,7 @@
           <t>PT11214</t>
         </is>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="28" t="n">
         <v>46003.74444444444</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7863,13 +8084,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G29" s="27" t="n">
+      <c r="G29" s="28" t="n">
         <v>46003.74652777778</v>
       </c>
-      <c r="H29" s="27" t="n">
+      <c r="H29" s="28" t="n">
         <v>46003.76388888889</v>
       </c>
-      <c r="I29" s="27" t="n">
+      <c r="I29" s="28" t="n">
         <v>46004.13958333333</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -7889,7 +8110,7 @@
           <t>PT11240</t>
         </is>
       </c>
-      <c r="C30" s="27" t="n">
+      <c r="C30" s="28" t="n">
         <v>46015.57847222222</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7905,13 +8126,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G30" s="27" t="n">
+      <c r="G30" s="28" t="n">
         <v>46015.58125</v>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="H30" s="28" t="n">
         <v>46015.64444444444</v>
       </c>
-      <c r="I30" s="27" t="n">
+      <c r="I30" s="28" t="n">
         <v>46015.99027777778</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -7931,7 +8152,7 @@
           <t>PT11246</t>
         </is>
       </c>
-      <c r="C31" s="27" t="n">
+      <c r="C31" s="28" t="n">
         <v>46016.66527777778</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7947,13 +8168,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G31" s="27" t="n">
+      <c r="G31" s="28" t="n">
         <v>46016.67013888889</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="28" t="n">
         <v>46016.72013888889</v>
       </c>
-      <c r="I31" s="27" t="n">
+      <c r="I31" s="28" t="n">
         <v>46017.02361111111</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -7973,7 +8194,7 @@
           <t>PT11247</t>
         </is>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="28" t="n">
         <v>45992.84583333333</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7989,13 +8210,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G32" s="27" t="n">
+      <c r="G32" s="28" t="n">
         <v>45992.85625</v>
       </c>
-      <c r="H32" s="27" t="n">
+      <c r="H32" s="28" t="n">
         <v>45992.86597222222</v>
       </c>
-      <c r="I32" s="27" t="n">
+      <c r="I32" s="28" t="n">
         <v>45993.11319444444</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -8015,7 +8236,7 @@
           <t>PT11427</t>
         </is>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="28" t="n">
         <v>46018.62361111111</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8031,13 +8252,13 @@
           <t>Back Pain</t>
         </is>
       </c>
-      <c r="G33" s="27" t="n">
+      <c r="G33" s="28" t="n">
         <v>46018.62916666667</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="28" t="n">
         <v>46018.65208333333</v>
       </c>
-      <c r="I33" s="27" t="n">
+      <c r="I33" s="28" t="n">
         <v>46018.77986111111</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -8057,7 +8278,7 @@
           <t>PT11452</t>
         </is>
       </c>
-      <c r="C34" s="27" t="n">
+      <c r="C34" s="28" t="n">
         <v>46021.72222222222</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8073,13 +8294,13 @@
           <t>Rash</t>
         </is>
       </c>
-      <c r="G34" s="27" t="n">
+      <c r="G34" s="28" t="n">
         <v>46021.72638888889</v>
       </c>
-      <c r="H34" s="27" t="n">
+      <c r="H34" s="28" t="n">
         <v>46021.76041666666</v>
       </c>
-      <c r="I34" s="27" t="n">
+      <c r="I34" s="28" t="n">
         <v>46021.88958333333</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -8099,7 +8320,7 @@
           <t>PT11518</t>
         </is>
       </c>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="28" t="n">
         <v>46004.63194444445</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8115,13 +8336,13 @@
           <t>Vomiting / Diarrhea</t>
         </is>
       </c>
-      <c r="G35" s="27" t="n">
+      <c r="G35" s="28" t="n">
         <v>46004.63472222222</v>
       </c>
-      <c r="H35" s="27" t="n">
+      <c r="H35" s="28" t="n">
         <v>46004.67916666667</v>
       </c>
-      <c r="I35" s="27" t="n">
+      <c r="I35" s="28" t="n">
         <v>46004.80555555555</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -8141,7 +8362,7 @@
           <t>PT11542</t>
         </is>
       </c>
-      <c r="C36" s="27" t="n">
+      <c r="C36" s="28" t="n">
         <v>46013.27569444444</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8157,13 +8378,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G36" s="27" t="n">
+      <c r="G36" s="28" t="n">
         <v>46013.28402777778</v>
       </c>
-      <c r="H36" s="27" t="n">
+      <c r="H36" s="28" t="n">
         <v>46013.35</v>
       </c>
-      <c r="I36" s="27" t="n">
+      <c r="I36" s="28" t="n">
         <v>46013.43263888889</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -8183,7 +8404,7 @@
           <t>PT11548</t>
         </is>
       </c>
-      <c r="C37" s="27" t="n">
+      <c r="C37" s="28" t="n">
         <v>46004.5375</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8199,13 +8420,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G37" s="27" t="n">
+      <c r="G37" s="28" t="n">
         <v>46004.54236111111</v>
       </c>
-      <c r="H37" s="27" t="n">
+      <c r="H37" s="28" t="n">
         <v>46004.56111111111</v>
       </c>
-      <c r="I37" s="27" t="n">
+      <c r="I37" s="28" t="n">
         <v>46004.70694444444</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -8225,7 +8446,7 @@
           <t>PT11673</t>
         </is>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="28" t="n">
         <v>45993.775</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8241,13 +8462,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G38" s="28" t="n">
         <v>45993.78333333333</v>
       </c>
-      <c r="H38" s="27" t="n">
+      <c r="H38" s="28" t="n">
         <v>45993.81527777778</v>
       </c>
-      <c r="I38" s="27" t="n">
+      <c r="I38" s="28" t="n">
         <v>45993.88055555556</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -8267,7 +8488,7 @@
           <t>PT11720</t>
         </is>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C39" s="28" t="n">
         <v>46013.49513888889</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8283,13 +8504,13 @@
           <t>Fall / Hip Pain</t>
         </is>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G39" s="28" t="n">
         <v>46013.49722222222</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="28" t="n">
         <v>46013.51597222222</v>
       </c>
-      <c r="I39" s="27" t="n">
+      <c r="I39" s="28" t="n">
         <v>46013.78680555556</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -8309,7 +8530,7 @@
           <t>PT11727</t>
         </is>
       </c>
-      <c r="C40" s="27" t="n">
+      <c r="C40" s="28" t="n">
         <v>46006.34444444445</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8325,13 +8546,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="G40" s="28" t="n">
         <v>46006.34722222222</v>
       </c>
-      <c r="H40" s="27" t="n">
+      <c r="H40" s="28" t="n">
         <v>46006.35208333333</v>
       </c>
-      <c r="I40" s="27" t="n">
+      <c r="I40" s="28" t="n">
         <v>46006.51875</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -8351,7 +8572,7 @@
           <t>PT11783</t>
         </is>
       </c>
-      <c r="C41" s="27" t="n">
+      <c r="C41" s="28" t="n">
         <v>46017.37569444445</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8367,13 +8588,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G41" s="27" t="n">
+      <c r="G41" s="28" t="n">
         <v>46017.38194444445</v>
       </c>
-      <c r="H41" s="27" t="n">
+      <c r="H41" s="28" t="n">
         <v>46017.40972222222</v>
       </c>
-      <c r="I41" s="27" t="n">
+      <c r="I41" s="28" t="n">
         <v>46017.47777777778</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -8393,7 +8614,7 @@
           <t>PT11816</t>
         </is>
       </c>
-      <c r="C42" s="27" t="n">
+      <c r="C42" s="28" t="n">
         <v>46001.32847222222</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8409,13 +8630,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G42" s="27" t="n">
+      <c r="G42" s="28" t="n">
         <v>46001.33333333334</v>
       </c>
-      <c r="H42" s="27" t="n">
+      <c r="H42" s="28" t="n">
         <v>46001.33402777778</v>
       </c>
-      <c r="I42" s="27" t="n">
+      <c r="I42" s="28" t="n">
         <v>46001.59375</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -8435,7 +8656,7 @@
           <t>PT11968</t>
         </is>
       </c>
-      <c r="C43" s="27" t="n">
+      <c r="C43" s="28" t="n">
         <v>45998.75555555556</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8451,13 +8672,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G43" s="27" t="n">
+      <c r="G43" s="28" t="n">
         <v>45998.76527777778</v>
       </c>
-      <c r="H43" s="27" t="n">
+      <c r="H43" s="28" t="n">
         <v>45998.76597222222</v>
       </c>
-      <c r="I43" s="27" t="n">
+      <c r="I43" s="28" t="n">
         <v>45998.88472222222</v>
       </c>
       <c r="J43" t="inlineStr">
@@ -8477,7 +8698,7 @@
           <t>PT11968</t>
         </is>
       </c>
-      <c r="C44" s="27" t="n">
+      <c r="C44" s="28" t="n">
         <v>46003.28333333333</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8493,13 +8714,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G44" s="27" t="n">
+      <c r="G44" s="28" t="n">
         <v>46003.29027777778</v>
       </c>
-      <c r="H44" s="27" t="n">
+      <c r="H44" s="28" t="n">
         <v>46003.30625</v>
       </c>
-      <c r="I44" s="27" t="n">
+      <c r="I44" s="28" t="n">
         <v>46003.46527777778</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -8519,7 +8740,7 @@
           <t>PT11977</t>
         </is>
       </c>
-      <c r="C45" s="27" t="n">
+      <c r="C45" s="28" t="n">
         <v>46007.77708333333</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8535,13 +8756,13 @@
           <t>Bloody Stool / Vomiting Blood</t>
         </is>
       </c>
-      <c r="G45" s="27" t="n">
+      <c r="G45" s="28" t="n">
         <v>46007.79444444444</v>
       </c>
-      <c r="H45" s="27" t="n">
+      <c r="H45" s="28" t="n">
         <v>46007.81180555555</v>
       </c>
-      <c r="I45" s="27" t="n">
+      <c r="I45" s="28" t="n">
         <v>46007.98888888889</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -8561,7 +8782,7 @@
           <t>PT12024</t>
         </is>
       </c>
-      <c r="C46" s="27" t="n">
+      <c r="C46" s="28" t="n">
         <v>46001.67569444444</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8577,13 +8798,13 @@
           <t>Laceration</t>
         </is>
       </c>
-      <c r="G46" s="27" t="n">
+      <c r="G46" s="28" t="n">
         <v>46001.68263888889</v>
       </c>
-      <c r="H46" s="27" t="n">
+      <c r="H46" s="28" t="n">
         <v>46001.70277777778</v>
       </c>
-      <c r="I46" s="27" t="n">
+      <c r="I46" s="28" t="n">
         <v>46001.88541666666</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -8603,7 +8824,7 @@
           <t>PT12026</t>
         </is>
       </c>
-      <c r="C47" s="27" t="n">
+      <c r="C47" s="28" t="n">
         <v>46008.67013888889</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8619,13 +8840,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G47" s="27" t="n">
+      <c r="G47" s="28" t="n">
         <v>46008.67361111111</v>
       </c>
-      <c r="H47" s="27" t="n">
+      <c r="H47" s="28" t="n">
         <v>46008.73194444444</v>
       </c>
-      <c r="I47" s="27" t="n">
+      <c r="I47" s="28" t="n">
         <v>46008.83819444444</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -8645,7 +8866,7 @@
           <t>PT12054</t>
         </is>
       </c>
-      <c r="C48" s="27" t="n">
+      <c r="C48" s="28" t="n">
         <v>46021.48055555556</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -8661,13 +8882,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G48" s="27" t="n">
+      <c r="G48" s="28" t="n">
         <v>46021.48472222222</v>
       </c>
-      <c r="H48" s="27" t="n">
+      <c r="H48" s="28" t="n">
         <v>46021.53263888889</v>
       </c>
-      <c r="I48" s="27" t="n">
+      <c r="I48" s="28" t="n">
         <v>46021.61527777778</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -8687,7 +8908,7 @@
           <t>PT12159</t>
         </is>
       </c>
-      <c r="C49" s="27" t="n">
+      <c r="C49" s="28" t="n">
         <v>46007.76736111111</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -8703,13 +8924,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G49" s="27" t="n">
+      <c r="G49" s="28" t="n">
         <v>46007.76875</v>
       </c>
-      <c r="H49" s="27" t="n">
+      <c r="H49" s="28" t="n">
         <v>46007.78819444445</v>
       </c>
-      <c r="I49" s="27" t="n">
+      <c r="I49" s="28" t="n">
         <v>46007.94097222222</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -8729,7 +8950,7 @@
           <t>PT12166</t>
         </is>
       </c>
-      <c r="C50" s="27" t="n">
+      <c r="C50" s="28" t="n">
         <v>46020.66388888889</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -8745,13 +8966,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G50" s="27" t="n">
+      <c r="G50" s="28" t="n">
         <v>46020.67013888889</v>
       </c>
-      <c r="H50" s="27" t="n">
+      <c r="H50" s="28" t="n">
         <v>46020.71180555555</v>
       </c>
-      <c r="I50" s="27" t="n">
+      <c r="I50" s="28" t="n">
         <v>46020.79861111111</v>
       </c>
       <c r="J50" t="inlineStr">
@@ -8771,7 +8992,7 @@
           <t>PT12187</t>
         </is>
       </c>
-      <c r="C51" s="27" t="n">
+      <c r="C51" s="28" t="n">
         <v>45992.74791666667</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -8787,13 +9008,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G51" s="27" t="n">
+      <c r="G51" s="28" t="n">
         <v>45992.75625</v>
       </c>
-      <c r="H51" s="27" t="n">
+      <c r="H51" s="28" t="n">
         <v>45992.82083333333</v>
       </c>
-      <c r="I51" s="27" t="n">
+      <c r="I51" s="28" t="n">
         <v>45992.90625</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -8813,7 +9034,7 @@
           <t>PT12210</t>
         </is>
       </c>
-      <c r="C52" s="27" t="n">
+      <c r="C52" s="28" t="n">
         <v>46009.04722222222</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -8829,13 +9050,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G52" s="27" t="n">
+      <c r="G52" s="28" t="n">
         <v>46009.05763888889</v>
       </c>
-      <c r="H52" s="27" t="n">
+      <c r="H52" s="28" t="n">
         <v>46009.06180555555</v>
       </c>
-      <c r="I52" s="27" t="n">
+      <c r="I52" s="28" t="n">
         <v>46009.18819444445</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -8855,7 +9076,7 @@
           <t>PT12274</t>
         </is>
       </c>
-      <c r="C53" s="27" t="n">
+      <c r="C53" s="28" t="n">
         <v>46013.71180555555</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -8871,13 +9092,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G53" s="27" t="n">
+      <c r="G53" s="28" t="n">
         <v>46013.72430555556</v>
       </c>
-      <c r="H53" s="27" t="n">
+      <c r="H53" s="28" t="n">
         <v>46013.75972222222</v>
       </c>
-      <c r="I53" s="27" t="n">
+      <c r="I53" s="28" t="n">
         <v>46013.84652777778</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -8897,7 +9118,7 @@
           <t>PT12307</t>
         </is>
       </c>
-      <c r="C54" s="27" t="n">
+      <c r="C54" s="28" t="n">
         <v>45993.67083333333</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -8913,13 +9134,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G54" s="27" t="n">
+      <c r="G54" s="28" t="n">
         <v>45993.68402777778</v>
       </c>
-      <c r="H54" s="27" t="n">
+      <c r="H54" s="28" t="n">
         <v>45993.74236111111</v>
       </c>
-      <c r="I54" s="27" t="n">
+      <c r="I54" s="28" t="n">
         <v>45993.78055555555</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -8939,7 +9160,7 @@
           <t>PT12325</t>
         </is>
       </c>
-      <c r="C55" s="27" t="n">
+      <c r="C55" s="28" t="n">
         <v>46010.80902777778</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -8955,13 +9176,13 @@
           <t>Fall / Hip Pain</t>
         </is>
       </c>
-      <c r="G55" s="27" t="n">
+      <c r="G55" s="28" t="n">
         <v>46010.8125</v>
       </c>
-      <c r="H55" s="27" t="n">
+      <c r="H55" s="28" t="n">
         <v>46010.87361111111</v>
       </c>
-      <c r="I55" s="27" t="n">
+      <c r="I55" s="28" t="n">
         <v>46011.19652777778</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -8981,7 +9202,7 @@
           <t>PT12362</t>
         </is>
       </c>
-      <c r="C56" s="27" t="n">
+      <c r="C56" s="28" t="n">
         <v>46016.23888888889</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8997,13 +9218,13 @@
           <t>Nausea</t>
         </is>
       </c>
-      <c r="G56" s="27" t="n">
+      <c r="G56" s="28" t="n">
         <v>46016.24444444444</v>
       </c>
-      <c r="H56" s="27" t="n">
+      <c r="H56" s="28" t="n">
         <v>46016.26805555556</v>
       </c>
-      <c r="I56" s="27" t="n">
+      <c r="I56" s="28" t="n">
         <v>46016.29652777778</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -9023,7 +9244,7 @@
           <t>PT12399</t>
         </is>
       </c>
-      <c r="C57" s="27" t="n">
+      <c r="C57" s="28" t="n">
         <v>46014.87638888889</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9039,13 +9260,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G57" s="27" t="n">
+      <c r="G57" s="28" t="n">
         <v>46014.88263888889</v>
       </c>
-      <c r="H57" s="27" t="n">
+      <c r="H57" s="28" t="n">
         <v>46014.92430555556</v>
       </c>
-      <c r="I57" s="27" t="n">
+      <c r="I57" s="28" t="n">
         <v>46015.19097222222</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -9065,7 +9286,7 @@
           <t>PT12426</t>
         </is>
       </c>
-      <c r="C58" s="27" t="n">
+      <c r="C58" s="28" t="n">
         <v>46004.79097222222</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9081,13 +9302,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G58" s="27" t="n">
+      <c r="G58" s="28" t="n">
         <v>46004.79583333333</v>
       </c>
-      <c r="H58" s="27" t="n">
+      <c r="H58" s="28" t="n">
         <v>46004.8125</v>
       </c>
-      <c r="I58" s="27" t="n">
+      <c r="I58" s="28" t="n">
         <v>46004.86736111111</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -9107,7 +9328,7 @@
           <t>PT12454</t>
         </is>
       </c>
-      <c r="C59" s="27" t="n">
+      <c r="C59" s="28" t="n">
         <v>46000.40277777778</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9123,13 +9344,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G59" s="27" t="n">
+      <c r="G59" s="28" t="n">
         <v>46000.41805555556</v>
       </c>
-      <c r="H59" s="27" t="n">
+      <c r="H59" s="28" t="n">
         <v>46000.42986111111</v>
       </c>
-      <c r="I59" s="27" t="n">
+      <c r="I59" s="28" t="n">
         <v>46000.70347222222</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -9149,7 +9370,7 @@
           <t>PT12464</t>
         </is>
       </c>
-      <c r="C60" s="27" t="n">
+      <c r="C60" s="28" t="n">
         <v>46012.48888888889</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9165,13 +9386,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G60" s="27" t="n">
+      <c r="G60" s="28" t="n">
         <v>46012.49861111111</v>
       </c>
-      <c r="H60" s="27" t="n">
+      <c r="H60" s="28" t="n">
         <v>46012.55416666667</v>
       </c>
-      <c r="I60" s="27" t="n">
+      <c r="I60" s="28" t="n">
         <v>46012.78888888889</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -9191,7 +9412,7 @@
           <t>PT12485</t>
         </is>
       </c>
-      <c r="C61" s="27" t="n">
+      <c r="C61" s="28" t="n">
         <v>45998.61875</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9207,13 +9428,13 @@
           <t>Head Injury</t>
         </is>
       </c>
-      <c r="G61" s="27" t="n">
+      <c r="G61" s="28" t="n">
         <v>45998.62222222222</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H61" s="28" t="n">
         <v>45998.66597222222</v>
       </c>
-      <c r="I61" s="27" t="n">
+      <c r="I61" s="28" t="n">
         <v>45998.70138888889</v>
       </c>
       <c r="J61" t="inlineStr">
@@ -9233,7 +9454,7 @@
           <t>PT12485</t>
         </is>
       </c>
-      <c r="C62" s="27" t="n">
+      <c r="C62" s="28" t="n">
         <v>46019.37430555555</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9249,13 +9470,13 @@
           <t>Fall</t>
         </is>
       </c>
-      <c r="G62" s="27" t="n">
+      <c r="G62" s="28" t="n">
         <v>46019.38611111111</v>
       </c>
-      <c r="H62" s="27" t="n">
+      <c r="H62" s="28" t="n">
         <v>46019.43819444445</v>
       </c>
-      <c r="I62" s="27" t="n">
+      <c r="I62" s="28" t="n">
         <v>46019.59027777778</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -9275,7 +9496,7 @@
           <t>PT12544</t>
         </is>
       </c>
-      <c r="C63" s="27" t="n">
+      <c r="C63" s="28" t="n">
         <v>46005.71666666667</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9291,13 +9512,13 @@
           <t>Chest Pain</t>
         </is>
       </c>
-      <c r="G63" s="27" t="n">
+      <c r="G63" s="28" t="n">
         <v>46005.72638888889</v>
       </c>
-      <c r="H63" s="27" t="n">
+      <c r="H63" s="28" t="n">
         <v>46005.78541666667</v>
       </c>
-      <c r="I63" s="27" t="n">
+      <c r="I63" s="28" t="n">
         <v>46005.94791666666</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -9317,7 +9538,7 @@
           <t>PT12586</t>
         </is>
       </c>
-      <c r="C64" s="27" t="n">
+      <c r="C64" s="28" t="n">
         <v>46016.61944444444</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9333,13 +9554,13 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G64" s="27" t="n">
+      <c r="G64" s="28" t="n">
         <v>46016.62291666667</v>
       </c>
-      <c r="H64" s="27" t="n">
+      <c r="H64" s="28" t="n">
         <v>46016.73055555556</v>
       </c>
-      <c r="I64" s="27" t="n">
+      <c r="I64" s="28" t="n">
         <v>46017.02083333334</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -9359,7 +9580,7 @@
           <t>PT12635</t>
         </is>
       </c>
-      <c r="C65" s="27" t="n">
+      <c r="C65" s="28" t="n">
         <v>46014.85347222222</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -9375,13 +9596,13 @@
           <t>Rash</t>
         </is>
       </c>
-      <c r="G65" s="27" t="n">
+      <c r="G65" s="28" t="n">
         <v>46014.85833333333</v>
       </c>
-      <c r="H65" s="27" t="n">
+      <c r="H65" s="28" t="n">
         <v>46014.96944444445</v>
       </c>
-      <c r="I65" s="27" t="n">
+      <c r="I65" s="28" t="n">
         <v>46015.05972222222</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -9401,7 +9622,7 @@
           <t>PT12649</t>
         </is>
       </c>
-      <c r="C66" s="27" t="n">
+      <c r="C66" s="28" t="n">
         <v>46012.3875</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -9417,13 +9638,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G66" s="27" t="n">
+      <c r="G66" s="28" t="n">
         <v>46012.39166666667</v>
       </c>
-      <c r="H66" s="27" t="n">
+      <c r="H66" s="28" t="n">
         <v>46012.42916666667</v>
       </c>
-      <c r="I66" s="27" t="n">
+      <c r="I66" s="28" t="n">
         <v>46012.47291666667</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -9443,7 +9664,7 @@
           <t>PT12677</t>
         </is>
       </c>
-      <c r="C67" s="27" t="n">
+      <c r="C67" s="28" t="n">
         <v>45995.16388888889</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -9459,13 +9680,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G67" s="27" t="n">
+      <c r="G67" s="28" t="n">
         <v>45995.16666666666</v>
       </c>
-      <c r="H67" s="27" t="n">
+      <c r="H67" s="28" t="n">
         <v>45995.17430555556</v>
       </c>
-      <c r="I67" s="27" t="n">
+      <c r="I67" s="28" t="n">
         <v>45995.43333333333</v>
       </c>
       <c r="J67" t="inlineStr">
@@ -9485,7 +9706,7 @@
           <t>PT12687</t>
         </is>
       </c>
-      <c r="C68" s="27" t="n">
+      <c r="C68" s="28" t="n">
         <v>46020.64444444444</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -9501,13 +9722,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G68" s="27" t="n">
+      <c r="G68" s="28" t="n">
         <v>46020.64791666667</v>
       </c>
-      <c r="H68" s="27" t="n">
+      <c r="H68" s="28" t="n">
         <v>46020.69652777778</v>
       </c>
-      <c r="I68" s="27" t="n">
+      <c r="I68" s="28" t="n">
         <v>46020.74861111111</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -9527,7 +9748,7 @@
           <t>PT12732</t>
         </is>
       </c>
-      <c r="C69" s="27" t="n">
+      <c r="C69" s="28" t="n">
         <v>46013.72777777778</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -9543,13 +9764,13 @@
           <t>Laceration</t>
         </is>
       </c>
-      <c r="G69" s="27" t="n">
+      <c r="G69" s="28" t="n">
         <v>46013.73333333333</v>
       </c>
-      <c r="H69" s="27" t="n">
+      <c r="H69" s="28" t="n">
         <v>46013.73958333334</v>
       </c>
-      <c r="I69" s="27" t="n">
+      <c r="I69" s="28" t="n">
         <v>46013.9125</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -9569,7 +9790,7 @@
           <t>PT12770</t>
         </is>
       </c>
-      <c r="C70" s="27" t="n">
+      <c r="C70" s="28" t="n">
         <v>45998.23958333334</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -9585,13 +9806,13 @@
           <t>Anxiety / Palpitations</t>
         </is>
       </c>
-      <c r="G70" s="27" t="n">
+      <c r="G70" s="28" t="n">
         <v>45998.24791666667</v>
       </c>
-      <c r="H70" s="27" t="n">
+      <c r="H70" s="28" t="n">
         <v>45998.24861111111</v>
       </c>
-      <c r="I70" s="27" t="n">
+      <c r="I70" s="28" t="n">
         <v>45998.30763888889</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -9611,7 +9832,7 @@
           <t>PT12826</t>
         </is>
       </c>
-      <c r="C71" s="27" t="n">
+      <c r="C71" s="28" t="n">
         <v>45996.64097222222</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -9627,13 +9848,13 @@
           <t>Ankle Injury</t>
         </is>
       </c>
-      <c r="G71" s="27" t="n">
+      <c r="G71" s="28" t="n">
         <v>45996.64861111111</v>
       </c>
-      <c r="H71" s="27" t="n">
+      <c r="H71" s="28" t="n">
         <v>45996.69236111111</v>
       </c>
-      <c r="I71" s="27" t="n">
+      <c r="I71" s="28" t="n">
         <v>45996.76111111111</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -9653,7 +9874,7 @@
           <t>PT12829</t>
         </is>
       </c>
-      <c r="C72" s="27" t="n">
+      <c r="C72" s="28" t="n">
         <v>46010.43055555555</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -9669,13 +9890,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G72" s="27" t="n">
+      <c r="G72" s="28" t="n">
         <v>46010.43541666667</v>
       </c>
-      <c r="H72" s="27" t="n">
+      <c r="H72" s="28" t="n">
         <v>46010.48402777778</v>
       </c>
-      <c r="I72" s="27" t="n">
+      <c r="I72" s="28" t="n">
         <v>46010.54791666667</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -9695,7 +9916,7 @@
           <t>PT12851</t>
         </is>
       </c>
-      <c r="C73" s="27" t="n">
+      <c r="C73" s="28" t="n">
         <v>46009.11180555556</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -9711,13 +9932,13 @@
           <t>Head Injury</t>
         </is>
       </c>
-      <c r="G73" s="27" t="n">
+      <c r="G73" s="28" t="n">
         <v>46009.12569444445</v>
       </c>
-      <c r="H73" s="27" t="n">
+      <c r="H73" s="28" t="n">
         <v>46009.12638888889</v>
       </c>
-      <c r="I73" s="27" t="n">
+      <c r="I73" s="28" t="n">
         <v>46009.21736111111</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -9737,7 +9958,7 @@
           <t>PT12860</t>
         </is>
       </c>
-      <c r="C74" s="27" t="n">
+      <c r="C74" s="28" t="n">
         <v>46017.00208333333</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -9753,13 +9974,13 @@
           <t>Palpitations</t>
         </is>
       </c>
-      <c r="G74" s="27" t="n">
+      <c r="G74" s="28" t="n">
         <v>46017.01041666666</v>
       </c>
-      <c r="H74" s="27" t="n">
+      <c r="H74" s="28" t="n">
         <v>46017.01111111111</v>
       </c>
-      <c r="I74" s="27" t="n">
+      <c r="I74" s="28" t="n">
         <v>46017.17361111111</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -9779,7 +10000,7 @@
           <t>PT12890</t>
         </is>
       </c>
-      <c r="C75" s="27" t="n">
+      <c r="C75" s="28" t="n">
         <v>45997.28680555556</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -9795,13 +10016,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G75" s="27" t="n">
+      <c r="G75" s="28" t="n">
         <v>45997.29097222222</v>
       </c>
-      <c r="H75" s="27" t="n">
+      <c r="H75" s="28" t="n">
         <v>45997.30277777778</v>
       </c>
-      <c r="I75" s="27" t="n">
+      <c r="I75" s="28" t="n">
         <v>45997.4625</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -9821,7 +10042,7 @@
           <t>PT12893</t>
         </is>
       </c>
-      <c r="C76" s="27" t="n">
+      <c r="C76" s="28" t="n">
         <v>46006.75902777778</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -9837,13 +10058,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G76" s="27" t="n">
+      <c r="G76" s="28" t="n">
         <v>46006.76041666666</v>
       </c>
-      <c r="H76" s="27" t="n">
+      <c r="H76" s="28" t="n">
         <v>46006.84513888889</v>
       </c>
-      <c r="I76" s="27" t="n">
+      <c r="I76" s="28" t="n">
         <v>46006.91111111111</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -9863,7 +10084,7 @@
           <t>PT12945</t>
         </is>
       </c>
-      <c r="C77" s="27" t="n">
+      <c r="C77" s="28" t="n">
         <v>46012.37083333333</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -9879,13 +10100,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G77" s="27" t="n">
+      <c r="G77" s="28" t="n">
         <v>46012.37569444445</v>
       </c>
-      <c r="H77" s="27" t="n">
+      <c r="H77" s="28" t="n">
         <v>46012.39375</v>
       </c>
-      <c r="I77" s="27" t="n">
+      <c r="I77" s="28" t="n">
         <v>46012.60902777778</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -9905,7 +10126,7 @@
           <t>PT12963</t>
         </is>
       </c>
-      <c r="C78" s="27" t="n">
+      <c r="C78" s="28" t="n">
         <v>45999.46319444444</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -9921,13 +10142,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G78" s="27" t="n">
+      <c r="G78" s="28" t="n">
         <v>45999.47013888889</v>
       </c>
-      <c r="H78" s="27" t="n">
+      <c r="H78" s="28" t="n">
         <v>45999.48125</v>
       </c>
-      <c r="I78" s="27" t="n">
+      <c r="I78" s="28" t="n">
         <v>45999.58125</v>
       </c>
       <c r="J78" t="inlineStr">
@@ -9947,7 +10168,7 @@
           <t>PT12983</t>
         </is>
       </c>
-      <c r="C79" s="27" t="n">
+      <c r="C79" s="28" t="n">
         <v>46007.86041666667</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -9963,13 +10184,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G79" s="27" t="n">
+      <c r="G79" s="28" t="n">
         <v>46007.86319444444</v>
       </c>
-      <c r="H79" s="27" t="n">
+      <c r="H79" s="28" t="n">
         <v>46007.88263888889</v>
       </c>
-      <c r="I79" s="27" t="n">
+      <c r="I79" s="28" t="n">
         <v>46007.94166666667</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -9989,7 +10210,7 @@
           <t>PT12989</t>
         </is>
       </c>
-      <c r="C80" s="27" t="n">
+      <c r="C80" s="28" t="n">
         <v>45992.5125</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -10005,13 +10226,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G80" s="27" t="n">
+      <c r="G80" s="28" t="n">
         <v>45992.51319444444</v>
       </c>
-      <c r="H80" s="27" t="n">
+      <c r="H80" s="28" t="n">
         <v>45992.51388888889</v>
       </c>
-      <c r="I80" s="27" t="n">
+      <c r="I80" s="28" t="n">
         <v>45992.82152777778</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -10031,7 +10252,7 @@
           <t>PT13031</t>
         </is>
       </c>
-      <c r="C81" s="27" t="n">
+      <c r="C81" s="28" t="n">
         <v>46018.11597222222</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -10047,13 +10268,13 @@
           <t>Abdominal Pain</t>
         </is>
       </c>
-      <c r="G81" s="27" t="n">
+      <c r="G81" s="28" t="n">
         <v>46018.11875</v>
       </c>
-      <c r="H81" s="27" t="n">
+      <c r="H81" s="28" t="n">
         <v>46018.12986111111</v>
       </c>
-      <c r="I81" s="27" t="n">
+      <c r="I81" s="28" t="n">
         <v>46018.29513888889</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -10073,7 +10294,7 @@
           <t>PT13107</t>
         </is>
       </c>
-      <c r="C82" s="27" t="n">
+      <c r="C82" s="28" t="n">
         <v>46020.52083333334</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -10089,13 +10310,13 @@
           <t>Painful Urination / Fever</t>
         </is>
       </c>
-      <c r="G82" s="27" t="n">
+      <c r="G82" s="28" t="n">
         <v>46020.52430555555</v>
       </c>
-      <c r="H82" s="27" t="n">
+      <c r="H82" s="28" t="n">
         <v>46020.64236111111</v>
       </c>
-      <c r="I82" s="27" t="n">
+      <c r="I82" s="28" t="n">
         <v>46020.78888888889</v>
       </c>
       <c r="J82" t="inlineStr">
@@ -10115,7 +10336,7 @@
           <t>PT13158</t>
         </is>
       </c>
-      <c r="C83" s="27" t="n">
+      <c r="C83" s="28" t="n">
         <v>46006.4375</v>
       </c>
       <c r="D83" t="inlineStr">
@@ -10131,13 +10352,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G83" s="27" t="n">
+      <c r="G83" s="28" t="n">
         <v>46006.43888888889</v>
       </c>
-      <c r="H83" s="27" t="n">
+      <c r="H83" s="28" t="n">
         <v>46006.45902777778</v>
       </c>
-      <c r="I83" s="27" t="n">
+      <c r="I83" s="28" t="n">
         <v>46006.53888888889</v>
       </c>
       <c r="J83" t="inlineStr">
@@ -10157,7 +10378,7 @@
           <t>PT13305</t>
         </is>
       </c>
-      <c r="C84" s="27" t="n">
+      <c r="C84" s="28" t="n">
         <v>45998.60486111111</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -10173,13 +10394,13 @@
           <t>Vomiting / Dizziness</t>
         </is>
       </c>
-      <c r="G84" s="27" t="n">
+      <c r="G84" s="28" t="n">
         <v>45998.61041666667</v>
       </c>
-      <c r="H84" s="27" t="n">
+      <c r="H84" s="28" t="n">
         <v>45998.61666666667</v>
       </c>
-      <c r="I84" s="27" t="n">
+      <c r="I84" s="28" t="n">
         <v>45998.77291666667</v>
       </c>
       <c r="J84" t="inlineStr">
@@ -10199,7 +10420,7 @@
           <t>PT13330</t>
         </is>
       </c>
-      <c r="C85" s="27" t="n">
+      <c r="C85" s="28" t="n">
         <v>46003.71527777778</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -10215,13 +10436,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G85" s="27" t="n">
+      <c r="G85" s="28" t="n">
         <v>46003.71805555555</v>
       </c>
-      <c r="H85" s="27" t="n">
+      <c r="H85" s="28" t="n">
         <v>46003.75555555556</v>
       </c>
-      <c r="I85" s="27" t="n">
+      <c r="I85" s="28" t="n">
         <v>46003.78888888889</v>
       </c>
       <c r="J85" t="inlineStr">
@@ -10241,7 +10462,7 @@
           <t>PT13353</t>
         </is>
       </c>
-      <c r="C86" s="27" t="n">
+      <c r="C86" s="28" t="n">
         <v>46022.65</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -10257,13 +10478,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G86" s="27" t="n">
+      <c r="G86" s="28" t="n">
         <v>46022.65694444445</v>
       </c>
-      <c r="H86" s="27" t="n">
+      <c r="H86" s="28" t="n">
         <v>46022.68958333333</v>
       </c>
-      <c r="I86" s="27" t="n">
+      <c r="I86" s="28" t="n">
         <v>46022.82916666667</v>
       </c>
       <c r="J86" t="inlineStr">
@@ -10283,7 +10504,7 @@
           <t>PT13473</t>
         </is>
       </c>
-      <c r="C87" s="27" t="n">
+      <c r="C87" s="28" t="n">
         <v>46010.82361111111</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -10299,13 +10520,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G87" s="27" t="n">
+      <c r="G87" s="28" t="n">
         <v>46010.83194444444</v>
       </c>
-      <c r="H87" s="27" t="n">
+      <c r="H87" s="28" t="n">
         <v>46010.94722222222</v>
       </c>
-      <c r="I87" s="27" t="n">
+      <c r="I87" s="28" t="n">
         <v>46011.04861111111</v>
       </c>
       <c r="J87" t="inlineStr">
@@ -10325,7 +10546,7 @@
           <t>PT13601</t>
         </is>
       </c>
-      <c r="C88" s="27" t="n">
+      <c r="C88" s="28" t="n">
         <v>45992.75555555556</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -10341,13 +10562,13 @@
           <t>Skin Redness / Swelling</t>
         </is>
       </c>
-      <c r="G88" s="27" t="n">
+      <c r="G88" s="28" t="n">
         <v>45992.75972222222</v>
       </c>
-      <c r="H88" s="27" t="n">
+      <c r="H88" s="28" t="n">
         <v>45992.76944444444</v>
       </c>
-      <c r="I88" s="27" t="n">
+      <c r="I88" s="28" t="n">
         <v>45992.84305555555</v>
       </c>
       <c r="J88" t="inlineStr">
@@ -10367,7 +10588,7 @@
           <t>PT13632</t>
         </is>
       </c>
-      <c r="C89" s="27" t="n">
+      <c r="C89" s="28" t="n">
         <v>45994.4</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -10383,13 +10604,13 @@
           <t>Dizziness</t>
         </is>
       </c>
-      <c r="G89" s="27" t="n">
+      <c r="G89" s="28" t="n">
         <v>45994.40555555555</v>
       </c>
-      <c r="H89" s="27" t="n">
+      <c r="H89" s="28" t="n">
         <v>45994.43680555555</v>
       </c>
-      <c r="I89" s="27" t="n">
+      <c r="I89" s="28" t="n">
         <v>45994.70416666667</v>
       </c>
       <c r="J89" t="inlineStr">
@@ -10409,7 +10630,7 @@
           <t>PT13672</t>
         </is>
       </c>
-      <c r="C90" s="27" t="n">
+      <c r="C90" s="28" t="n">
         <v>45994.45208333333</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -10425,13 +10646,13 @@
           <t>Shortness of Breath</t>
         </is>
       </c>
-      <c r="G90" s="27" t="n">
+      <c r="G90" s="28" t="n">
         <v>45994.45833333334</v>
       </c>
-      <c r="H90" s="27" t="n">
+      <c r="H90" s="28" t="n">
         <v>45994.48472222222</v>
       </c>
-      <c r="I90" s="27" t="n">
+      <c r="I90" s="28" t="n">
         <v>45994.70277777778</v>
       </c>
       <c r="J90" t="inlineStr">
@@ -10451,7 +10672,7 @@
           <t>PT13682</t>
         </is>
       </c>
-      <c r="C91" s="27" t="n">
+      <c r="C91" s="28" t="n">
         <v>46005.61458333334</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -10467,13 +10688,13 @@
           <t>Headache</t>
         </is>
       </c>
-      <c r="G91" s="27" t="n">
+      <c r="G91" s="28" t="n">
         <v>46005.61666666667</v>
       </c>
-      <c r="H91" s="27" t="n">
+      <c r="H91" s="28" t="n">
         <v>46005.64861111111</v>
       </c>
-      <c r="I91" s="27" t="n">
+      <c r="I91" s="28" t="n">
         <v>46005.72986111111</v>
       </c>
       <c r="J91" t="inlineStr">
@@ -10493,7 +10714,7 @@
           <t>PT13806</t>
         </is>
       </c>
-      <c r="C92" s="27" t="n">
+      <c r="C92" s="28" t="n">
         <v>46002.34930555556</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -10509,13 +10730,13 @@
           <t>Head Injury</t>
         </is>
       </c>
-      <c r="G92" s="27" t="n">
+      <c r="G92" s="28" t="n">
         <v>46002.35347222222</v>
       </c>
-      <c r="H92" s="27" t="n">
+      <c r="H92" s="28" t="n">
         <v>46002.35416666666</v>
       </c>
-      <c r="I92" s="27" t="n">
+      <c r="I92" s="28" t="n">
         <v>46002.52152777778</v>
       </c>
       <c r="J92" t="inlineStr">
@@ -10535,7 +10756,7 @@
           <t>PT13869</t>
         </is>
       </c>
-      <c r="C93" s="27" t="n">
+      <c r="C93" s="28" t="n">
         <v>46001.64791666667</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -10551,13 +10772,13 @@
           <t>Cough / Fever</t>
         </is>
       </c>
-      <c r="G93" s="27" t="n">
+      <c r="G93" s="28" t="n">
         <v>46001.65138888889</v>
       </c>
-      <c r="H93" s="27" t="n">
+      <c r="H93" s="28" t="n">
         <v>46001.73680555556</v>
       </c>
-      <c r="I93" s="27" t="n">
+      <c r="I93" s="28" t="n">
         <v>46001.78333333333</v>
       </c>
       <c r="J93" t="inlineStr">
@@ -10577,7 +10798,7 @@
           <t>PT13940</t>
         </is>
       </c>
-      <c r="C94" s="27" t="n">
+      <c r="C94" s="28" t="n">
         <v>46010.40694444445</v>
       </c>
       <c r="D94" t="inlineStr">
@@ -10593,13 +10814,13 @@
           <t>Fainting</t>
         </is>
       </c>
-      <c r="G94" s="27" t="n">
+      <c r="G94" s="28" t="n">
         <v>46010.41180555556</v>
       </c>
-      <c r="H94" s="27" t="n">
+      <c r="H94" s="28" t="n">
         <v>46010.49236111111</v>
       </c>
-      <c r="I94" s="27" t="n">
+      <c r="I94" s="28" t="n">
         <v>46010.52569444444</v>
       </c>
       <c r="J94" t="inlineStr">
@@ -10610,227 +10831,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00BF9000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>Lesson 5.1 · Bonus: The high-acuity ED list</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="259" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Cedar Ridge's ED medical director reviews every high-acuity visit (ESI 1 or 2) each month. The tracking system exports the month's visits sorted by PatientID, and someone spends 20 minutes turning that export into a list. Automate it. The macro must:
-1. Filter the export's ESILevel column to values less than or equal to 2.
-2. Copy the visible rows, with the header, to a new sheet named HighAcuity.
-3. Sort that sheet by ESILevel (smallest first), then ArrivalDateTime (oldest first), and AutoFit the columns.
-4. Go back to the export and turn its filter off.
-Recording tips: Check that Use Relative References is off. Click A1 and turn the filter on with Data → Filter, then use the ESILevel filter arrow → Number Filters → Less Than Or Equal To → 2 → OK. Select the data with Ctrl + Shift + → and then Ctrl + Shift + ↓ (Mac: ⌘ + Shift + arrows), and copy it with Ctrl + C (Mac: ⌘ + C). Add a sheet with the + (New sheet) button next to the sheet tabs, paste with Ctrl + V (Mac: ⌘ + V), and rename the sheet by double-clicking its tab. In Data → Sort (Lesson 1.6), sort by ESILevel (Smallest to Largest), then click Add Level and pick ArrivalDateTime (Oldest to Newest). AutoFit every column: click the Select All button (the triangle where the row and column headings meet), then double-click any column boundary. Finish by clicking the ED_Nov tab, then A1, then Data → Filter again.
-Record it on ED_Nov (80 visits) as ExtractHighAcuity (shortcut Ctrl + Shift + H). Then delete the HighAcuity sheet it made (right-click its tab → Delete), open the VBE, and edit the code so it works on ED_Dec (93 visits). Guide section 9 lists the edits recorded code usually needs and what to do if the macro stops with a run-time error. Run it on ED_Dec. The gray cells read the HighAcuity sheet your macro builds from December, so they stay blank until it exists. While the sheet from your November recording is still there, they show ✘ Not yet or stay blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>There's nothing to type on this sheet. The gray cells read the HighAcuity sheet your macro builds from ED_Dec, and the Check column turns green when they match. Stuck? Read the hint, then Guide section 9. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16">
-        <f>"Score: "&amp;COUNTIF(E6:E10,"✔*")&amp;" of 5 auto-checked tasks correct"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Hint</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Your Answer</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>How many visits (data rows, not counting the header) are on the HighAcuity sheet built from ED_Dec?</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>COUNTIF on ED_Dec's ESILevel column gives you a target to compare with</t>
-        </is>
-      </c>
-      <c r="D6" cm="1" s="23">
-        <f t="array" ref="D6">IF(ISREF(INDIRECT("'HighAcuity'!A1")),COUNTA(INDIRECT("'HighAcuity'!A:A"))-1,"")</f>
-        <v/>
-      </c>
-      <c r="E6" s="22">
-        <f>IF(IFERROR(D6="",FALSE),"",IF(IFERROR(AND(ISNUMBER(D6),OR(ABS(D6-'Bonus Key'!$C$5)&lt;=0.0001)),FALSE),"✔ Correct","✘ Not yet"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Which EDVisitID is in the first data row (A2) of HighAcuity?</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>It should be the earliest ESI 1 arrival in December</t>
-        </is>
-      </c>
-      <c r="D7" cm="1" s="28">
-        <f t="array" ref="D7">IFERROR(INDIRECT("'HighAcuity'!A2")&amp;"","")</f>
-        <v/>
-      </c>
-      <c r="E7" s="22">
-        <f>IF(IFERROR(D7="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D7&amp;""))=LOWER(TRIM('Bonus Key'!$C$6&amp;""))),FALSE),"✔ Correct","✘ Not yet"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Which EDVisitID is in cell A5 of HighAcuity?</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>This cell depends on both sort levels</t>
-        </is>
-      </c>
-      <c r="D8" cm="1" s="28">
-        <f t="array" ref="D8">IFERROR(INDIRECT("'HighAcuity'!A5")&amp;"","")</f>
-        <v/>
-      </c>
-      <c r="E8" s="22">
-        <f>IF(IFERROR(D8="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D8&amp;""))=LOWER(TRIM('Bonus Key'!$C$7&amp;""))),FALSE),"✔ Correct","✘ Not yet"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>Which EDVisitID is in the last data row of HighAcuity?</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>Rows below row 21 are only sorted if the sort range adapts</t>
-        </is>
-      </c>
-      <c r="D9" cm="1" s="28">
-        <f t="array" ref="D9">IFERROR(IF(ISREF(INDIRECT("'HighAcuity'!A1")),INDEX(INDIRECT("'HighAcuity'!A:A"),MAX(1,COUNTA(INDIRECT("'HighAcuity'!A:A"))))&amp;"",""),"")</f>
-        <v/>
-      </c>
-      <c r="E9" s="22">
-        <f>IF(IFERROR(D9="",FALSE),"",IF(IFERROR(OR(LOWER(TRIM(D9&amp;""))=LOWER(TRIM('Bonus Key'!$C$8&amp;""))),FALSE),"✔ Correct","✘ Not yet"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>After your macro finishes, how many rows of ED_Dec are visible? The gray cell counts them with SUBTOTAL(103, …), which skips rows a filter hides. It should be every December visit. It stays blank until HighAcuity holds December visits.</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>Which sheet does the end of your recorded code go back to?</t>
-        </is>
-      </c>
-      <c r="D10" cm="1" s="23">
-        <f t="array" ref="D10">IFERROR(IF(ISREF(INDIRECT("'HighAcuity'!A1")),IF(COUNTIF(ED_Dec!A2:A94,INDIRECT("'HighAcuity'!A2")&amp;"")&gt;0,SUBTOTAL(103,ED_Dec!A2:A94),""),""),"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f>IF(IFERROR(D10="",FALSE),"",IF(IFERROR(AND(ISNUMBER(D10),OR(ABS(D10-'Bonus Key'!$C$9)&lt;=0.0001)),FALSE),"✔ Correct","✘ Not yet"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A3:E3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E6:E10">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>LEFT(E6,1)="✔"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>LEFT(E6,1)="✘"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10966,7 +10966,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="51" customHeight="1">
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
           <t>3</t>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
-          <t>F11: Alt + F11 on Windows, Option + F11 on a Mac (add Fn if your top-row keys control brightness and volume).</t>
+          <t>F11: Alt + F11 (Mac: Option + F11, or Developer → Visual Basic). On a Mac laptop, add Fn if your top-row keys control brightness and volume.</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Record the FormatCensusReport macro on the Census_Nov sheet by following the recipe in Guide section 7 (TOTAL row recorded with relative references, shortcut Ctrl + Shift + R). The gray cell finds the row your macro labeled TOTAL and reads its MidnightCensus cell, which should equal November's patient days.</t>
+          <t>Record the FormatCensusReport macro on the Census_Nov sheet by following the recipe in Guide section 7 (TOTAL row recorded with relative references, shortcut Ctrl + Shift + R, Mac: Option + ⌘ + Shift + R). The gray cell finds the row your macro labeled TOTAL and reads its MidnightCensus cell, which should equal November's patient days.</t>
         </is>
       </c>
       <c r="C11" s="32" t="n">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="D12" s="33" t="inlineStr">
         <is>
-          <t>In H32 type =G32/D32, then Percent Style and Increase Decimal once. The recorder stores it as "=RC[-1]/RC[-4]": same row, 1 and 4 columns to the left.</t>
+          <t>In H32 type =G32/D32, then click Home → Percent Style and Increase Decimal once. The recorder stores it as "=RC[-1]/RC[-4]": same row, 1 and 4 columns to the left.</t>
         </is>
       </c>
       <c r="E12" cm="1" s="35">
@@ -11197,7 +11197,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="81" customHeight="1">
+    <row r="13" ht="96" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -11205,12 +11205,12 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>In the Record Macro dialog you typed an uppercase R in the Shortcut key box. Which key combination runs the macro on Windows? Type it like Ctrl+Alt+X.</t>
+          <t>In the Record Macro dialog you typed an uppercase R in the Shortcut key box. Which key combination runs the macro on Windows? Type it like Ctrl + Alt + X.</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>Ctrl+Shift+R</t>
+          <t>Ctrl + Shift + R</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>A lowercase letter gives Ctrl + letter, which replaces Excel's own shortcut while this workbook is open (Ctrl + r would stop doing Fill Right). An uppercase letter adds Shift, which collides with far fewer built-in shortcuts. Change it later in Alt + F8 → select the macro → Options…</t>
+          <t>A lowercase letter gives Ctrl + letter, which replaces Excel's own shortcut while this workbook is open (Ctrl + r would stop doing Fill Right). An uppercase letter adds Shift, which collides with far fewer built-in shortcuts. Change it later with Macros (Alt + F8; Mac: Option + F8) → select the macro → Options…</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Go to Census_Dec and run your macro (Ctrl + Shift + R or your button). December has 31 days. The gray cell finds your TOTAL row and counts the daily rows above it. It should show all 31 days.</t>
+          <t>Go to Census_Dec and run your macro (Ctrl + Shift + R, Mac: Option + ⌘ + Shift + R, or your button). December has 31 days. The gray cell finds your TOTAL row and counts the daily rows above it. It should show all 31 days.</t>
         </is>
       </c>
       <c r="C15" s="32" t="n">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>Click the Census_Dec tab and press Ctrl + Shift + R. Selection.End(xlDown) finds the last date (row 32) and ActiveCell.Offset(1, 0) steps to row 33.</t>
+          <t>Click the Census_Dec tab and press Ctrl + Shift + R (Mac: Option + ⌘ + Shift + R). Selection.End(xlDown) finds the last date (row 32) and ActiveCell.Offset(1, 0) steps to row 33.</t>
         </is>
       </c>
       <c r="E15" cm="1" s="19">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>If you recorded the TOTAL steps with relative references off, the code says Range("A32").Select, so on December it types TOTAL over 12/31/2025 in row 32 and the gray cell shows 30. Ctrl + Down plus a relative one-row move finds the first empty row on any month. Macros can't be undone, so close without saving (or reopen your saved copy), fix the recording, and run it again.</t>
+          <t>If you recorded the TOTAL steps with relative references off, the code says Range("A32").Select, so on December it types TOTAL over 12/31/2025 in row 32 and the gray cell shows 30. Ctrl + ↓ (Mac: ⌘ + ↓) plus a relative one-row move finds the first empty row on any month. Macros can't be undone, so close without saving (or reopen your saved copy), fix the recording, and run it again.</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
     ActiveSheet.Name = "HighAcuity"                     ' EDIT: was Sheets("Sheet1").Select / .Name
     ActiveWorkbook.Worksheets("HighAcuity").Sort.SortFields.Clear
     ' EDIT: keys were Range("E2:E21") and Range("C2:C21"). One cell is enough
-    ' to name the key column. (.Add works in Excel 2007 and later; Excel 365 records .Add2.)
+    ' to name the key column. (.Add works in Excel 2007 and later; Microsoft 365 records .Add2.)
     ActiveWorkbook.Worksheets("HighAcuity").Sort.SortFields.Add Key:=Range("E1"), _
         SortOn:=xlSortOnValues, Order:=xlAscending, DataOption:=xlSortNormal
     ActiveWorkbook.Worksheets("HighAcuity").Sort.SortFields.Add Key:=Range("C1"), _
